--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-24.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.84</v>
+        <v>2.9</v>
       </c>
       <c r="G2" t="n">
         <v>3.15</v>
@@ -766,10 +766,10 @@
         <v>2.96</v>
       </c>
       <c r="I2" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="J2" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="K2" t="n">
         <v>3.05</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -954,19 +954,19 @@
         <v>2.18</v>
       </c>
       <c r="G3" t="n">
-        <v>2.58</v>
+        <v>2.42</v>
       </c>
       <c r="H3" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J3" t="n">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K3" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -1154,7 +1154,7 @@
         <v>1.93</v>
       </c>
       <c r="I4" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J4" t="n">
         <v>3.75</v>
@@ -1175,7 +1175,7 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q4" t="n">
         <v>1.64</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -1345,7 +1345,7 @@
         <v>2.52</v>
       </c>
       <c r="H5" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="I5" t="n">
         <v>2.94</v>
@@ -1354,7 +1354,7 @@
         <v>3.8</v>
       </c>
       <c r="K5" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -1539,7 +1539,7 @@
         <v>2.86</v>
       </c>
       <c r="H6" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I6" t="n">
         <v>3.25</v>
@@ -1566,7 +1566,7 @@
         <v>2.38</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -1730,16 +1730,16 @@
         <v>1.73</v>
       </c>
       <c r="G7" t="n">
-        <v>1.83</v>
+        <v>1.8</v>
       </c>
       <c r="H7" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I7" t="n">
-        <v>5.5</v>
+        <v>5.3</v>
       </c>
       <c r="J7" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K7" t="n">
         <v>4.7</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -2697,22 +2697,22 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G12" t="n">
-        <v>2.4</v>
+        <v>2.18</v>
       </c>
       <c r="H12" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I12" t="n">
         <v>6</v>
       </c>
       <c r="J12" t="n">
-        <v>2.68</v>
+        <v>3.05</v>
       </c>
       <c r="K12" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -3088,19 +3088,19 @@
         <v>2.14</v>
       </c>
       <c r="G14" t="n">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
       <c r="H14" t="n">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="I14" t="n">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="J14" t="n">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="K14" t="n">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -3279,22 +3279,22 @@
         </is>
       </c>
       <c r="F15" t="n">
-        <v>1.98</v>
+        <v>4.4</v>
       </c>
       <c r="G15" t="n">
-        <v>9.199999999999999</v>
+        <v>6</v>
       </c>
       <c r="H15" t="n">
-        <v>1.63</v>
+        <v>1.69</v>
       </c>
       <c r="I15" t="n">
-        <v>2.02</v>
+        <v>1.86</v>
       </c>
       <c r="J15" t="n">
-        <v>3.65</v>
+        <v>4</v>
       </c>
       <c r="K15" t="n">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -3727,7 +3727,7 @@
         <v>10.5</v>
       </c>
       <c r="Z17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AA17" t="n">
         <v>18</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -3963,7 +3963,7 @@
         <v>110</v>
       </c>
       <c r="AN18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AO18" t="n">
         <v>38</v>
@@ -4014,7 +4014,7 @@
         <v>44</v>
       </c>
       <c r="BE18" t="n">
-        <v>42</v>
+        <v>70</v>
       </c>
       <c r="BF18" t="n">
         <v>30</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -4055,19 +4055,19 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G19" t="n">
         <v>4.1</v>
       </c>
       <c r="H19" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="I19" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="J19" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K19" t="n">
         <v>4.4</v>
@@ -4085,7 +4085,7 @@
         <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q19" t="n">
         <v>1.55</v>
@@ -4109,40 +4109,40 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>30</v>
+        <v>44</v>
       </c>
       <c r="Y19" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="Z19" t="n">
-        <v>17</v>
+        <v>15.5</v>
       </c>
       <c r="AA19" t="n">
         <v>24</v>
       </c>
       <c r="AB19" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AC19" t="n">
         <v>10.5</v>
       </c>
       <c r="AD19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AE19" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AF19" t="n">
-        <v>60</v>
+        <v>34</v>
       </c>
       <c r="AG19" t="n">
-        <v>18.5</v>
+        <v>16.5</v>
       </c>
       <c r="AH19" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AI19" t="n">
-        <v>29</v>
+        <v>42</v>
       </c>
       <c r="AJ19" t="n">
         <v>1000</v>
@@ -4157,7 +4157,7 @@
         <v>1000</v>
       </c>
       <c r="AN19" t="n">
-        <v>32</v>
+        <v>50</v>
       </c>
       <c r="AO19" t="n">
         <v>9.4</v>
@@ -4211,14 +4211,14 @@
         <v>46</v>
       </c>
       <c r="BF19" t="n">
-        <v>19.5</v>
+        <v>24</v>
       </c>
       <c r="BG19" t="n">
         <v>7.6</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="G21" t="n">
         <v>4.6</v>
@@ -4455,7 +4455,7 @@
         <v>2.54</v>
       </c>
       <c r="J21" t="n">
-        <v>2.74</v>
+        <v>2.76</v>
       </c>
       <c r="K21" t="n">
         <v>3.05</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -4640,13 +4640,13 @@
         <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="H22" t="n">
         <v>2.38</v>
       </c>
       <c r="I22" t="n">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="J22" t="n">
         <v>3.25</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -4834,19 +4834,19 @@
         <v>3.75</v>
       </c>
       <c r="G23" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="H23" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="I23" t="n">
         <v>2.34</v>
       </c>
       <c r="J23" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K23" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4861,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.08</v>
+        <v>2.26</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -5025,13 +5025,13 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="G24" t="n">
         <v>1.59</v>
       </c>
       <c r="H24" t="n">
-        <v>2.78</v>
+        <v>7.2</v>
       </c>
       <c r="I24" t="n">
         <v>1000</v>
@@ -5040,7 +5040,7 @@
         <v>3.7</v>
       </c>
       <c r="K24" t="n">
-        <v>5.1</v>
+        <v>4.2</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -5219,7 +5219,7 @@
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="G25" t="n">
         <v>5.6</v>
@@ -5228,13 +5228,13 @@
         <v>1.95</v>
       </c>
       <c r="I25" t="n">
-        <v>2.08</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
         <v>3.25</v>
       </c>
       <c r="K25" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G26" t="n">
         <v>3.5</v>
@@ -5422,7 +5422,7 @@
         <v>2.8</v>
       </c>
       <c r="I26" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J26" t="n">
         <v>2.72</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-22 00:49:35</t>
+          <t>2026-04-22 03:05:10</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-24.xlsx
@@ -766,13 +766,13 @@
         <v>2.96</v>
       </c>
       <c r="I2" t="n">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="J2" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="K2" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -787,7 +787,7 @@
         <v>0</v>
       </c>
       <c r="P2" t="n">
-        <v>1.37</v>
+        <v>1.32</v>
       </c>
       <c r="Q2" t="n">
         <v>2.78</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -954,19 +954,19 @@
         <v>2.18</v>
       </c>
       <c r="G3" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="H3" t="n">
         <v>3.7</v>
       </c>
       <c r="I3" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="J3" t="n">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K3" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.25</v>
+        <v>1.59</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
         <v>2.16</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -1348,10 +1348,10 @@
         <v>2.82</v>
       </c>
       <c r="I5" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K5" t="n">
         <v>4</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.64</v>
+        <v>1.76</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
         <v>2.7</v>
       </c>
       <c r="I6" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J6" t="n">
         <v>3.45</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.26</v>
+        <v>2.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.93</v>
+        <v>2.1</v>
       </c>
       <c r="G8" t="n">
-        <v>2.54</v>
+        <v>2.36</v>
       </c>
       <c r="H8" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="I8" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="J8" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="K8" t="n">
-        <v>5.6</v>
+        <v>3.9</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.8</v>
+        <v>1.94</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.72</v>
+        <v>1.9</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -2115,22 +2115,22 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.4</v>
+        <v>2.64</v>
       </c>
       <c r="G9" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="H9" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="I9" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="J9" t="n">
         <v>3.35</v>
       </c>
-      <c r="H9" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="J9" t="n">
-        <v>3.25</v>
-      </c>
       <c r="K9" t="n">
-        <v>6.6</v>
+        <v>3.85</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.82</v>
+        <v>1.92</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.78</v>
+        <v>1.89</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -2309,22 +2309,22 @@
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.61</v>
+        <v>1.71</v>
       </c>
       <c r="G10" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="H10" t="n">
-        <v>2.08</v>
+        <v>4.5</v>
       </c>
       <c r="I10" t="n">
-        <v>10</v>
+        <v>5.9</v>
       </c>
       <c r="J10" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="K10" t="n">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,7 +2339,7 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="Q10" t="n">
         <v>1.69</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -2503,22 +2503,22 @@
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="G11" t="n">
         <v>4.8</v>
       </c>
       <c r="H11" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="I11" t="n">
         <v>3.1</v>
       </c>
       <c r="J11" t="n">
-        <v>2.5</v>
+        <v>2.58</v>
       </c>
       <c r="K11" t="n">
-        <v>4.1</v>
+        <v>2.98</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,7 +2533,7 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="Q11" t="n">
         <v>3</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -2700,7 +2700,7 @@
         <v>1.98</v>
       </c>
       <c r="G12" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="H12" t="n">
         <v>4.7</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.4</v>
+        <v>1.51</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.4</v>
+        <v>2.7</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -2891,22 +2891,22 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.05</v>
+        <v>3.3</v>
       </c>
       <c r="G13" t="n">
-        <v>4.8</v>
+        <v>4</v>
       </c>
       <c r="H13" t="n">
-        <v>1.93</v>
+        <v>2.06</v>
       </c>
       <c r="I13" t="n">
-        <v>2.54</v>
+        <v>2.24</v>
       </c>
       <c r="J13" t="n">
-        <v>3.1</v>
+        <v>3.8</v>
       </c>
       <c r="K13" t="n">
-        <v>6.8</v>
+        <v>4.3</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.06</v>
+        <v>2.32</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.61</v>
+        <v>1.72</v>
       </c>
       <c r="Q14" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -3282,13 +3282,13 @@
         <v>4.4</v>
       </c>
       <c r="G15" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="H15" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="I15" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="J15" t="n">
         <v>4</v>
@@ -3312,7 +3312,7 @@
         <v>2.38</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -3473,22 +3473,22 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.43</v>
+        <v>1.47</v>
       </c>
       <c r="G16" t="n">
-        <v>1.7</v>
+        <v>1.61</v>
       </c>
       <c r="H16" t="n">
-        <v>2.42</v>
+        <v>5.2</v>
       </c>
       <c r="I16" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
       <c r="J16" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="K16" t="n">
-        <v>950</v>
+        <v>5.1</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -3706,7 +3706,7 @@
         <v>1.51</v>
       </c>
       <c r="S17" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T17" t="n">
         <v>1.75</v>
@@ -3721,7 +3721,7 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="Y17" t="n">
         <v>10.5</v>
@@ -3811,26 +3811,26 @@
         <v>22</v>
       </c>
       <c r="BB17" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="BC17" t="n">
         <v>38</v>
       </c>
       <c r="BD17" t="n">
-        <v>11</v>
+        <v>40</v>
       </c>
       <c r="BE17" t="n">
         <v>70</v>
       </c>
       <c r="BF17" t="n">
-        <v>44</v>
+        <v>10.5</v>
       </c>
       <c r="BG17" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="G18" t="n">
         <v>2.86</v>
@@ -3873,10 +3873,10 @@
         <v>2.88</v>
       </c>
       <c r="J18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K18" t="n">
         <v>3.35</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.4</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3903,7 +3903,7 @@
         <v>4.2</v>
       </c>
       <c r="T18" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="U18" t="n">
         <v>2.04</v>
@@ -3939,7 +3939,7 @@
         <v>40</v>
       </c>
       <c r="AF18" t="n">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AG18" t="n">
         <v>13</v>
@@ -3963,7 +3963,7 @@
         <v>110</v>
       </c>
       <c r="AN18" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AO18" t="n">
         <v>38</v>
@@ -4005,7 +4005,7 @@
         <v>44</v>
       </c>
       <c r="BB18" t="n">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="BC18" t="n">
         <v>27</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -4130,7 +4130,7 @@
         <v>11</v>
       </c>
       <c r="AE19" t="n">
-        <v>17.5</v>
+        <v>21</v>
       </c>
       <c r="AF19" t="n">
         <v>34</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -4252,19 +4252,19 @@
         <v>2.32</v>
       </c>
       <c r="G20" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="H20" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="I20" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="J20" t="n">
         <v>3.35</v>
       </c>
       <c r="K20" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -4458,7 +4458,7 @@
         <v>2.76</v>
       </c>
       <c r="K21" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.1</v>
+        <v>3.3</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -4640,19 +4640,19 @@
         <v>3</v>
       </c>
       <c r="G22" t="n">
-        <v>3.7</v>
+        <v>3.45</v>
       </c>
       <c r="H22" t="n">
-        <v>2.38</v>
+        <v>2.34</v>
       </c>
       <c r="I22" t="n">
         <v>2.68</v>
       </c>
       <c r="J22" t="n">
-        <v>3.25</v>
+        <v>2.96</v>
       </c>
       <c r="K22" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4667,10 +4667,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.24</v>
+        <v>1.85</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -4864,7 +4864,7 @@
         <v>1.67</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.25</v>
+        <v>1.62</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
         <v>3.25</v>
       </c>
       <c r="K25" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -5249,7 +5249,7 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.5</v>
+        <v>1.54</v>
       </c>
       <c r="Q25" t="n">
         <v>2.6</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>
@@ -5416,16 +5416,16 @@
         <v>2.8</v>
       </c>
       <c r="G26" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="H26" t="n">
         <v>2.8</v>
       </c>
       <c r="I26" t="n">
-        <v>3.45</v>
+        <v>3</v>
       </c>
       <c r="J26" t="n">
-        <v>2.72</v>
+        <v>2.94</v>
       </c>
       <c r="K26" t="n">
         <v>3.4</v>
@@ -5443,10 +5443,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.25</v>
+        <v>1.68</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-22 03:05:10</t>
+          <t>2026-04-22 05:21:00</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH26"/>
+  <dimension ref="A1:BH27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Australian A-League Men</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,184 +743,184 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>06:35:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Pharco FC</t>
+          <t>Macarthur FC</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Wellington Phoenix</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.9</v>
+        <v>2.02</v>
       </c>
       <c r="G2" t="n">
-        <v>3.15</v>
+        <v>2.14</v>
       </c>
       <c r="H2" t="n">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="I2" t="n">
-        <v>3.35</v>
+        <v>3.65</v>
       </c>
       <c r="J2" t="n">
-        <v>2.82</v>
+        <v>4.1</v>
       </c>
       <c r="K2" t="n">
-        <v>3</v>
+        <v>4.6</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>1.32</v>
+        <v>2.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.78</v>
+        <v>1.53</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AS2" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AT2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AU2" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AV2" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AX2" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AY2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BB2" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BC2" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BD2" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BG2" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
@@ -942,31 +942,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Pharco FC</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.18</v>
+        <v>2.9</v>
       </c>
       <c r="G3" t="n">
-        <v>2.5</v>
+        <v>3.15</v>
       </c>
       <c r="H3" t="n">
-        <v>3.7</v>
+        <v>2.96</v>
       </c>
       <c r="I3" t="n">
-        <v>4.7</v>
+        <v>3.35</v>
       </c>
       <c r="J3" t="n">
-        <v>3.05</v>
+        <v>2.82</v>
       </c>
       <c r="K3" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="L3" t="n">
         <v>0</v>
@@ -981,10 +981,10 @@
         <v>0</v>
       </c>
       <c r="P3" t="n">
-        <v>1.59</v>
+        <v>1.45</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.42</v>
+        <v>2.98</v>
       </c>
       <c r="R3" t="n">
         <v>0</v>
@@ -1114,14 +1114,14 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,36 +1131,36 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>3.95</v>
+        <v>2.18</v>
       </c>
       <c r="G4" t="n">
-        <v>4.3</v>
+        <v>2.54</v>
       </c>
       <c r="H4" t="n">
-        <v>1.93</v>
+        <v>3.7</v>
       </c>
       <c r="I4" t="n">
-        <v>2.04</v>
+        <v>4.8</v>
       </c>
       <c r="J4" t="n">
-        <v>3.75</v>
+        <v>2.98</v>
       </c>
       <c r="K4" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="L4" t="n">
         <v>0</v>
@@ -1175,10 +1175,10 @@
         <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>2.16</v>
+        <v>1.59</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.76</v>
+        <v>2.42</v>
       </c>
       <c r="R4" t="n">
         <v>0</v>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
@@ -1330,31 +1330,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.48</v>
+        <v>3.95</v>
       </c>
       <c r="G5" t="n">
-        <v>2.52</v>
+        <v>4.3</v>
       </c>
       <c r="H5" t="n">
-        <v>2.82</v>
+        <v>1.93</v>
       </c>
       <c r="I5" t="n">
-        <v>2.96</v>
+        <v>2.04</v>
       </c>
       <c r="J5" t="n">
         <v>3.75</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1502,14 +1502,14 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,36 +1519,36 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12:45:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Al-Fateh (KSA)</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al-Khaleej Saihat</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="G6" t="n">
-        <v>2.86</v>
+        <v>2.52</v>
       </c>
       <c r="H6" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="I6" t="n">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="J6" t="n">
-        <v>3.45</v>
+        <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,10 +1563,10 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.38</v>
+        <v>2.14</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="R6" t="n">
         <v>0</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,37 +1713,37 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:45:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Al-Fateh (KSA)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Al-Khaleej Saihat</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1.73</v>
+        <v>2.4</v>
       </c>
       <c r="G7" t="n">
-        <v>1.8</v>
+        <v>2.86</v>
       </c>
       <c r="H7" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="I7" t="n">
-        <v>5.3</v>
+        <v>3.25</v>
       </c>
       <c r="J7" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="K7" t="n">
         <v>4.3</v>
       </c>
-      <c r="K7" t="n">
-        <v>4.7</v>
-      </c>
       <c r="L7" t="n">
         <v>0</v>
       </c>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.5</v>
+        <v>2.38</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.53</v>
+        <v>1.61</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1912,31 +1912,31 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Znicz Pruszkow</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Gornik Leczna</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.1</v>
+        <v>1.72</v>
       </c>
       <c r="G8" t="n">
-        <v>2.36</v>
+        <v>1.81</v>
       </c>
       <c r="H8" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="I8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J8" t="n">
-        <v>3.45</v>
+        <v>4.3</v>
       </c>
       <c r="K8" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>1.94</v>
+        <v>2.44</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.9</v>
+        <v>1.58</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,36 +2101,36 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13:10:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Al-Hazm (KSA)</t>
+          <t>Znicz Pruszkow</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>Gornik Leczna</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.64</v>
+        <v>2.1</v>
       </c>
       <c r="G9" t="n">
-        <v>3.05</v>
+        <v>2.36</v>
       </c>
       <c r="H9" t="n">
-        <v>2.54</v>
+        <v>3.45</v>
       </c>
       <c r="I9" t="n">
-        <v>2.92</v>
+        <v>4.3</v>
       </c>
       <c r="J9" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K9" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,37 +2295,37 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:10:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Al-Hazm (KSA)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Esbjerg</t>
+          <t>Al Riyadh SC</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>1.71</v>
+        <v>2.64</v>
       </c>
       <c r="G10" t="n">
-        <v>1.92</v>
+        <v>3.05</v>
       </c>
       <c r="H10" t="n">
-        <v>4.5</v>
+        <v>2.54</v>
       </c>
       <c r="I10" t="n">
-        <v>5.9</v>
+        <v>2.96</v>
       </c>
       <c r="J10" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K10" t="n">
         <v>3.85</v>
       </c>
-      <c r="K10" t="n">
-        <v>4.5</v>
-      </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>2.14</v>
+        <v>1.91</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.69</v>
+        <v>1.89</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2494,31 +2494,31 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Modern Sport FC</t>
+          <t>Esbjerg</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>3.45</v>
+        <v>1.71</v>
       </c>
       <c r="G11" t="n">
-        <v>4.8</v>
+        <v>1.92</v>
       </c>
       <c r="H11" t="n">
-        <v>2.38</v>
+        <v>4.5</v>
       </c>
       <c r="I11" t="n">
-        <v>3.1</v>
+        <v>5.9</v>
       </c>
       <c r="J11" t="n">
-        <v>2.58</v>
+        <v>3.85</v>
       </c>
       <c r="K11" t="n">
-        <v>2.98</v>
+        <v>4.5</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.27</v>
+        <v>2.14</v>
       </c>
       <c r="Q11" t="n">
-        <v>3</v>
+        <v>1.69</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
@@ -2688,31 +2688,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Modern Sport FC</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.98</v>
+        <v>3.6</v>
       </c>
       <c r="G12" t="n">
-        <v>2.12</v>
+        <v>4.3</v>
       </c>
       <c r="H12" t="n">
-        <v>4.7</v>
+        <v>2.4</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>2.92</v>
       </c>
       <c r="J12" t="n">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="K12" t="n">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="Q12" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2877,36 +2877,36 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Etoile Carouge</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.3</v>
+        <v>1.98</v>
       </c>
       <c r="G13" t="n">
-        <v>4</v>
+        <v>2.12</v>
       </c>
       <c r="H13" t="n">
-        <v>2.06</v>
+        <v>4.7</v>
       </c>
       <c r="I13" t="n">
-        <v>2.24</v>
+        <v>6</v>
       </c>
       <c r="J13" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="K13" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>2.32</v>
+        <v>1.51</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.64</v>
+        <v>2.72</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3076,31 +3076,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>FC Blau Weiss Linz</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Etoile Carouge</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>2.14</v>
+        <v>3.3</v>
       </c>
       <c r="G14" t="n">
-        <v>2.26</v>
+        <v>4</v>
       </c>
       <c r="H14" t="n">
-        <v>3.85</v>
+        <v>2.06</v>
       </c>
       <c r="I14" t="n">
-        <v>4.4</v>
+        <v>2.24</v>
       </c>
       <c r="J14" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="K14" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.72</v>
+        <v>2.32</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.14</v>
+        <v>1.64</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,36 +3265,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>15:15:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>FC Blau Weiss Linz</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>FC Vaduz</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="F15" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="G15" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H15" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I15" t="n">
         <v>4.4</v>
       </c>
-      <c r="G15" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="I15" t="n">
-        <v>1.85</v>
-      </c>
       <c r="J15" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="K15" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>2.38</v>
+        <v>1.72</v>
       </c>
       <c r="Q15" t="n">
-        <v>1.58</v>
+        <v>2.14</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,36 +3459,36 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wisla Krakow</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Puszcza Niepolomice</t>
+          <t>FC Vaduz</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.47</v>
+        <v>4.4</v>
       </c>
       <c r="G16" t="n">
-        <v>1.61</v>
+        <v>5.2</v>
       </c>
       <c r="H16" t="n">
-        <v>5.2</v>
+        <v>1.7</v>
       </c>
       <c r="I16" t="n">
-        <v>10</v>
+        <v>1.85</v>
       </c>
       <c r="J16" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K16" t="n">
-        <v>5.1</v>
+        <v>4.8</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.69</v>
+        <v>1.58</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>French Ligue 1</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,66 +3653,66 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Wisla Krakow</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Puszcza Niepolomice</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>5</v>
+        <v>1.53</v>
       </c>
       <c r="G17" t="n">
-        <v>5.4</v>
+        <v>1.67</v>
       </c>
       <c r="H17" t="n">
-        <v>1.73</v>
+        <v>6.4</v>
       </c>
       <c r="I17" t="n">
-        <v>1.74</v>
+        <v>9</v>
       </c>
       <c r="J17" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K17" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N17" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O17" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.72</v>
+        <v>1.81</v>
       </c>
       <c r="R17" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T17" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="U17" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -3721,123 +3721,123 @@
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Y17" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Z17" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AA17" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AB17" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AC17" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AD17" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AE17" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AG17" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AH17" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AI17" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AJ17" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AK17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AL17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AM17" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AN17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AO17" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AP17" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AQ17" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AR17" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AS17" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AT17" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AU17" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AV17" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AW17" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AX17" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AY17" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AZ17" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BA17" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BB17" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BC17" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BD17" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BE17" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="BF17" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BG17" t="n">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>French Ligue 1</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,67 +3847,67 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>2.82</v>
+        <v>5</v>
       </c>
       <c r="G18" t="n">
-        <v>2.86</v>
+        <v>5.4</v>
       </c>
       <c r="H18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="I18" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="J18" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L18" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="N18" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O18" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="P18" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S18" t="n">
         <v>2.84</v>
       </c>
-      <c r="I18" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="J18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K18" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="L18" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="N18" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="O18" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="P18" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="Q18" t="n">
+      <c r="T18" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="U18" t="n">
         <v>2.24</v>
       </c>
-      <c r="R18" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S18" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="U18" t="n">
-        <v>2.04</v>
-      </c>
       <c r="V18" t="n">
         <v>0</v>
       </c>
@@ -3915,123 +3915,123 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
+        <v>23</v>
+      </c>
+      <c r="Y18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="Z18" t="n">
         <v>11.5</v>
       </c>
-      <c r="Y18" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="Z18" t="n">
-        <v>19</v>
-      </c>
       <c r="AA18" t="n">
-        <v>50</v>
+        <v>18</v>
       </c>
       <c r="AB18" t="n">
+        <v>22</v>
+      </c>
+      <c r="AC18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD18" t="n">
         <v>10</v>
       </c>
-      <c r="AC18" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD18" t="n">
-        <v>13</v>
-      </c>
       <c r="AE18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF18" t="n">
+        <v>48</v>
+      </c>
+      <c r="AG18" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI18" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ18" t="n">
+        <v>140</v>
+      </c>
+      <c r="AK18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AL18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM18" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>70</v>
+      </c>
+      <c r="AO18" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AP18" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ18" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>11</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>18</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="BC18" t="n">
+        <v>38</v>
+      </c>
+      <c r="BD18" t="n">
         <v>40</v>
       </c>
-      <c r="AF18" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AG18" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH18" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ18" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK18" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL18" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM18" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>40</v>
-      </c>
-      <c r="AO18" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP18" t="n">
+      <c r="BE18" t="n">
+        <v>12</v>
+      </c>
+      <c r="BF18" t="n">
         <v>10.5</v>
       </c>
-      <c r="AQ18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AR18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS18" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>28</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>38</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>27</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE18" t="n">
-        <v>70</v>
-      </c>
-      <c r="BF18" t="n">
-        <v>30</v>
-      </c>
       <c r="BG18" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4046,61 +4046,61 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>3.75</v>
+        <v>2.82</v>
       </c>
       <c r="G19" t="n">
-        <v>4.1</v>
+        <v>2.86</v>
       </c>
       <c r="H19" t="n">
-        <v>1.92</v>
+        <v>2.86</v>
       </c>
       <c r="I19" t="n">
-        <v>1.98</v>
+        <v>2.88</v>
       </c>
       <c r="J19" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N19" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O19" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P19" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R19" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S19" t="n">
         <v>4.2</v>
       </c>
-      <c r="K19" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>2.66</v>
-      </c>
-      <c r="Q19" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
       <c r="T19" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="U19" t="n">
-        <v>2.62</v>
+        <v>2.04</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4109,123 +4109,123 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="Z19" t="n">
+        <v>18.5</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>48</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>38</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>38</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AU19" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ19" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA19" t="n">
         <v>44</v>
       </c>
-      <c r="Y19" t="n">
-        <v>14</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AA19" t="n">
-        <v>24</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>28</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE19" t="n">
+      <c r="BB19" t="n">
+        <v>38</v>
+      </c>
+      <c r="BC19" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD19" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE19" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF19" t="n">
         <v>21</v>
       </c>
-      <c r="AF19" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG19" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>95</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>50</v>
-      </c>
-      <c r="AO19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>21</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>18</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD19" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE19" t="n">
-        <v>46</v>
-      </c>
-      <c r="BF19" t="n">
-        <v>24</v>
-      </c>
       <c r="BG19" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,42 +4235,42 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Arouca</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.32</v>
+        <v>3.75</v>
       </c>
       <c r="G20" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="H20" t="n">
-        <v>3.25</v>
+        <v>1.92</v>
       </c>
       <c r="I20" t="n">
-        <v>3.6</v>
+        <v>1.98</v>
       </c>
       <c r="J20" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="K20" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N20" t="n">
         <v>0</v>
@@ -4279,10 +4279,10 @@
         <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="R20" t="n">
         <v>0</v>
@@ -4291,10 +4291,10 @@
         <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4303,123 +4303,123 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AT20" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AY20" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BG20" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,36 +4429,36 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>Arouca</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.9</v>
+        <v>2.32</v>
       </c>
       <c r="G21" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="H21" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="I21" t="n">
-        <v>2.54</v>
+        <v>3.6</v>
       </c>
       <c r="J21" t="n">
-        <v>2.76</v>
+        <v>3.35</v>
       </c>
       <c r="K21" t="n">
-        <v>3</v>
+        <v>3.55</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4606,14 +4606,14 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,37 +4623,37 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>CA Independiente</t>
         </is>
       </c>
       <c r="F22" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G22" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="H22" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="I22" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="J22" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="K22" t="n">
         <v>3</v>
       </c>
-      <c r="G22" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="H22" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="I22" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K22" t="n">
-        <v>3.7</v>
-      </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
@@ -4667,10 +4667,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.85</v>
+        <v>1.39</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.96</v>
+        <v>3.3</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -4800,14 +4800,14 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,36 +4817,36 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Cucuta Deportivo</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Junior FC Barranquilla</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="G23" t="n">
-        <v>4.7</v>
+        <v>3.8</v>
       </c>
       <c r="H23" t="n">
-        <v>2.14</v>
+        <v>2.34</v>
       </c>
       <c r="I23" t="n">
-        <v>2.34</v>
+        <v>2.68</v>
       </c>
       <c r="J23" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="K23" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4861,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.67</v>
+        <v>1.86</v>
       </c>
       <c r="Q23" t="n">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,14 +4994,14 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,36 +5011,36 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Central Cordoba (SdE)</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>1.53</v>
+        <v>3.75</v>
       </c>
       <c r="G24" t="n">
-        <v>1.59</v>
+        <v>4.7</v>
       </c>
       <c r="H24" t="n">
-        <v>7.2</v>
+        <v>2.14</v>
       </c>
       <c r="I24" t="n">
-        <v>1000</v>
+        <v>2.34</v>
       </c>
       <c r="J24" t="n">
-        <v>3.7</v>
+        <v>3.15</v>
       </c>
       <c r="K24" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5252,7 @@
         <v>1.54</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,201 +5382,395 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-22 05:21:00</t>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>19:15:00</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>Lanus</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Central Cordoba (SdE)</t>
+        </is>
+      </c>
+      <c r="F26" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H26" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="I26" t="n">
+        <v>1000</v>
+      </c>
+      <c r="J26" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K26" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" t="n">
+        <v>0</v>
+      </c>
+      <c r="P26" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
+      </c>
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="n">
+        <v>0</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG26" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH26" t="inlineStr">
+        <is>
+          <t>2026-04-22 07:36:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="B27" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="C26" t="inlineStr">
+      <c r="C27" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr">
+      <c r="D27" t="inlineStr">
         <is>
           <t>Ponte Preta</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="E27" t="inlineStr">
         <is>
           <t>America MG</t>
         </is>
       </c>
-      <c r="F26" t="n">
+      <c r="F27" t="n">
         <v>2.8</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G27" t="n">
         <v>3.05</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H27" t="n">
         <v>2.8</v>
       </c>
-      <c r="I26" t="n">
+      <c r="I27" t="n">
         <v>3</v>
       </c>
-      <c r="J26" t="n">
+      <c r="J27" t="n">
         <v>2.94</v>
       </c>
-      <c r="K26" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L26" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" t="n">
-        <v>0</v>
-      </c>
-      <c r="P26" t="n">
+      <c r="K27" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
         <v>1.68</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="Q27" t="n">
         <v>2.28</v>
       </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH26" t="inlineStr">
-        <is>
-          <t>2026-04-22 05:21:00</t>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-04-22 07:36:40</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH27"/>
+  <dimension ref="A1:BH28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -805,7 +805,7 @@
         <v>2.68</v>
       </c>
       <c r="V2" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="W2" t="n">
         <v>1.88</v>
@@ -820,7 +820,7 @@
         <v>1000</v>
       </c>
       <c r="AA2" t="n">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB2" t="n">
         <v>15.5</v>
@@ -832,10 +832,10 @@
         <v>16</v>
       </c>
       <c r="AE2" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AG2" t="n">
         <v>11.5</v>
@@ -844,19 +844,19 @@
         <v>15.5</v>
       </c>
       <c r="AI2" t="n">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK2" t="n">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AL2" t="n">
+        <v>28</v>
+      </c>
+      <c r="AM2" t="n">
         <v>1000</v>
-      </c>
-      <c r="AM2" t="n">
-        <v>65</v>
       </c>
       <c r="AN2" t="n">
         <v>9.199999999999999</v>
@@ -868,13 +868,13 @@
         <v>21</v>
       </c>
       <c r="AQ2" t="n">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AR2" t="n">
-        <v>8</v>
+        <v>24</v>
       </c>
       <c r="AS2" t="n">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AT2" t="n">
         <v>13.5</v>
@@ -886,7 +886,7 @@
         <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX2" t="n">
         <v>15</v>
@@ -898,7 +898,7 @@
         <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB2" t="n">
         <v>19.5</v>
@@ -910,7 +910,7 @@
         <v>18.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="BF2" t="n">
         <v>8</v>
@@ -920,14 +920,14 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Thai League 1</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,184 +937,184 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>11:00:00</t>
+          <t>09:00:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Pharco FC</t>
+          <t>Sukhothai</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Ratchaburi</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.9</v>
+        <v>3.55</v>
       </c>
       <c r="G3" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="H3" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="I3" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="J3" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K3" t="n">
+        <v>4</v>
+      </c>
+      <c r="L3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M3" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="O3" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="R3" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S3" t="n">
         <v>3.15</v>
       </c>
-      <c r="H3" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="I3" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="J3" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="K3" t="n">
-        <v>3</v>
-      </c>
-      <c r="L3" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" t="n">
-        <v>0</v>
-      </c>
-      <c r="N3" t="n">
-        <v>0</v>
-      </c>
-      <c r="O3" t="n">
-        <v>0</v>
-      </c>
-      <c r="P3" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="Q3" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BG3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
@@ -1136,50 +1136,50 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>National Bank</t>
+          <t>Pharco FC</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ZED FC</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.18</v>
+        <v>2.94</v>
       </c>
       <c r="G4" t="n">
-        <v>2.54</v>
+        <v>3.15</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7</v>
+        <v>2.96</v>
       </c>
       <c r="I4" t="n">
-        <v>4.8</v>
+        <v>3.2</v>
       </c>
       <c r="J4" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="K4" t="n">
+        <v>3</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="Q4" t="n">
         <v>2.98</v>
       </c>
-      <c r="K4" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>2.42</v>
-      </c>
       <c r="R4" t="n">
         <v>0</v>
       </c>
@@ -1308,14 +1308,14 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1325,36 +1325,36 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:00:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>National Bank</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>ZED FC</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>3.95</v>
+        <v>2.18</v>
       </c>
       <c r="G5" t="n">
-        <v>4.3</v>
+        <v>2.5</v>
       </c>
       <c r="H5" t="n">
-        <v>1.93</v>
+        <v>3.7</v>
       </c>
       <c r="I5" t="n">
-        <v>2.04</v>
+        <v>4.7</v>
       </c>
       <c r="J5" t="n">
-        <v>3.75</v>
+        <v>3.05</v>
       </c>
       <c r="K5" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="L5" t="n">
         <v>0</v>
@@ -1369,10 +1369,10 @@
         <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.16</v>
+        <v>1.59</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.76</v>
+        <v>2.42</v>
       </c>
       <c r="R5" t="n">
         <v>0</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
@@ -1524,31 +1524,31 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2.48</v>
+        <v>3.95</v>
       </c>
       <c r="G6" t="n">
-        <v>2.52</v>
+        <v>4.4</v>
       </c>
       <c r="H6" t="n">
-        <v>2.82</v>
+        <v>1.92</v>
       </c>
       <c r="I6" t="n">
-        <v>2.96</v>
+        <v>2.04</v>
       </c>
       <c r="J6" t="n">
         <v>3.75</v>
       </c>
       <c r="K6" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L6" t="n">
         <v>0</v>
@@ -1563,7 +1563,7 @@
         <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q6" t="n">
         <v>1.76</v>
@@ -1696,14 +1696,14 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,36 +1713,36 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>12:45:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Al-Fateh (KSA)</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al-Khaleej Saihat</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G7" t="n">
-        <v>2.86</v>
+        <v>2.52</v>
       </c>
       <c r="H7" t="n">
-        <v>2.7</v>
+        <v>2.84</v>
       </c>
       <c r="I7" t="n">
-        <v>3.25</v>
+        <v>2.98</v>
       </c>
       <c r="J7" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="K7" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L7" t="n">
         <v>0</v>
@@ -1757,10 +1757,10 @@
         <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.61</v>
+        <v>1.76</v>
       </c>
       <c r="R7" t="n">
         <v>0</v>
@@ -1890,14 +1890,14 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,37 +1907,37 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:45:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Al-Fateh (KSA)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Al-Khaleej Saihat</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>1.72</v>
+        <v>2.4</v>
       </c>
       <c r="G8" t="n">
-        <v>1.81</v>
+        <v>2.64</v>
       </c>
       <c r="H8" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="I8" t="n">
-        <v>5</v>
+        <v>3.2</v>
       </c>
       <c r="J8" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K8" t="n">
         <v>4.3</v>
       </c>
-      <c r="K8" t="n">
-        <v>4.6</v>
-      </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
@@ -1951,10 +1951,10 @@
         <v>0</v>
       </c>
       <c r="P8" t="n">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -2084,14 +2084,14 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2106,31 +2106,31 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Znicz Pruszkow</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Gornik Leczna</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>2.1</v>
+        <v>1.75</v>
       </c>
       <c r="G9" t="n">
-        <v>2.36</v>
+        <v>1.83</v>
       </c>
       <c r="H9" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="I9" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="J9" t="n">
         <v>4.3</v>
       </c>
-      <c r="J9" t="n">
-        <v>3.45</v>
-      </c>
       <c r="K9" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="L9" t="n">
         <v>0</v>
@@ -2145,10 +2145,10 @@
         <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>1.94</v>
+        <v>2.46</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.9</v>
+        <v>1.58</v>
       </c>
       <c r="R9" t="n">
         <v>0</v>
@@ -2278,14 +2278,14 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2295,36 +2295,36 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>13:10:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Al-Hazm (KSA)</t>
+          <t>Znicz Pruszkow</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>Gornik Leczna</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.64</v>
+        <v>2.1</v>
       </c>
       <c r="G10" t="n">
-        <v>3.05</v>
+        <v>2.36</v>
       </c>
       <c r="H10" t="n">
-        <v>2.54</v>
+        <v>3.45</v>
       </c>
       <c r="I10" t="n">
-        <v>2.96</v>
+        <v>4.3</v>
       </c>
       <c r="J10" t="n">
         <v>3.35</v>
       </c>
       <c r="K10" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,37 +2489,37 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:10:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Al-Hazm (KSA)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Esbjerg</t>
+          <t>Al Riyadh SC</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>1.71</v>
+        <v>2.64</v>
       </c>
       <c r="G11" t="n">
-        <v>1.92</v>
+        <v>3.05</v>
       </c>
       <c r="H11" t="n">
-        <v>4.5</v>
+        <v>2.54</v>
       </c>
       <c r="I11" t="n">
-        <v>5.9</v>
+        <v>2.92</v>
       </c>
       <c r="J11" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="K11" t="n">
         <v>3.85</v>
       </c>
-      <c r="K11" t="n">
-        <v>4.5</v>
-      </c>
       <c r="L11" t="n">
         <v>0</v>
       </c>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.14</v>
+        <v>1.94</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.69</v>
+        <v>1.88</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2688,31 +2688,31 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Modern Sport FC</t>
+          <t>Esbjerg</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>3.6</v>
+        <v>1.73</v>
       </c>
       <c r="G12" t="n">
-        <v>4.3</v>
+        <v>1.9</v>
       </c>
       <c r="H12" t="n">
-        <v>2.4</v>
+        <v>4.5</v>
       </c>
       <c r="I12" t="n">
-        <v>2.92</v>
+        <v>6</v>
       </c>
       <c r="J12" t="n">
-        <v>2.62</v>
+        <v>3.8</v>
       </c>
       <c r="K12" t="n">
-        <v>2.96</v>
+        <v>4.4</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.34</v>
+        <v>2.06</v>
       </c>
       <c r="Q12" t="n">
-        <v>3.3</v>
+        <v>1.74</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
@@ -2882,31 +2882,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Modern Sport FC</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.98</v>
+        <v>3.6</v>
       </c>
       <c r="G13" t="n">
-        <v>2.12</v>
+        <v>4.6</v>
       </c>
       <c r="H13" t="n">
-        <v>4.7</v>
+        <v>2.44</v>
       </c>
       <c r="I13" t="n">
-        <v>6</v>
+        <v>2.74</v>
       </c>
       <c r="J13" t="n">
-        <v>3.05</v>
+        <v>2.62</v>
       </c>
       <c r="K13" t="n">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.51</v>
+        <v>1.34</v>
       </c>
       <c r="Q13" t="n">
-        <v>2.72</v>
+        <v>3.3</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,14 +3054,14 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3071,36 +3071,36 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Etoile Carouge</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>3.3</v>
+        <v>1.98</v>
       </c>
       <c r="G14" t="n">
-        <v>4</v>
+        <v>2.18</v>
       </c>
       <c r="H14" t="n">
-        <v>2.06</v>
+        <v>4.7</v>
       </c>
       <c r="I14" t="n">
-        <v>2.24</v>
+        <v>6</v>
       </c>
       <c r="J14" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="K14" t="n">
-        <v>4.3</v>
+        <v>3.35</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>2.32</v>
+        <v>1.51</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.64</v>
+        <v>2.72</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3270,31 +3270,31 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>FC Blau Weiss Linz</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Etoile Carouge</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>2.14</v>
+        <v>3.3</v>
       </c>
       <c r="G15" t="n">
-        <v>2.26</v>
+        <v>4</v>
       </c>
       <c r="H15" t="n">
-        <v>3.85</v>
+        <v>2.06</v>
       </c>
       <c r="I15" t="n">
-        <v>4.4</v>
+        <v>2.24</v>
       </c>
       <c r="J15" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="K15" t="n">
-        <v>3.65</v>
+        <v>4.2</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3459,36 +3459,36 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>15:15:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>FC Blau Weiss Linz</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>FC Vaduz</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="F16" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G16" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="H16" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="I16" t="n">
         <v>4.4</v>
       </c>
-      <c r="G16" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="I16" t="n">
-        <v>1.85</v>
-      </c>
       <c r="J16" t="n">
-        <v>4</v>
+        <v>3.25</v>
       </c>
       <c r="K16" t="n">
-        <v>4.8</v>
+        <v>3.65</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>2.38</v>
+        <v>1.72</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.58</v>
+        <v>2.14</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,33 +3653,33 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Wisla Krakow</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Puszcza Niepolomice</t>
+          <t>FC Vaduz</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.53</v>
+        <v>4.4</v>
       </c>
       <c r="G17" t="n">
-        <v>1.67</v>
+        <v>5.2</v>
       </c>
       <c r="H17" t="n">
-        <v>6.4</v>
+        <v>1.7</v>
       </c>
       <c r="I17" t="n">
-        <v>9</v>
+        <v>1.82</v>
       </c>
       <c r="J17" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K17" t="n">
         <v>4.8</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.02</v>
+        <v>2.38</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.81</v>
+        <v>1.58</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>French Ligue 1</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,66 +3847,66 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Wisla Krakow</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Puszcza Niepolomice</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>5</v>
+        <v>1.53</v>
       </c>
       <c r="G18" t="n">
-        <v>5.4</v>
+        <v>1.65</v>
       </c>
       <c r="H18" t="n">
-        <v>1.73</v>
+        <v>6.4</v>
       </c>
       <c r="I18" t="n">
-        <v>1.74</v>
+        <v>9</v>
       </c>
       <c r="J18" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N18" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O18" t="n">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.28</v>
+        <v>2.02</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="R18" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S18" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T18" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -3915,123 +3915,123 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Y18" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Z18" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AA18" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AC18" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AD18" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AE18" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AF18" t="n">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AG18" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AH18" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AI18" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AJ18" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AK18" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AL18" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AM18" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AN18" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AO18" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AP18" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AQ18" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AR18" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AS18" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AT18" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AU18" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AV18" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AW18" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AX18" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AY18" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AZ18" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BA18" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="BC18" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BD18" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="BE18" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BF18" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BG18" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>French Ligue 1</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,66 +4041,66 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.82</v>
+        <v>5</v>
       </c>
       <c r="G19" t="n">
-        <v>2.86</v>
+        <v>5.3</v>
       </c>
       <c r="H19" t="n">
-        <v>2.86</v>
+        <v>1.73</v>
       </c>
       <c r="I19" t="n">
-        <v>2.88</v>
+        <v>1.74</v>
       </c>
       <c r="J19" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="K19" t="n">
-        <v>3.35</v>
+        <v>4.4</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.09</v>
+        <v>1.05</v>
       </c>
       <c r="N19" t="n">
-        <v>3.35</v>
+        <v>4.7</v>
       </c>
       <c r="O19" t="n">
-        <v>1.41</v>
+        <v>1.25</v>
       </c>
       <c r="P19" t="n">
-        <v>1.77</v>
+        <v>2.26</v>
       </c>
       <c r="Q19" t="n">
-        <v>2.24</v>
+        <v>1.73</v>
       </c>
       <c r="R19" t="n">
-        <v>1.29</v>
+        <v>1.51</v>
       </c>
       <c r="S19" t="n">
-        <v>4.2</v>
+        <v>2.84</v>
       </c>
       <c r="T19" t="n">
-        <v>1.9</v>
+        <v>1.75</v>
       </c>
       <c r="U19" t="n">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4109,123 +4109,123 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>11.5</v>
+        <v>23</v>
       </c>
       <c r="Y19" t="n">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Z19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF19" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG19" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH19" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI19" t="n">
+        <v>32</v>
+      </c>
+      <c r="AJ19" t="n">
+        <v>140</v>
+      </c>
+      <c r="AK19" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL19" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM19" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>60</v>
+      </c>
+      <c r="AO19" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AP19" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AQ19" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AR19" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS19" t="n">
+        <v>16</v>
+      </c>
+      <c r="AT19" t="n">
         <v>18.5</v>
       </c>
-      <c r="AA19" t="n">
-        <v>50</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>10</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE19" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF19" t="n">
+      <c r="AU19" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV19" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AW19" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>12</v>
+      </c>
+      <c r="AY19" t="n">
         <v>18</v>
       </c>
-      <c r="AG19" t="n">
-        <v>13</v>
-      </c>
-      <c r="AH19" t="n">
-        <v>19</v>
-      </c>
-      <c r="AI19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ19" t="n">
-        <v>48</v>
-      </c>
-      <c r="AK19" t="n">
-        <v>40</v>
-      </c>
-      <c r="AL19" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM19" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN19" t="n">
+      <c r="AZ19" t="n">
+        <v>16</v>
+      </c>
+      <c r="BA19" t="n">
+        <v>22</v>
+      </c>
+      <c r="BB19" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="BC19" t="n">
         <v>38</v>
       </c>
-      <c r="AO19" t="n">
-        <v>38</v>
-      </c>
-      <c r="AP19" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AQ19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AR19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AS19" t="n">
-        <v>40</v>
-      </c>
-      <c r="AT19" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AU19" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AV19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW19" t="n">
-        <v>30</v>
-      </c>
-      <c r="AX19" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY19" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AZ19" t="n">
-        <v>18</v>
-      </c>
-      <c r="BA19" t="n">
-        <v>44</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>38</v>
-      </c>
-      <c r="BC19" t="n">
-        <v>30</v>
-      </c>
       <c r="BD19" t="n">
-        <v>44</v>
+        <v>12.5</v>
       </c>
       <c r="BE19" t="n">
-        <v>65</v>
+        <v>14</v>
       </c>
       <c r="BF19" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="BG19" t="n">
-        <v>30</v>
+        <v>8</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4240,61 +4240,61 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>3.75</v>
+        <v>2.82</v>
       </c>
       <c r="G20" t="n">
-        <v>4</v>
+        <v>2.86</v>
       </c>
       <c r="H20" t="n">
-        <v>1.92</v>
+        <v>2.84</v>
       </c>
       <c r="I20" t="n">
-        <v>1.98</v>
+        <v>2.88</v>
       </c>
       <c r="J20" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L20" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N20" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="S20" t="n">
         <v>4.2</v>
       </c>
-      <c r="K20" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L20" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N20" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" t="n">
-        <v>0</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="n">
-        <v>0</v>
-      </c>
       <c r="T20" t="n">
-        <v>1.55</v>
+        <v>1.9</v>
       </c>
       <c r="U20" t="n">
-        <v>2.62</v>
+        <v>2.04</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4303,123 +4303,123 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>44</v>
+        <v>11.5</v>
       </c>
       <c r="Y20" t="n">
-        <v>14</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z20" t="n">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AA20" t="n">
-        <v>24</v>
+        <v>46</v>
       </c>
       <c r="AB20" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="AC20" t="n">
+        <v>7</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>18</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>19</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>46</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>50</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>36</v>
+      </c>
+      <c r="AP20" t="n">
         <v>10.5</v>
       </c>
-      <c r="AD20" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH20" t="n">
+      <c r="AQ20" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AR20" t="n">
         <v>16</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AS20" t="n">
+        <v>40</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>30</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>16</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>18</v>
+      </c>
+      <c r="BA20" t="n">
         <v>42</v>
       </c>
-      <c r="AJ20" t="n">
-        <v>75</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>50</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>23</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>20</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AX20" t="n">
+      <c r="BB20" t="n">
+        <v>38</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>30</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>42</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>65</v>
+      </c>
+      <c r="BF20" t="n">
         <v>21</v>
       </c>
-      <c r="AY20" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>18</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>34</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>32</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>32</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>46</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>19.5</v>
-      </c>
       <c r="BG20" t="n">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,42 +4429,42 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Arouca</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.32</v>
+        <v>3.75</v>
       </c>
       <c r="G21" t="n">
-        <v>2.5</v>
+        <v>4.1</v>
       </c>
       <c r="H21" t="n">
-        <v>3.25</v>
+        <v>1.91</v>
       </c>
       <c r="I21" t="n">
-        <v>3.6</v>
+        <v>1.98</v>
       </c>
       <c r="J21" t="n">
-        <v>3.35</v>
+        <v>4.2</v>
       </c>
       <c r="K21" t="n">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="L21" t="n">
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N21" t="n">
         <v>0</v>
@@ -4473,10 +4473,10 @@
         <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="R21" t="n">
         <v>0</v>
@@ -4485,10 +4485,10 @@
         <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4497,123 +4497,123 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AQ21" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR21" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AT21" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AU21" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AV21" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW21" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AY21" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA21" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BB21" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BC21" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BD21" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="BE21" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BF21" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BG21" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,36 +4623,36 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>Arouca</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>3.9</v>
+        <v>2.32</v>
       </c>
       <c r="G22" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
       </c>
       <c r="H22" t="n">
-        <v>2.3</v>
+        <v>3.25</v>
       </c>
       <c r="I22" t="n">
-        <v>2.54</v>
+        <v>3.6</v>
       </c>
       <c r="J22" t="n">
-        <v>2.76</v>
+        <v>3.35</v>
       </c>
       <c r="K22" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4667,10 +4667,10 @@
         <v>0</v>
       </c>
       <c r="P22" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
         <v>0</v>
@@ -4800,14 +4800,14 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,36 +4817,36 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>CA Independiente</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="G23" t="n">
-        <v>3.8</v>
+        <v>4.5</v>
       </c>
       <c r="H23" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="I23" t="n">
-        <v>2.68</v>
+        <v>2.54</v>
       </c>
       <c r="J23" t="n">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="K23" t="n">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
@@ -4861,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.86</v>
+        <v>1.39</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.97</v>
+        <v>3.3</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4994,14 +4994,14 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,36 +5011,36 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Cucuta Deportivo</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Junior FC Barranquilla</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="G24" t="n">
-        <v>4.7</v>
+        <v>3.45</v>
       </c>
       <c r="H24" t="n">
-        <v>2.14</v>
+        <v>2.38</v>
       </c>
       <c r="I24" t="n">
-        <v>2.34</v>
+        <v>2.68</v>
       </c>
       <c r="J24" t="n">
-        <v>3.15</v>
+        <v>2.96</v>
       </c>
       <c r="K24" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.67</v>
+        <v>1.85</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.28</v>
+        <v>1.97</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,14 +5188,14 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,33 +5205,33 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Estudiantes Rio Cuarto</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>4.9</v>
+        <v>3.75</v>
       </c>
       <c r="G25" t="n">
-        <v>5.6</v>
+        <v>4.8</v>
       </c>
       <c r="H25" t="n">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="I25" t="n">
-        <v>2</v>
+        <v>2.6</v>
       </c>
       <c r="J25" t="n">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="K25" t="n">
         <v>3.5</v>
@@ -5249,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.54</v>
+        <v>1.67</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.62</v>
+        <v>2.26</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
@@ -5404,31 +5404,31 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Estudiantes Rio Cuarto</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Central Cordoba (SdE)</t>
+          <t>Rosario Central</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.53</v>
+        <v>5.1</v>
       </c>
       <c r="G26" t="n">
-        <v>1.59</v>
+        <v>5.4</v>
       </c>
       <c r="H26" t="n">
-        <v>7.2</v>
+        <v>1.95</v>
       </c>
       <c r="I26" t="n">
-        <v>1000</v>
+        <v>1.98</v>
       </c>
       <c r="J26" t="n">
-        <v>3.7</v>
+        <v>3.35</v>
       </c>
       <c r="K26" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5443,10 +5443,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.62</v>
+        <v>1.52</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.4</v>
+        <v>2.68</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -5576,201 +5576,395 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-22 07:36:40</t>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>19:15:00</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Lanus</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>Central Cordoba (SdE)</t>
+        </is>
+      </c>
+      <c r="F27" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H27" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="I27" t="n">
+        <v>11</v>
+      </c>
+      <c r="J27" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K27" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L27" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" t="n">
+        <v>0</v>
+      </c>
+      <c r="P27" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R27" t="n">
+        <v>0</v>
+      </c>
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="n">
+        <v>0</v>
+      </c>
+      <c r="W27" t="n">
+        <v>0</v>
+      </c>
+      <c r="X27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y27" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY27" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG27" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH27" t="inlineStr">
+        <is>
+          <t>2026-04-22 10:44:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
+      <c r="B28" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="C27" t="inlineStr">
+      <c r="C28" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr">
+      <c r="D28" t="inlineStr">
         <is>
           <t>Ponte Preta</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="E28" t="inlineStr">
         <is>
           <t>America MG</t>
         </is>
       </c>
-      <c r="F27" t="n">
+      <c r="F28" t="n">
         <v>2.8</v>
       </c>
-      <c r="G27" t="n">
+      <c r="G28" t="n">
         <v>3.05</v>
       </c>
-      <c r="H27" t="n">
+      <c r="H28" t="n">
         <v>2.8</v>
       </c>
-      <c r="I27" t="n">
+      <c r="I28" t="n">
         <v>3</v>
       </c>
-      <c r="J27" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="K27" t="n">
+      <c r="J28" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K28" t="n">
         <v>3.35</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" t="n">
-        <v>0</v>
-      </c>
-      <c r="P27" t="n">
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
         <v>1.68</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="Q28" t="n">
         <v>2.28</v>
       </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="n">
-        <v>0</v>
-      </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="n">
-        <v>0</v>
-      </c>
-      <c r="W27" t="n">
-        <v>0</v>
-      </c>
-      <c r="X27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y27" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG27" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH27" t="inlineStr">
-        <is>
-          <t>2026-04-22 07:36:40</t>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-04-22 10:44:38</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH28"/>
+  <dimension ref="A1:BH30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -760,7 +760,7 @@
         <v>2.02</v>
       </c>
       <c r="G2" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H2" t="n">
         <v>3.35</v>
@@ -769,13 +769,13 @@
         <v>3.65</v>
       </c>
       <c r="J2" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="K2" t="n">
         <v>4.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
@@ -808,10 +808,10 @@
         <v>1.38</v>
       </c>
       <c r="W2" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="X2" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y2" t="n">
         <v>22</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-22 10:44:38</t>
+          <t>2026-04-22 12:59:55</t>
         </is>
       </c>
     </row>
@@ -963,13 +963,13 @@
         <v>2.22</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>3.45</v>
       </c>
       <c r="K3" t="n">
         <v>4</v>
       </c>
       <c r="L3" t="n">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
@@ -1092,29 +1092,29 @@
         <v>13</v>
       </c>
       <c r="BA3" t="n">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="BB3" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BC3" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BD3" t="n">
-        <v>1.03</v>
+        <v>4.6</v>
       </c>
       <c r="BE3" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>32</v>
+        <v>4.6</v>
       </c>
       <c r="BG3" t="n">
         <v>11</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-22 10:44:38</t>
+          <t>2026-04-22 12:59:55</t>
         </is>
       </c>
     </row>
@@ -1145,170 +1145,170 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.94</v>
+        <v>2.22</v>
       </c>
       <c r="G4" t="n">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="H4" t="n">
-        <v>2.96</v>
+        <v>2.8</v>
       </c>
       <c r="I4" t="n">
-        <v>3.2</v>
+        <v>3.65</v>
       </c>
       <c r="J4" t="n">
-        <v>2.82</v>
+        <v>2.68</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>5.3</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="P4" t="n">
         <v>1.45</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.98</v>
+        <v>2.76</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>270</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AR4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AS4" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AT4" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AU4" t="n">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW4" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AX4" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AY4" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BG4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-22 10:44:38</t>
+          <t>2026-04-22 12:59:55</t>
         </is>
       </c>
     </row>
@@ -1357,16 +1357,16 @@
         <v>3.4</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P5" t="n">
         <v>1.59</v>
@@ -1375,141 +1375,141 @@
         <v>2.42</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AQ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AR5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AS5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AT5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AU5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AV5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AW5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AX5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AY5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BA5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BB5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BC5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BD5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BE5" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BF5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-22 10:44:38</t>
+          <t>2026-04-22 12:59:55</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,184 +1519,184 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>12:00:00</t>
+          <t>11:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VPS</t>
+          <t>Hermannstadt</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ilves</t>
+          <t>Csikszereda</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3.95</v>
+        <v>1.71</v>
       </c>
       <c r="G6" t="n">
-        <v>4.4</v>
+        <v>1.86</v>
       </c>
       <c r="H6" t="n">
-        <v>1.92</v>
+        <v>5.1</v>
       </c>
       <c r="I6" t="n">
-        <v>2.04</v>
+        <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="K6" t="n">
         <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P6" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="S6" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1.82</v>
+      </c>
+      <c r="V6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="W6" t="n">
         <v>2.16</v>
       </c>
-      <c r="Q6" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
-      <c r="T6" t="n">
-        <v>0</v>
-      </c>
-      <c r="U6" t="n">
-        <v>0</v>
-      </c>
-      <c r="V6" t="n">
-        <v>0</v>
-      </c>
-      <c r="W6" t="n">
-        <v>0</v>
-      </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>120</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AR6" t="n">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AU6" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV6" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AW6" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AX6" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AY6" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BA6" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BB6" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BC6" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BD6" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="BE6" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF6" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="BG6" t="n">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-22 10:44:38</t>
+          <t>2026-04-22 12:59:55</t>
         </is>
       </c>
     </row>
@@ -1718,43 +1718,43 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>TPS</t>
+          <t>VPS</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Gnistan</t>
+          <t>Ilves</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2.42</v>
+        <v>3.95</v>
       </c>
       <c r="G7" t="n">
-        <v>2.52</v>
+        <v>4.4</v>
       </c>
       <c r="H7" t="n">
-        <v>2.84</v>
+        <v>1.92</v>
       </c>
       <c r="I7" t="n">
-        <v>2.98</v>
+        <v>2.04</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K7" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P7" t="n">
         <v>2.16</v>
@@ -1763,141 +1763,141 @@
         <v>1.76</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AR7" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS7" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AT7" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AU7" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AV7" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AW7" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AX7" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AY7" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="BG7" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-22 10:44:38</t>
+          <t>2026-04-22 12:59:55</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,191 +1907,191 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>12:45:00</t>
+          <t>12:00:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Al-Fateh (KSA)</t>
+          <t>TPS</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Al-Khaleej Saihat</t>
+          <t>Gnistan</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G8" t="n">
-        <v>2.64</v>
+        <v>2.52</v>
       </c>
       <c r="H8" t="n">
-        <v>2.7</v>
+        <v>2.82</v>
       </c>
       <c r="I8" t="n">
-        <v>3.2</v>
+        <v>2.98</v>
       </c>
       <c r="J8" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K8" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="P8" t="n">
-        <v>2.38</v>
+        <v>2.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.6</v>
+        <v>1.76</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AR8" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="AS8" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="AT8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AU8" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AV8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AW8" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="AX8" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AY8" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BA8" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BB8" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BC8" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BD8" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BE8" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BF8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BG8" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-22 10:44:38</t>
+          <t>2026-04-22 12:59:55</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Finnish Veikkausliiga</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2101,191 +2101,191 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>13:00:00</t>
+          <t>12:45:00</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>SJK</t>
+          <t>Al-Fateh (KSA)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Jaro</t>
+          <t>Al-Khaleej Saihat</t>
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.75</v>
+        <v>2.4</v>
       </c>
       <c r="G9" t="n">
-        <v>1.83</v>
+        <v>2.64</v>
       </c>
       <c r="H9" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="I9" t="n">
-        <v>4.9</v>
+        <v>3.15</v>
       </c>
       <c r="J9" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="K9" t="n">
         <v>4.3</v>
       </c>
-      <c r="K9" t="n">
-        <v>4.6</v>
-      </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="P9" t="n">
-        <v>2.46</v>
+        <v>2.38</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-22 10:44:38</t>
+          <t>2026-04-22 12:59:55</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Finnish Veikkausliiga</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2300,31 +2300,31 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Znicz Pruszkow</t>
+          <t>SJK</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Gornik Leczna</t>
+          <t>Jaro</t>
         </is>
       </c>
       <c r="F10" t="n">
-        <v>2.1</v>
+        <v>1.78</v>
       </c>
       <c r="G10" t="n">
-        <v>2.36</v>
+        <v>1.84</v>
       </c>
       <c r="H10" t="n">
-        <v>3.45</v>
+        <v>4.5</v>
       </c>
       <c r="I10" t="n">
-        <v>4.3</v>
+        <v>4.9</v>
       </c>
       <c r="J10" t="n">
-        <v>3.35</v>
+        <v>4.1</v>
       </c>
       <c r="K10" t="n">
-        <v>3.9</v>
+        <v>4.6</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -2339,10 +2339,10 @@
         <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1.93</v>
+        <v>2.5</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.9</v>
+        <v>1.59</v>
       </c>
       <c r="R10" t="n">
         <v>0</v>
@@ -2472,14 +2472,14 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-22 10:44:38</t>
+          <t>2026-04-22 12:59:55</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Saudi Professional League</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2489,36 +2489,36 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>13:10:00</t>
+          <t>13:00:00</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Al-Hazm (KSA)</t>
+          <t>Znicz Pruszkow</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Al Riyadh SC</t>
+          <t>Gornik Leczna</t>
         </is>
       </c>
       <c r="F11" t="n">
-        <v>2.64</v>
+        <v>2.1</v>
       </c>
       <c r="G11" t="n">
-        <v>3.05</v>
+        <v>2.36</v>
       </c>
       <c r="H11" t="n">
-        <v>2.54</v>
+        <v>3.45</v>
       </c>
       <c r="I11" t="n">
-        <v>2.92</v>
+        <v>4</v>
       </c>
       <c r="J11" t="n">
         <v>3.35</v>
       </c>
       <c r="K11" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L11" t="n">
         <v>0</v>
@@ -2533,10 +2533,10 @@
         <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.88</v>
+        <v>1.9</v>
       </c>
       <c r="R11" t="n">
         <v>0</v>
@@ -2666,14 +2666,14 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-22 10:44:38</t>
+          <t>2026-04-22 12:59:55</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Danish 1st Division</t>
+          <t>Saudi Professional League</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2683,36 +2683,36 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>14:00:00</t>
+          <t>13:10:00</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Lyngby</t>
+          <t>Al-Hazm (KSA)</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Esbjerg</t>
+          <t>Al Riyadh SC</t>
         </is>
       </c>
       <c r="F12" t="n">
-        <v>1.73</v>
+        <v>2.64</v>
       </c>
       <c r="G12" t="n">
-        <v>1.9</v>
+        <v>3.05</v>
       </c>
       <c r="H12" t="n">
-        <v>4.5</v>
+        <v>2.54</v>
       </c>
       <c r="I12" t="n">
-        <v>6</v>
+        <v>2.92</v>
       </c>
       <c r="J12" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="K12" t="n">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="L12" t="n">
         <v>0</v>
@@ -2727,10 +2727,10 @@
         <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>2.06</v>
+        <v>1.94</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="R12" t="n">
         <v>0</v>
@@ -2860,14 +2860,14 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-22 10:44:38</t>
+          <t>2026-04-22 12:59:55</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Egyptian Premier</t>
+          <t>Danish 1st Division</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2882,31 +2882,31 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Ismaily</t>
+          <t>Lyngby</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Modern Sport FC</t>
+          <t>Esbjerg</t>
         </is>
       </c>
       <c r="F13" t="n">
-        <v>3.6</v>
+        <v>1.74</v>
       </c>
       <c r="G13" t="n">
-        <v>4.6</v>
+        <v>1.9</v>
       </c>
       <c r="H13" t="n">
-        <v>2.44</v>
+        <v>4.5</v>
       </c>
       <c r="I13" t="n">
-        <v>2.74</v>
+        <v>5.9</v>
       </c>
       <c r="J13" t="n">
-        <v>2.62</v>
+        <v>3.85</v>
       </c>
       <c r="K13" t="n">
-        <v>2.96</v>
+        <v>4.5</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -2921,10 +2921,10 @@
         <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.34</v>
+        <v>2.06</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.3</v>
+        <v>1.75</v>
       </c>
       <c r="R13" t="n">
         <v>0</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-22 10:44:38</t>
+          <t>2026-04-22 12:59:55</t>
         </is>
       </c>
     </row>
@@ -3076,31 +3076,31 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>El Geish</t>
+          <t>Ismaily</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Kahraba Ismailia</t>
+          <t>Modern Sport FC</t>
         </is>
       </c>
       <c r="F14" t="n">
-        <v>1.98</v>
+        <v>3.15</v>
       </c>
       <c r="G14" t="n">
-        <v>2.18</v>
+        <v>4.8</v>
       </c>
       <c r="H14" t="n">
-        <v>4.7</v>
+        <v>2.46</v>
       </c>
       <c r="I14" t="n">
-        <v>6</v>
+        <v>3.1</v>
       </c>
       <c r="J14" t="n">
-        <v>3.05</v>
+        <v>2.58</v>
       </c>
       <c r="K14" t="n">
-        <v>3.35</v>
+        <v>2.98</v>
       </c>
       <c r="L14" t="n">
         <v>0</v>
@@ -3115,10 +3115,10 @@
         <v>0</v>
       </c>
       <c r="P14" t="n">
-        <v>1.51</v>
+        <v>1.26</v>
       </c>
       <c r="Q14" t="n">
-        <v>2.72</v>
+        <v>3</v>
       </c>
       <c r="R14" t="n">
         <v>0</v>
@@ -3248,14 +3248,14 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-22 10:44:38</t>
+          <t>2026-04-22 12:59:55</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>Egyptian Premier</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3265,36 +3265,36 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>14:30:00</t>
+          <t>14:00:00</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>El Geish</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Etoile Carouge</t>
+          <t>Kahraba Ismailia</t>
         </is>
       </c>
       <c r="F15" t="n">
-        <v>3.3</v>
+        <v>1.98</v>
       </c>
       <c r="G15" t="n">
-        <v>4</v>
+        <v>2.12</v>
       </c>
       <c r="H15" t="n">
-        <v>2.06</v>
+        <v>4.7</v>
       </c>
       <c r="I15" t="n">
-        <v>2.24</v>
+        <v>6</v>
       </c>
       <c r="J15" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="K15" t="n">
-        <v>4.2</v>
+        <v>3.35</v>
       </c>
       <c r="L15" t="n">
         <v>0</v>
@@ -3309,10 +3309,10 @@
         <v>0</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="R15" t="n">
         <v>0</v>
@@ -3442,14 +3442,14 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-22 10:44:38</t>
+          <t>2026-04-22 12:59:55</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Austrian Bundesliga</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -3464,31 +3464,31 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>FC Blau Weiss Linz</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>SCR Altach</t>
+          <t>Etoile Carouge</t>
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.1</v>
+        <v>3.3</v>
       </c>
       <c r="G16" t="n">
-        <v>2.26</v>
+        <v>4</v>
       </c>
       <c r="H16" t="n">
-        <v>3.85</v>
+        <v>2.06</v>
       </c>
       <c r="I16" t="n">
-        <v>4.4</v>
+        <v>2.24</v>
       </c>
       <c r="J16" t="n">
-        <v>3.25</v>
+        <v>3.8</v>
       </c>
       <c r="K16" t="n">
-        <v>3.65</v>
+        <v>4.3</v>
       </c>
       <c r="L16" t="n">
         <v>0</v>
@@ -3503,10 +3503,10 @@
         <v>0</v>
       </c>
       <c r="P16" t="n">
-        <v>1.72</v>
+        <v>2.32</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.14</v>
+        <v>1.65</v>
       </c>
       <c r="R16" t="n">
         <v>0</v>
@@ -3636,14 +3636,14 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-22 10:44:38</t>
+          <t>2026-04-22 12:59:55</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Swiss Challenge League</t>
+          <t>Austrian Bundesliga</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3653,36 +3653,36 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>15:15:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>FC Blau Weiss Linz</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>FC Vaduz</t>
+          <t>SCR Altach</t>
         </is>
       </c>
       <c r="F17" t="n">
-        <v>4.4</v>
+        <v>2.1</v>
       </c>
       <c r="G17" t="n">
-        <v>5.2</v>
+        <v>2.26</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7</v>
+        <v>3.85</v>
       </c>
       <c r="I17" t="n">
-        <v>1.82</v>
+        <v>4.3</v>
       </c>
       <c r="J17" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="K17" t="n">
-        <v>4.8</v>
+        <v>3.6</v>
       </c>
       <c r="L17" t="n">
         <v>0</v>
@@ -3697,10 +3697,10 @@
         <v>0</v>
       </c>
       <c r="P17" t="n">
-        <v>2.38</v>
+        <v>1.73</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.58</v>
+        <v>2.18</v>
       </c>
       <c r="R17" t="n">
         <v>0</v>
@@ -3830,14 +3830,14 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-22 10:44:38</t>
+          <t>2026-04-22 12:59:55</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Romanian Liga I</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3847,36 +3847,36 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>15:30:00</t>
+          <t>14:30:00</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Wisla Krakow</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Puszcza Niepolomice</t>
+          <t>ACS Petrolul 52</t>
         </is>
       </c>
       <c r="F18" t="n">
-        <v>1.53</v>
+        <v>1.49</v>
       </c>
       <c r="G18" t="n">
-        <v>1.65</v>
+        <v>1.6</v>
       </c>
       <c r="H18" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="I18" t="n">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="J18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K18" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
@@ -3891,10 +3891,10 @@
         <v>0</v>
       </c>
       <c r="P18" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="Q18" t="n">
-        <v>1.72</v>
+        <v>1.86</v>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -4024,14 +4024,14 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-22 10:44:38</t>
+          <t>2026-04-22 12:59:55</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>French Ligue 1</t>
+          <t>Swiss Challenge League</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -4041,66 +4041,66 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>15:45:00</t>
+          <t>15:15:00</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Brest</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>FC Vaduz</t>
         </is>
       </c>
       <c r="F19" t="n">
-        <v>5</v>
+        <v>4.4</v>
       </c>
       <c r="G19" t="n">
-        <v>5.3</v>
+        <v>5.2</v>
       </c>
       <c r="H19" t="n">
-        <v>1.73</v>
+        <v>1.7</v>
       </c>
       <c r="I19" t="n">
-        <v>1.74</v>
+        <v>1.82</v>
       </c>
       <c r="J19" t="n">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="K19" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N19" t="n">
-        <v>4.7</v>
+        <v>0</v>
       </c>
       <c r="O19" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="P19" t="n">
-        <v>2.26</v>
+        <v>2.38</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.73</v>
+        <v>1.58</v>
       </c>
       <c r="R19" t="n">
-        <v>1.51</v>
+        <v>0</v>
       </c>
       <c r="S19" t="n">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="T19" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -4109,123 +4109,123 @@
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="Y19" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Z19" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AA19" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AC19" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AD19" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AE19" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AG19" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AH19" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AI19" t="n">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AJ19" t="n">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AK19" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL19" t="n">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AM19" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AN19" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AO19" t="n">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AP19" t="n">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AQ19" t="n">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AR19" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AS19" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AT19" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AU19" t="n">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AV19" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AW19" t="n">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AX19" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AY19" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AZ19" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BA19" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BC19" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BD19" t="n">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BE19" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="BF19" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BG19" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-22 10:44:38</t>
+          <t>2026-04-22 12:59:55</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>English Premier League</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -4235,66 +4235,66 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:30:00</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Wisla Krakow</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Nottm Forest</t>
+          <t>Puszcza Niepolomice</t>
         </is>
       </c>
       <c r="F20" t="n">
-        <v>2.82</v>
+        <v>1.53</v>
       </c>
       <c r="G20" t="n">
-        <v>2.86</v>
+        <v>1.65</v>
       </c>
       <c r="H20" t="n">
-        <v>2.84</v>
+        <v>6.4</v>
       </c>
       <c r="I20" t="n">
-        <v>2.88</v>
+        <v>9</v>
       </c>
       <c r="J20" t="n">
-        <v>3.3</v>
+        <v>4.1</v>
       </c>
       <c r="K20" t="n">
-        <v>3.35</v>
+        <v>4.8</v>
       </c>
       <c r="L20" t="n">
         <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="N20" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="O20" t="n">
-        <v>1.41</v>
+        <v>0</v>
       </c>
       <c r="P20" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="Q20" t="n">
-        <v>2.24</v>
+        <v>1.72</v>
       </c>
       <c r="R20" t="n">
-        <v>1.29</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="T20" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U20" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="V20" t="n">
         <v>0</v>
@@ -4303,123 +4303,123 @@
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="Y20" t="n">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z20" t="n">
-        <v>18.5</v>
+        <v>0</v>
       </c>
       <c r="AA20" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AC20" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AD20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AH20" t="n">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AI20" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AJ20" t="n">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AK20" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AL20" t="n">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AM20" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AN20" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AO20" t="n">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AQ20" t="n">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AR20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AS20" t="n">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AT20" t="n">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AV20" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AW20" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="AX20" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="AY20" t="n">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="BA20" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BB20" t="n">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BC20" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BD20" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="BE20" t="n">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="BF20" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BG20" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-22 10:44:38</t>
+          <t>2026-04-22 12:59:55</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Spanish La Liga</t>
+          <t>French Ligue 1</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -4429,30 +4429,30 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>16:00:00</t>
+          <t>15:45:00</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Brest</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F21" t="n">
-        <v>3.75</v>
+        <v>5.1</v>
       </c>
       <c r="G21" t="n">
-        <v>4.1</v>
+        <v>5.4</v>
       </c>
       <c r="H21" t="n">
-        <v>1.91</v>
+        <v>1.73</v>
       </c>
       <c r="I21" t="n">
-        <v>1.98</v>
+        <v>1.74</v>
       </c>
       <c r="J21" t="n">
         <v>4.2</v>
@@ -4464,31 +4464,31 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.03</v>
+        <v>1.05</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P21" t="n">
-        <v>2.62</v>
+        <v>2.26</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.56</v>
+        <v>1.73</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="T21" t="n">
-        <v>1.57</v>
+        <v>1.76</v>
       </c>
       <c r="U21" t="n">
-        <v>2.62</v>
+        <v>2.24</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -4497,123 +4497,123 @@
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>44</v>
+        <v>23</v>
       </c>
       <c r="Y21" t="n">
-        <v>14</v>
+        <v>10.5</v>
       </c>
       <c r="Z21" t="n">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AA21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>21</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>10</v>
+      </c>
+      <c r="AE21" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AF21" t="n">
+        <v>42</v>
+      </c>
+      <c r="AG21" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH21" t="n">
+        <v>18</v>
+      </c>
+      <c r="AI21" t="n">
         <v>32</v>
       </c>
-      <c r="AB21" t="n">
-        <v>22</v>
-      </c>
-      <c r="AC21" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>11</v>
-      </c>
-      <c r="AE21" t="n">
-        <v>21</v>
-      </c>
-      <c r="AF21" t="n">
+      <c r="AJ21" t="n">
+        <v>140</v>
+      </c>
+      <c r="AK21" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL21" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM21" t="n">
+        <v>100</v>
+      </c>
+      <c r="AN21" t="n">
         <v>60</v>
-      </c>
-      <c r="AG21" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AH21" t="n">
-        <v>16</v>
-      </c>
-      <c r="AI21" t="n">
-        <v>42</v>
-      </c>
-      <c r="AJ21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK21" t="n">
-        <v>85</v>
-      </c>
-      <c r="AL21" t="n">
-        <v>44</v>
-      </c>
-      <c r="AM21" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>50</v>
       </c>
       <c r="AO21" t="n">
         <v>8.6</v>
       </c>
       <c r="AP21" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="AQ21" t="n">
-        <v>12.5</v>
+        <v>9.6</v>
       </c>
       <c r="AR21" t="n">
-        <v>13.5</v>
+        <v>10.5</v>
       </c>
       <c r="AS21" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AT21" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AU21" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV21" t="n">
         <v>9.4</v>
-      </c>
-      <c r="AV21" t="n">
-        <v>9.800000000000001</v>
       </c>
       <c r="AW21" t="n">
         <v>15.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="AY21" t="n">
-        <v>14.5</v>
+        <v>18</v>
       </c>
       <c r="AZ21" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BA21" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="BB21" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="BC21" t="n">
-        <v>32</v>
+        <v>13.5</v>
       </c>
       <c r="BD21" t="n">
-        <v>24</v>
+        <v>40</v>
       </c>
       <c r="BE21" t="n">
-        <v>30</v>
+        <v>13.5</v>
       </c>
       <c r="BF21" t="n">
-        <v>19.5</v>
+        <v>13</v>
       </c>
       <c r="BG21" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-22 10:44:38</t>
+          <t>2026-04-22 12:59:55</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Portuguese Primeira Liga</t>
+          <t>English Premier League</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -4623,66 +4623,66 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>16:15:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Alverca</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Arouca</t>
+          <t>Nottm Forest</t>
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.32</v>
+        <v>2.84</v>
       </c>
       <c r="G22" t="n">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="H22" t="n">
-        <v>3.25</v>
+        <v>2.84</v>
       </c>
       <c r="I22" t="n">
-        <v>3.6</v>
+        <v>2.88</v>
       </c>
       <c r="J22" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K22" t="n">
         <v>3.35</v>
       </c>
-      <c r="K22" t="n">
-        <v>3.6</v>
-      </c>
       <c r="L22" t="n">
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -4691,123 +4691,123 @@
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AQ22" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AR22" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AS22" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AT22" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AU22" t="n">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV22" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AW22" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AX22" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AY22" t="n">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BA22" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BB22" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="BC22" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BD22" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="BE22" t="n">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="BF22" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BG22" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-22 10:44:38</t>
+          <t>2026-04-22 12:59:55</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Spanish La Liga</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -4817,42 +4817,42 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>17:00:00</t>
+          <t>16:00:00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Deportivo Riestra</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CA Independiente</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="F23" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="G23" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="H23" t="n">
-        <v>2.3</v>
+        <v>1.92</v>
       </c>
       <c r="I23" t="n">
-        <v>2.54</v>
+        <v>1.98</v>
       </c>
       <c r="J23" t="n">
-        <v>2.78</v>
+        <v>4.2</v>
       </c>
       <c r="K23" t="n">
-        <v>3.05</v>
+        <v>4.4</v>
       </c>
       <c r="L23" t="n">
         <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="N23" t="n">
         <v>0</v>
@@ -4861,10 +4861,10 @@
         <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>1.39</v>
+        <v>2.64</v>
       </c>
       <c r="Q23" t="n">
-        <v>3.3</v>
+        <v>1.56</v>
       </c>
       <c r="R23" t="n">
         <v>0</v>
@@ -4873,10 +4873,10 @@
         <v>0</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -4885,123 +4885,123 @@
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AQ23" t="n">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AR23" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AS23" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AT23" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="AU23" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AV23" t="n">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW23" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AY23" t="n">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BA23" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BB23" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="BC23" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BD23" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="BE23" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="BF23" t="n">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="BG23" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-22 10:44:38</t>
+          <t>2026-04-22 12:59:55</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Portuguese Primeira Liga</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -5011,36 +5011,36 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>16:15:00</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>Alverca</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>Arouca</t>
         </is>
       </c>
       <c r="F24" t="n">
-        <v>3</v>
+        <v>2.34</v>
       </c>
       <c r="G24" t="n">
-        <v>3.45</v>
+        <v>2.5</v>
       </c>
       <c r="H24" t="n">
-        <v>2.38</v>
+        <v>3.25</v>
       </c>
       <c r="I24" t="n">
-        <v>2.68</v>
+        <v>3.6</v>
       </c>
       <c r="J24" t="n">
-        <v>2.96</v>
+        <v>3.35</v>
       </c>
       <c r="K24" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
@@ -5055,10 +5055,10 @@
         <v>0</v>
       </c>
       <c r="P24" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
         <v>0</v>
@@ -5188,14 +5188,14 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-22 10:44:38</t>
+          <t>2026-04-22 12:59:55</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -5205,36 +5205,36 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>17:00:00</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Deportivo Riestra</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>CA Independiente</t>
         </is>
       </c>
       <c r="F25" t="n">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="G25" t="n">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="H25" t="n">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="I25" t="n">
-        <v>2.6</v>
+        <v>2.5</v>
       </c>
       <c r="J25" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="K25" t="n">
-        <v>3.5</v>
+        <v>3.05</v>
       </c>
       <c r="L25" t="n">
         <v>0</v>
@@ -5249,10 +5249,10 @@
         <v>0</v>
       </c>
       <c r="P25" t="n">
-        <v>1.67</v>
+        <v>1.39</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.26</v>
+        <v>3.3</v>
       </c>
       <c r="R25" t="n">
         <v>0</v>
@@ -5382,14 +5382,14 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-22 10:44:38</t>
+          <t>2026-04-22 12:59:55</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -5399,36 +5399,36 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Estudiantes Rio Cuarto</t>
+          <t>Cucuta Deportivo</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Junior FC Barranquilla</t>
         </is>
       </c>
       <c r="F26" t="n">
-        <v>5.1</v>
+        <v>2.96</v>
       </c>
       <c r="G26" t="n">
-        <v>5.4</v>
+        <v>3.45</v>
       </c>
       <c r="H26" t="n">
-        <v>1.95</v>
+        <v>2.34</v>
       </c>
       <c r="I26" t="n">
-        <v>1.98</v>
+        <v>2.68</v>
       </c>
       <c r="J26" t="n">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K26" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5443,10 +5443,10 @@
         <v>0</v>
       </c>
       <c r="P26" t="n">
-        <v>1.52</v>
+        <v>1.85</v>
       </c>
       <c r="Q26" t="n">
-        <v>2.68</v>
+        <v>1.97</v>
       </c>
       <c r="R26" t="n">
         <v>0</v>
@@ -5576,14 +5576,14 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-22 10:44:38</t>
+          <t>2026-04-22 12:59:55</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -5593,36 +5593,36 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Central Cordoba (SdE)</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F27" t="n">
-        <v>1.53</v>
+        <v>3.75</v>
       </c>
       <c r="G27" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="H27" t="n">
-        <v>8.6</v>
+        <v>2.14</v>
       </c>
       <c r="I27" t="n">
-        <v>11</v>
+        <v>2.42</v>
       </c>
       <c r="J27" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="K27" t="n">
-        <v>4.2</v>
+        <v>3.45</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -5637,10 +5637,10 @@
         <v>0</v>
       </c>
       <c r="P27" t="n">
-        <v>1.62</v>
+        <v>1.67</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="R27" t="n">
         <v>0</v>
@@ -5770,201 +5770,589 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-22 10:44:38</t>
+          <t>2026-04-22 12:59:55</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>19:15:00</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Lanus</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Central Cordoba (SdE)</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H28" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I28" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J28" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K28" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L28" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" t="n">
+        <v>0</v>
+      </c>
+      <c r="P28" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R28" t="n">
+        <v>0</v>
+      </c>
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
+      </c>
+      <c r="V28" t="n">
+        <v>0</v>
+      </c>
+      <c r="W28" t="n">
+        <v>0</v>
+      </c>
+      <c r="X28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y28" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY28" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG28" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH28" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:59:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>19:15:00</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>Estudiantes Rio Cuarto</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>Rosario Central</t>
+        </is>
+      </c>
+      <c r="F29" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G29" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="I29" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="J29" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K29" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="L29" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" t="n">
+        <v>0</v>
+      </c>
+      <c r="P29" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="R29" t="n">
+        <v>0</v>
+      </c>
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>0</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
+      </c>
+      <c r="V29" t="n">
+        <v>0</v>
+      </c>
+      <c r="W29" t="n">
+        <v>0</v>
+      </c>
+      <c r="X29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y29" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY29" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG29" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH29" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:59:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
+      <c r="B30" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="C28" t="inlineStr">
+      <c r="C30" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr">
+      <c r="D30" t="inlineStr">
         <is>
           <t>Ponte Preta</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="E30" t="inlineStr">
         <is>
           <t>America MG</t>
         </is>
       </c>
-      <c r="F28" t="n">
+      <c r="F30" t="n">
         <v>2.8</v>
       </c>
-      <c r="G28" t="n">
+      <c r="G30" t="n">
         <v>3.05</v>
       </c>
-      <c r="H28" t="n">
+      <c r="H30" t="n">
         <v>2.8</v>
       </c>
-      <c r="I28" t="n">
-        <v>3</v>
-      </c>
-      <c r="J28" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="K28" t="n">
+      <c r="I30" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="J30" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K30" t="n">
         <v>3.35</v>
       </c>
-      <c r="L28" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" t="n">
-        <v>0</v>
-      </c>
-      <c r="P28" t="n">
+      <c r="L30" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" t="n">
+        <v>0</v>
+      </c>
+      <c r="P30" t="n">
         <v>1.68</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="Q30" t="n">
         <v>2.28</v>
       </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="n">
-        <v>0</v>
-      </c>
-      <c r="T28" t="n">
-        <v>0</v>
-      </c>
-      <c r="U28" t="n">
-        <v>0</v>
-      </c>
-      <c r="V28" t="n">
-        <v>0</v>
-      </c>
-      <c r="W28" t="n">
-        <v>0</v>
-      </c>
-      <c r="X28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y28" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG28" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH28" t="inlineStr">
-        <is>
-          <t>2026-04-22 10:44:38</t>
+      <c r="R30" t="n">
+        <v>0</v>
+      </c>
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
+      </c>
+      <c r="V30" t="n">
+        <v>0</v>
+      </c>
+      <c r="W30" t="n">
+        <v>0</v>
+      </c>
+      <c r="X30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y30" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY30" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG30" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH30" t="inlineStr">
+        <is>
+          <t>2026-04-22 12:59:55</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH85"/>
+  <dimension ref="A1:BH88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -763,7 +763,7 @@
         <v>2.12</v>
       </c>
       <c r="H2" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="I2" t="n">
         <v>3.65</v>
@@ -775,13 +775,13 @@
         <v>4.6</v>
       </c>
       <c r="L2" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="M2" t="n">
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="O2" t="n">
         <v>1.17</v>
@@ -790,16 +790,16 @@
         <v>2.7</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R2" t="n">
         <v>1.69</v>
       </c>
       <c r="S2" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="T2" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="U2" t="n">
         <v>2.68</v>
@@ -814,7 +814,7 @@
         <v>34</v>
       </c>
       <c r="Y2" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="Z2" t="n">
         <v>1000</v>
@@ -886,7 +886,7 @@
         <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AX2" t="n">
         <v>15</v>
@@ -898,7 +898,7 @@
         <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB2" t="n">
         <v>19.5</v>
@@ -910,7 +910,7 @@
         <v>18.5</v>
       </c>
       <c r="BE2" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="BF2" t="n">
         <v>8</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -996,7 +996,7 @@
         <v>1.71</v>
       </c>
       <c r="U3" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V3" t="n">
         <v>1.81</v>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -1348,7 +1348,7 @@
         <v>3.75</v>
       </c>
       <c r="I5" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J5" t="n">
         <v>3</v>
@@ -1502,7 +1502,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
         <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1566,7 +1566,7 @@
         <v>1.86</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="R6" t="n">
         <v>1.32</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -2315,10 +2315,10 @@
         <v>2.36</v>
       </c>
       <c r="H10" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I10" t="n">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="J10" t="n">
         <v>3.35</v>
@@ -2333,22 +2333,22 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="O10" t="n">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P10" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="R10" t="n">
         <v>1.18</v>
       </c>
       <c r="S10" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="T10" t="n">
         <v>1.01</v>
@@ -2360,7 +2360,7 @@
         <v>1.33</v>
       </c>
       <c r="W10" t="n">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -2721,7 +2721,7 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="O12" t="n">
         <v>1.31</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -3130,7 +3130,7 @@
         <v>1.62</v>
       </c>
       <c r="U14" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="V14" t="n">
         <v>1.26</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -3473,7 +3473,7 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G16" t="n">
         <v>2.32</v>
@@ -3482,34 +3482,34 @@
         <v>3.2</v>
       </c>
       <c r="I16" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="J16" t="n">
-        <v>3.8</v>
+        <v>3.65</v>
       </c>
       <c r="K16" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>1.98</v>
+        <v>1.79</v>
       </c>
       <c r="O16" t="n">
         <v>1.3</v>
       </c>
       <c r="P16" t="n">
-        <v>1.98</v>
+        <v>1.78</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.9</v>
+        <v>1.76</v>
       </c>
       <c r="R16" t="n">
-        <v>1.4</v>
+        <v>1.27</v>
       </c>
       <c r="S16" t="n">
         <v>2.92</v>
@@ -3521,7 +3521,7 @@
         <v>1.01</v>
       </c>
       <c r="V16" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W16" t="n">
         <v>1.75</v>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
         <v>3.65</v>
       </c>
       <c r="K17" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="L17" t="n">
         <v>1.01</v>
@@ -3691,22 +3691,22 @@
         <v>1.02</v>
       </c>
       <c r="N17" t="n">
-        <v>2.1</v>
+        <v>1.45</v>
       </c>
       <c r="O17" t="n">
         <v>1.19</v>
       </c>
       <c r="P17" t="n">
-        <v>2.08</v>
+        <v>1.44</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.59</v>
+        <v>1.52</v>
       </c>
       <c r="R17" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S17" t="n">
-        <v>2.4</v>
+        <v>2.32</v>
       </c>
       <c r="T17" t="n">
         <v>1.01</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -3864,10 +3864,10 @@
         <v>4.9</v>
       </c>
       <c r="G18" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="H18" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="I18" t="n">
         <v>1.91</v>
@@ -3879,7 +3879,7 @@
         <v>4.1</v>
       </c>
       <c r="L18" t="n">
-        <v>1.41</v>
+        <v>1.35</v>
       </c>
       <c r="M18" t="n">
         <v>1.07</v>
@@ -3900,13 +3900,13 @@
         <v>1.31</v>
       </c>
       <c r="S18" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="T18" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U18" t="n">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="V18" t="n">
         <v>2.08</v>
@@ -3966,10 +3966,10 @@
         <v>1000</v>
       </c>
       <c r="AO18" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AP18" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ18" t="n">
         <v>6</v>
@@ -3993,7 +3993,7 @@
         <v>14.5</v>
       </c>
       <c r="AX18" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="AY18" t="n">
         <v>15</v>
@@ -4005,7 +4005,7 @@
         <v>3.95</v>
       </c>
       <c r="BB18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC18" t="n">
         <v>4.1</v>
@@ -4014,7 +4014,7 @@
         <v>4.1</v>
       </c>
       <c r="BE18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF18" t="n">
         <v>4.1</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -4088,7 +4088,7 @@
         <v>2.14</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R19" t="n">
         <v>1.44</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -4249,58 +4249,58 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.9</v>
+        <v>1.84</v>
       </c>
       <c r="G20" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="H20" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="I20" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="J20" t="n">
         <v>3.25</v>
       </c>
       <c r="K20" t="n">
-        <v>85</v>
+        <v>8</v>
       </c>
       <c r="L20" t="n">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="M20" t="n">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N20" t="n">
-        <v>2.08</v>
+        <v>1.41</v>
       </c>
       <c r="O20" t="n">
         <v>1.21</v>
       </c>
       <c r="P20" t="n">
-        <v>2.08</v>
+        <v>1.41</v>
       </c>
       <c r="Q20" t="n">
-        <v>1.75</v>
+        <v>1.54</v>
       </c>
       <c r="R20" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S20" t="n">
-        <v>2.6</v>
+        <v>2.36</v>
       </c>
       <c r="T20" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="U20" t="n">
-        <v>1.96</v>
+        <v>1.01</v>
       </c>
       <c r="V20" t="n">
-        <v>1.31</v>
+        <v>1.26</v>
       </c>
       <c r="W20" t="n">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="X20" t="n">
         <v>1000</v>
@@ -4309,7 +4309,7 @@
         <v>23</v>
       </c>
       <c r="Z20" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AA20" t="n">
         <v>1000</v>
@@ -4339,7 +4339,7 @@
         <v>1000</v>
       </c>
       <c r="AJ20" t="n">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AK20" t="n">
         <v>29</v>
@@ -4357,62 +4357,62 @@
         <v>1000</v>
       </c>
       <c r="AP20" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="AQ20" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AR20" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>1.79</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BB20" t="n">
         <v>1.85</v>
       </c>
-      <c r="AS20" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.76</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.71</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.84</v>
-      </c>
       <c r="BC20" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="BD20" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="BE20" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="BF20" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="BG20" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="F21" t="n">
-        <v>2.52</v>
+        <v>2.38</v>
       </c>
       <c r="G21" t="n">
         <v>3.25</v>
@@ -4452,7 +4452,7 @@
         <v>2.38</v>
       </c>
       <c r="I21" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="J21" t="n">
         <v>3.55</v>
@@ -4467,22 +4467,22 @@
         <v>1.01</v>
       </c>
       <c r="N21" t="n">
-        <v>1.95</v>
+        <v>1.81</v>
       </c>
       <c r="O21" t="n">
         <v>1.27</v>
       </c>
       <c r="P21" t="n">
-        <v>1.94</v>
+        <v>1.81</v>
       </c>
       <c r="Q21" t="n">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R21" t="n">
         <v>1.18</v>
       </c>
       <c r="S21" t="n">
-        <v>1.8</v>
+        <v>1.27</v>
       </c>
       <c r="T21" t="n">
         <v>1.01</v>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -4637,22 +4637,22 @@
         </is>
       </c>
       <c r="F22" t="n">
-        <v>2.36</v>
+        <v>1.09</v>
       </c>
       <c r="G22" t="n">
         <v>2.6</v>
       </c>
       <c r="H22" t="n">
-        <v>2.86</v>
+        <v>1.09</v>
       </c>
       <c r="I22" t="n">
-        <v>3.15</v>
+        <v>1000</v>
       </c>
       <c r="J22" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K22" t="n">
-        <v>4.1</v>
+        <v>1000</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5058,7 @@
         <v>2.14</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="R24" t="n">
         <v>1.45</v>
@@ -5070,7 +5070,7 @@
         <v>1.64</v>
       </c>
       <c r="U24" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="V24" t="n">
         <v>1.41</v>
@@ -5127,7 +5127,7 @@
         <v>90</v>
       </c>
       <c r="AN24" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AO24" t="n">
         <v>34</v>
@@ -5175,10 +5175,10 @@
         <v>20</v>
       </c>
       <c r="BD24" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BE24" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BF24" t="n">
         <v>11</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5255,7 @@
         <v>1.73</v>
       </c>
       <c r="R25" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S25" t="n">
         <v>2.84</v>
@@ -5306,7 +5306,7 @@
         <v>19</v>
       </c>
       <c r="AI25" t="n">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="AJ25" t="n">
         <v>21</v>
@@ -5324,7 +5324,7 @@
         <v>9</v>
       </c>
       <c r="AO25" t="n">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP25" t="n">
         <v>16.5</v>
@@ -5372,7 +5372,7 @@
         <v>8</v>
       </c>
       <c r="BE25" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BF25" t="n">
         <v>7</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -5437,7 +5437,7 @@
         <v>1.01</v>
       </c>
       <c r="N26" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O26" t="n">
         <v>1.19</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -5810,28 +5810,28 @@
         <v>2.48</v>
       </c>
       <c r="I28" t="n">
-        <v>2.74</v>
+        <v>2.7</v>
       </c>
       <c r="J28" t="n">
         <v>2.72</v>
       </c>
       <c r="K28" t="n">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="L28" t="n">
         <v>1.71</v>
       </c>
       <c r="M28" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="N28" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="O28" t="n">
         <v>1.78</v>
       </c>
       <c r="P28" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="Q28" t="n">
         <v>3.4</v>
@@ -5840,7 +5840,7 @@
         <v>1.12</v>
       </c>
       <c r="S28" t="n">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="T28" t="n">
         <v>2.44</v>
@@ -5849,7 +5849,7 @@
         <v>1.57</v>
       </c>
       <c r="V28" t="n">
-        <v>1.57</v>
+        <v>1.59</v>
       </c>
       <c r="W28" t="n">
         <v>1.3</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -5995,22 +5995,22 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.72</v>
+        <v>1.63</v>
       </c>
       <c r="G29" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="H29" t="n">
-        <v>4.5</v>
+        <v>3.9</v>
       </c>
       <c r="I29" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="J29" t="n">
-        <v>3.75</v>
+        <v>3.4</v>
       </c>
       <c r="K29" t="n">
-        <v>4.3</v>
+        <v>7.6</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -6019,34 +6019,34 @@
         <v>1.02</v>
       </c>
       <c r="N29" t="n">
-        <v>2.1</v>
+        <v>1.9</v>
       </c>
       <c r="O29" t="n">
         <v>1.22</v>
       </c>
       <c r="P29" t="n">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="Q29" t="n">
-        <v>1.75</v>
+        <v>1.22</v>
       </c>
       <c r="R29" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="S29" t="n">
-        <v>2.84</v>
+        <v>2.58</v>
       </c>
       <c r="T29" t="n">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="U29" t="n">
         <v>1.01</v>
       </c>
       <c r="V29" t="n">
-        <v>1.2</v>
+        <v>1.17</v>
       </c>
       <c r="W29" t="n">
-        <v>2.1</v>
+        <v>1.96</v>
       </c>
       <c r="X29" t="n">
         <v>1000</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -6383,13 +6383,13 @@
         </is>
       </c>
       <c r="F31" t="n">
-        <v>2.34</v>
+        <v>2.18</v>
       </c>
       <c r="G31" t="n">
-        <v>2.72</v>
+        <v>2.78</v>
       </c>
       <c r="H31" t="n">
-        <v>3.2</v>
+        <v>2.94</v>
       </c>
       <c r="I31" t="n">
         <v>3.95</v>
@@ -6407,7 +6407,7 @@
         <v>1.01</v>
       </c>
       <c r="N31" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="O31" t="n">
         <v>1.39</v>
@@ -6431,10 +6431,10 @@
         <v>1.01</v>
       </c>
       <c r="V31" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W31" t="n">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -6613,10 +6613,10 @@
         <v>1.56</v>
       </c>
       <c r="R32" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S32" t="n">
-        <v>1.56</v>
+        <v>2.32</v>
       </c>
       <c r="T32" t="n">
         <v>1.01</v>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -6998,7 +6998,7 @@
         <v>1.94</v>
       </c>
       <c r="Q34" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="R34" t="n">
         <v>1.35</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7159,7 @@
         </is>
       </c>
       <c r="F35" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="G35" t="n">
         <v>1.57</v>
@@ -7171,7 +7171,7 @@
         <v>10</v>
       </c>
       <c r="J35" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="K35" t="n">
         <v>4.8</v>
@@ -7180,7 +7180,7 @@
         <v>1.01</v>
       </c>
       <c r="M35" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N35" t="n">
         <v>1.94</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -7380,7 +7380,7 @@
         <v>1.85</v>
       </c>
       <c r="O36" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="P36" t="n">
         <v>1.85</v>
@@ -7404,7 +7404,7 @@
         <v>1.64</v>
       </c>
       <c r="W36" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X36" t="n">
         <v>1000</v>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -7547,22 +7547,22 @@
         </is>
       </c>
       <c r="F37" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="G37" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="H37" t="n">
-        <v>2.02</v>
+        <v>1.9</v>
       </c>
       <c r="I37" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="J37" t="n">
-        <v>3.15</v>
+        <v>2.9</v>
       </c>
       <c r="K37" t="n">
-        <v>3.75</v>
+        <v>5.7</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
@@ -7571,22 +7571,22 @@
         <v>1.01</v>
       </c>
       <c r="N37" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="O37" t="n">
         <v>1.36</v>
       </c>
       <c r="P37" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="Q37" t="n">
-        <v>2.12</v>
+        <v>1.98</v>
       </c>
       <c r="R37" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="S37" t="n">
-        <v>2.12</v>
+        <v>3.4</v>
       </c>
       <c r="T37" t="n">
         <v>1.01</v>
@@ -7595,10 +7595,10 @@
         <v>1.01</v>
       </c>
       <c r="V37" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="W37" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X37" t="n">
         <v>1000</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -7741,28 +7741,28 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="G38" t="n">
-        <v>1.62</v>
+        <v>1.71</v>
       </c>
       <c r="H38" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="I38" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="J38" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K38" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L38" t="n">
         <v>1.01</v>
       </c>
       <c r="M38" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N38" t="n">
         <v>1.94</v>
@@ -7774,7 +7774,7 @@
         <v>1.94</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R38" t="n">
         <v>1.29</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -7935,19 +7935,19 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="G39" t="n">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="H39" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="I39" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="J39" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K39" t="n">
         <v>4.5</v>
@@ -7983,10 +7983,10 @@
         <v>1.77</v>
       </c>
       <c r="V39" t="n">
-        <v>1.16</v>
+        <v>1.14</v>
       </c>
       <c r="W39" t="n">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="X39" t="n">
         <v>18.5</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -8138,10 +8138,10 @@
         <v>2.4</v>
       </c>
       <c r="I40" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="J40" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K40" t="n">
         <v>3.95</v>
@@ -8153,22 +8153,22 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="O40" t="n">
         <v>1.26</v>
       </c>
       <c r="P40" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q40" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="R40" t="n">
         <v>1.18</v>
       </c>
       <c r="S40" t="n">
-        <v>2.92</v>
+        <v>1.66</v>
       </c>
       <c r="T40" t="n">
         <v>1.01</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -8323,13 +8323,13 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="G41" t="n">
         <v>1.98</v>
       </c>
       <c r="H41" t="n">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="I41" t="n">
         <v>5.9</v>
@@ -8338,7 +8338,7 @@
         <v>3.35</v>
       </c>
       <c r="K41" t="n">
-        <v>4.1</v>
+        <v>5.1</v>
       </c>
       <c r="L41" t="n">
         <v>1.01</v>
@@ -8347,16 +8347,16 @@
         <v>1.01</v>
       </c>
       <c r="N41" t="n">
-        <v>1.83</v>
+        <v>1.71</v>
       </c>
       <c r="O41" t="n">
         <v>1.31</v>
       </c>
       <c r="P41" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="Q41" t="n">
         <v>1.83</v>
-      </c>
-      <c r="Q41" t="n">
-        <v>1.96</v>
       </c>
       <c r="R41" t="n">
         <v>1.27</v>
@@ -8374,7 +8374,7 @@
         <v>1.22</v>
       </c>
       <c r="W41" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="X41" t="n">
         <v>1000</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -8711,7 +8711,7 @@
         </is>
       </c>
       <c r="F43" t="n">
-        <v>1.99</v>
+        <v>1.95</v>
       </c>
       <c r="G43" t="n">
         <v>2.12</v>
@@ -8741,7 +8741,7 @@
         <v>1.31</v>
       </c>
       <c r="P43" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="Q43" t="n">
         <v>1.86</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -8908,13 +8908,13 @@
         <v>2.54</v>
       </c>
       <c r="G44" t="n">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="H44" t="n">
         <v>2.74</v>
       </c>
       <c r="I44" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="J44" t="n">
         <v>3.4</v>
@@ -8926,13 +8926,13 @@
         <v>1.01</v>
       </c>
       <c r="M44" t="n">
-        <v>1.05</v>
+        <v>1.07</v>
       </c>
       <c r="N44" t="n">
-        <v>1.93</v>
+        <v>3.8</v>
       </c>
       <c r="O44" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="P44" t="n">
         <v>1.93</v>
@@ -8941,73 +8941,73 @@
         <v>1.89</v>
       </c>
       <c r="R44" t="n">
-        <v>1.31</v>
+        <v>1.37</v>
       </c>
       <c r="S44" t="n">
-        <v>2.84</v>
+        <v>3.25</v>
       </c>
       <c r="T44" t="n">
-        <v>1.5</v>
+        <v>1.7</v>
       </c>
       <c r="U44" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="V44" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="W44" t="n">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="X44" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="Y44" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="Z44" t="n">
         <v>21</v>
       </c>
       <c r="AA44" t="n">
-        <v>65</v>
+        <v>48</v>
       </c>
       <c r="AB44" t="n">
-        <v>16</v>
+        <v>12.5</v>
       </c>
       <c r="AC44" t="n">
-        <v>11</v>
+        <v>8.6</v>
       </c>
       <c r="AD44" t="n">
         <v>13.5</v>
       </c>
       <c r="AE44" t="n">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="AF44" t="n">
         <v>19</v>
       </c>
       <c r="AG44" t="n">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="AH44" t="n">
-        <v>23</v>
+        <v>17.5</v>
       </c>
       <c r="AI44" t="n">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="AJ44" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="AK44" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AL44" t="n">
-        <v>55</v>
+        <v>42</v>
       </c>
       <c r="AM44" t="n">
         <v>1000</v>
       </c>
       <c r="AN44" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AO44" t="n">
         <v>1000</v>
@@ -9022,7 +9022,7 @@
         <v>17</v>
       </c>
       <c r="AS44" t="n">
-        <v>3.35</v>
+        <v>36</v>
       </c>
       <c r="AT44" t="n">
         <v>9.800000000000001</v>
@@ -9034,7 +9034,7 @@
         <v>11</v>
       </c>
       <c r="AW44" t="n">
-        <v>3.25</v>
+        <v>6.8</v>
       </c>
       <c r="AX44" t="n">
         <v>15</v>
@@ -9046,19 +9046,19 @@
         <v>14</v>
       </c>
       <c r="BA44" t="n">
-        <v>3.3</v>
+        <v>7.2</v>
       </c>
       <c r="BB44" t="n">
-        <v>3.3</v>
+        <v>7.2</v>
       </c>
       <c r="BC44" t="n">
-        <v>3.25</v>
+        <v>6.6</v>
       </c>
       <c r="BD44" t="n">
-        <v>3.3</v>
+        <v>7.2</v>
       </c>
       <c r="BE44" t="n">
-        <v>3.5</v>
+        <v>8</v>
       </c>
       <c r="BF44" t="n">
         <v>16.5</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -9108,7 +9108,7 @@
         <v>2.62</v>
       </c>
       <c r="I45" t="n">
-        <v>2.9</v>
+        <v>2.96</v>
       </c>
       <c r="J45" t="n">
         <v>3.2</v>
@@ -9207,10 +9207,10 @@
         <v>42</v>
       </c>
       <c r="AP45" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AQ45" t="n">
-        <v>8.4</v>
+        <v>7.2</v>
       </c>
       <c r="AR45" t="n">
         <v>13</v>
@@ -9219,13 +9219,13 @@
         <v>3.95</v>
       </c>
       <c r="AT45" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="AU45" t="n">
-        <v>6.4</v>
+        <v>5.6</v>
       </c>
       <c r="AV45" t="n">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW45" t="n">
         <v>3.9</v>
@@ -9240,10 +9240,10 @@
         <v>16</v>
       </c>
       <c r="BA45" t="n">
+        <v>36</v>
+      </c>
+      <c r="BB45" t="n">
         <v>4</v>
-      </c>
-      <c r="BB45" t="n">
-        <v>34</v>
       </c>
       <c r="BC45" t="n">
         <v>3.9</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -9293,7 +9293,7 @@
         </is>
       </c>
       <c r="F46" t="n">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="G46" t="n">
         <v>2.9</v>
@@ -9302,7 +9302,7 @@
         <v>2.34</v>
       </c>
       <c r="I46" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="J46" t="n">
         <v>4.1</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -9496,7 +9496,7 @@
         <v>2.1</v>
       </c>
       <c r="I47" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="J47" t="n">
         <v>3.7</v>
@@ -9508,13 +9508,13 @@
         <v>1.01</v>
       </c>
       <c r="M47" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N47" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="O47" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P47" t="n">
         <v>2.08</v>
@@ -9523,58 +9523,58 @@
         <v>1.76</v>
       </c>
       <c r="R47" t="n">
-        <v>1.35</v>
+        <v>1.42</v>
       </c>
       <c r="S47" t="n">
-        <v>2.6</v>
+        <v>2.9</v>
       </c>
       <c r="T47" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="U47" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="V47" t="n">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="W47" t="n">
         <v>1.37</v>
       </c>
       <c r="X47" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Y47" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Z47" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA47" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AB47" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AC47" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD47" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AE47" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AF47" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AG47" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AH47" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI47" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ47" t="n">
         <v>1000</v>
@@ -9583,16 +9583,16 @@
         <v>1000</v>
       </c>
       <c r="AL47" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM47" t="n">
         <v>1000</v>
       </c>
       <c r="AN47" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO47" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AP47" t="n">
         <v>15</v>
@@ -9604,7 +9604,7 @@
         <v>12.5</v>
       </c>
       <c r="AS47" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AT47" t="n">
         <v>13.5</v>
@@ -9616,10 +9616,10 @@
         <v>9.4</v>
       </c>
       <c r="AW47" t="n">
-        <v>1.03</v>
+        <v>3.75</v>
       </c>
       <c r="AX47" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AY47" t="n">
         <v>13</v>
@@ -9628,29 +9628,29 @@
         <v>14</v>
       </c>
       <c r="BA47" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BB47" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BC47" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BD47" t="n">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BE47" t="n">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BF47" t="n">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BG47" t="n">
         <v>10</v>
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -9684,19 +9684,19 @@
         <v>3.6</v>
       </c>
       <c r="G48" t="n">
-        <v>5.4</v>
+        <v>5.9</v>
       </c>
       <c r="H48" t="n">
-        <v>1.74</v>
+        <v>1.65</v>
       </c>
       <c r="I48" t="n">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="J48" t="n">
-        <v>3.8</v>
+        <v>4</v>
       </c>
       <c r="K48" t="n">
-        <v>4.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L48" t="n">
         <v>1.01</v>
@@ -9708,7 +9708,7 @@
         <v>2.16</v>
       </c>
       <c r="O48" t="n">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P48" t="n">
         <v>2.16</v>
@@ -9732,7 +9732,7 @@
         <v>2</v>
       </c>
       <c r="W48" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="X48" t="n">
         <v>1000</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -9896,10 +9896,10 @@
         <v>1.36</v>
       </c>
       <c r="M49" t="n">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N49" t="n">
-        <v>1.9</v>
+        <v>3.4</v>
       </c>
       <c r="O49" t="n">
         <v>1.29</v>
@@ -9911,16 +9911,16 @@
         <v>1.96</v>
       </c>
       <c r="R49" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="S49" t="n">
-        <v>3</v>
+        <v>3.15</v>
       </c>
       <c r="T49" t="n">
         <v>1.75</v>
       </c>
       <c r="U49" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="V49" t="n">
         <v>1.33</v>
@@ -9929,7 +9929,7 @@
         <v>1.85</v>
       </c>
       <c r="X49" t="n">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y49" t="n">
         <v>16</v>
@@ -9938,10 +9938,10 @@
         <v>1000</v>
       </c>
       <c r="AA49" t="n">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB49" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC49" t="n">
         <v>9.4</v>
@@ -9950,10 +9950,10 @@
         <v>18.5</v>
       </c>
       <c r="AE49" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AF49" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AG49" t="n">
         <v>12.5</v>
@@ -9983,19 +9983,19 @@
         <v>1000</v>
       </c>
       <c r="AP49" t="n">
-        <v>2.48</v>
+        <v>2.56</v>
       </c>
       <c r="AQ49" t="n">
         <v>10</v>
       </c>
       <c r="AR49" t="n">
-        <v>2.92</v>
+        <v>2.56</v>
       </c>
       <c r="AS49" t="n">
-        <v>2.84</v>
+        <v>2.5</v>
       </c>
       <c r="AT49" t="n">
-        <v>2.38</v>
+        <v>2.12</v>
       </c>
       <c r="AU49" t="n">
         <v>6.2</v>
@@ -10004,19 +10004,19 @@
         <v>11.5</v>
       </c>
       <c r="AW49" t="n">
-        <v>2.8</v>
+        <v>2.46</v>
       </c>
       <c r="AX49" t="n">
         <v>9.6</v>
       </c>
       <c r="AY49" t="n">
-        <v>2.36</v>
+        <v>2.12</v>
       </c>
       <c r="AZ49" t="n">
-        <v>2.56</v>
+        <v>2.28</v>
       </c>
       <c r="BA49" t="n">
-        <v>2.82</v>
+        <v>2.48</v>
       </c>
       <c r="BB49" t="n">
         <v>19.5</v>
@@ -10025,20 +10025,20 @@
         <v>17</v>
       </c>
       <c r="BD49" t="n">
-        <v>2.76</v>
+        <v>2.44</v>
       </c>
       <c r="BE49" t="n">
-        <v>2.92</v>
+        <v>2.56</v>
       </c>
       <c r="BF49" t="n">
-        <v>2.92</v>
+        <v>2.56</v>
       </c>
       <c r="BG49" t="n">
-        <v>2.92</v>
+        <v>2.56</v>
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -10072,10 +10072,10 @@
         <v>2.6</v>
       </c>
       <c r="G50" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="H50" t="n">
-        <v>2.48</v>
+        <v>2.42</v>
       </c>
       <c r="I50" t="n">
         <v>2.76</v>
@@ -10120,7 +10120,7 @@
         <v>1.57</v>
       </c>
       <c r="W50" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="X50" t="n">
         <v>1000</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -10254,31 +10254,31 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VVV Venlo</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>De Graafschap</t>
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.52</v>
+        <v>2.92</v>
       </c>
       <c r="G51" t="n">
-        <v>2.82</v>
+        <v>3.65</v>
       </c>
       <c r="H51" t="n">
-        <v>2.42</v>
+        <v>2.06</v>
       </c>
       <c r="I51" t="n">
-        <v>2.64</v>
+        <v>2.26</v>
       </c>
       <c r="J51" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K51" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="L51" t="n">
         <v>1.01</v>
@@ -10287,22 +10287,22 @@
         <v>1.02</v>
       </c>
       <c r="N51" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="O51" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="P51" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="Q51" t="n">
-        <v>1.42</v>
+        <v>1.38</v>
       </c>
       <c r="R51" t="n">
         <v>1.75</v>
       </c>
       <c r="S51" t="n">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="T51" t="n">
         <v>1.01</v>
@@ -10311,122 +10311,122 @@
         <v>1.01</v>
       </c>
       <c r="V51" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="W51" t="n">
-        <v>1.54</v>
+        <v>1.38</v>
       </c>
       <c r="X51" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="Y51" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="Z51" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA51" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AB51" t="n">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AC51" t="n">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="AD51" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AE51" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AF51" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AG51" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AH51" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AI51" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AJ51" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK51" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AL51" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM51" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AN51" t="n">
         <v>1000</v>
       </c>
       <c r="AO51" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AP51" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="AQ51" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="AR51" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="AS51" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="AT51" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="AU51" t="n">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="AV51" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="AW51" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="AX51" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="AY51" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="AZ51" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BA51" t="n">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BB51" t="n">
-        <v>2.34</v>
+        <v>1.01</v>
       </c>
       <c r="BC51" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="BD51" t="n">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="BE51" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="BF51" t="n">
-        <v>2.46</v>
+        <v>1.01</v>
       </c>
       <c r="BG51" t="n">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -10460,16 +10460,16 @@
         <v>2.82</v>
       </c>
       <c r="G52" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="H52" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="I52" t="n">
-        <v>2.44</v>
+        <v>2.8</v>
       </c>
       <c r="J52" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="K52" t="n">
         <v>4.6</v>
@@ -10481,7 +10481,7 @@
         <v>1.02</v>
       </c>
       <c r="N52" t="n">
-        <v>2.82</v>
+        <v>2.8</v>
       </c>
       <c r="O52" t="n">
         <v>1.13</v>
@@ -10490,7 +10490,7 @@
         <v>2.8</v>
       </c>
       <c r="Q52" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="R52" t="n">
         <v>1.63</v>
@@ -10505,10 +10505,10 @@
         <v>1.01</v>
       </c>
       <c r="V52" t="n">
-        <v>1.69</v>
+        <v>1.56</v>
       </c>
       <c r="W52" t="n">
-        <v>1.45</v>
+        <v>1.39</v>
       </c>
       <c r="X52" t="n">
         <v>1000</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -10642,31 +10642,31 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>RKC Waalwijk</t>
+          <t>VVV Venlo</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Jong PSV Eindhoven</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.64</v>
+        <v>2.52</v>
       </c>
       <c r="G53" t="n">
-        <v>1.88</v>
+        <v>2.82</v>
       </c>
       <c r="H53" t="n">
-        <v>4.2</v>
+        <v>2.42</v>
       </c>
       <c r="I53" t="n">
-        <v>5.8</v>
+        <v>2.64</v>
       </c>
       <c r="J53" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="K53" t="n">
-        <v>6.6</v>
+        <v>4.8</v>
       </c>
       <c r="L53" t="n">
         <v>1.01</v>
@@ -10675,22 +10675,22 @@
         <v>1.02</v>
       </c>
       <c r="N53" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="O53" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="P53" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q53" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="R53" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="S53" t="n">
-        <v>1.84</v>
+        <v>1.89</v>
       </c>
       <c r="T53" t="n">
         <v>1.01</v>
@@ -10699,122 +10699,122 @@
         <v>1.01</v>
       </c>
       <c r="V53" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="W53" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="X53" t="n">
+        <v>48</v>
+      </c>
+      <c r="Y53" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z53" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA53" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB53" t="n">
+        <v>30</v>
+      </c>
+      <c r="AC53" t="n">
+        <v>16</v>
+      </c>
+      <c r="AD53" t="n">
+        <v>19</v>
+      </c>
+      <c r="AE53" t="n">
+        <v>32</v>
+      </c>
+      <c r="AF53" t="n">
+        <v>34</v>
+      </c>
+      <c r="AG53" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH53" t="n">
+        <v>20</v>
+      </c>
+      <c r="AI53" t="n">
+        <v>38</v>
+      </c>
+      <c r="AJ53" t="n">
+        <v>55</v>
+      </c>
+      <c r="AK53" t="n">
+        <v>34</v>
+      </c>
+      <c r="AL53" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM53" t="n">
+        <v>65</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO53" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AP53" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AQ53" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AR53" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AS53" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AT53" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AU53" t="n">
         <v>2.14</v>
       </c>
-      <c r="X53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO53" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AQ53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AR53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AS53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AT53" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AU53" t="n">
-        <v>1.01</v>
-      </c>
       <c r="AV53" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="AW53" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="AX53" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="AY53" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="AZ53" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BA53" t="n">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BB53" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BC53" t="n">
-        <v>1.01</v>
+        <v>2.3</v>
       </c>
       <c r="BD53" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BE53" t="n">
-        <v>1.01</v>
+        <v>2.38</v>
       </c>
       <c r="BF53" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BG53" t="n">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -10836,179 +10836,179 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>MVV Maastricht</t>
+          <t>Cambuur Leeuwarden</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>FC Oss</t>
+          <t>Vitesse Arnhem</t>
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.52</v>
+        <v>2.16</v>
       </c>
       <c r="G54" t="n">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="H54" t="n">
-        <v>2.5</v>
+        <v>2.98</v>
       </c>
       <c r="I54" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="J54" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K54" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L54" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M54" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="N54" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="O54" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="P54" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="Q54" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="R54" t="n">
+        <v>1.74</v>
+      </c>
+      <c r="S54" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="U54" t="n">
         <v>2.78</v>
       </c>
-      <c r="J54" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K54" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="L54" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M54" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N54" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="O54" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="P54" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="Q54" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="R54" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="S54" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="T54" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U54" t="n">
-        <v>1.01</v>
-      </c>
       <c r="V54" t="n">
-        <v>1.56</v>
+        <v>1.46</v>
       </c>
       <c r="W54" t="n">
-        <v>1.55</v>
+        <v>1.76</v>
       </c>
       <c r="X54" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y54" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z54" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA54" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB54" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AC54" t="n">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD54" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE54" t="n">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AF54" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AG54" t="n">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH54" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AI54" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ54" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK54" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL54" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AM54" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AN54" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AO54" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AP54" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AQ54" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AR54" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AS54" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT54" t="n">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AU54" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV54" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AW54" t="n">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AX54" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AY54" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AZ54" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA54" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BB54" t="n">
-        <v>1.01</v>
+        <v>25</v>
       </c>
       <c r="BC54" t="n">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BD54" t="n">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE54" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF54" t="n">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BG54" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -11030,55 +11030,55 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>FC Eindhoven</t>
+          <t>Den Bosch</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>ADO Den Haag</t>
         </is>
       </c>
       <c r="F55" t="n">
-        <v>1.95</v>
+        <v>10</v>
       </c>
       <c r="G55" t="n">
-        <v>2.1</v>
+        <v>980</v>
       </c>
       <c r="H55" t="n">
-        <v>3.7</v>
+        <v>1.2</v>
       </c>
       <c r="I55" t="n">
-        <v>4.5</v>
+        <v>1.33</v>
       </c>
       <c r="J55" t="n">
-        <v>3.8</v>
+        <v>6.4</v>
       </c>
       <c r="K55" t="n">
-        <v>4.3</v>
+        <v>15</v>
       </c>
       <c r="L55" t="n">
         <v>1.01</v>
       </c>
       <c r="M55" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="N55" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="O55" t="n">
-        <v>1.21</v>
+        <v>1.11</v>
       </c>
       <c r="P55" t="n">
-        <v>2.28</v>
+        <v>1.72</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.67</v>
+        <v>1.32</v>
       </c>
       <c r="R55" t="n">
-        <v>1.25</v>
+        <v>1.72</v>
       </c>
       <c r="S55" t="n">
-        <v>2.62</v>
+        <v>1.89</v>
       </c>
       <c r="T55" t="n">
         <v>1.01</v>
@@ -11087,122 +11087,122 @@
         <v>1.01</v>
       </c>
       <c r="V55" t="n">
-        <v>1.3</v>
+        <v>3.95</v>
       </c>
       <c r="W55" t="n">
-        <v>1.9</v>
+        <v>1.01</v>
       </c>
       <c r="X55" t="n">
         <v>1000</v>
       </c>
       <c r="Y55" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Z55" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA55" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB55" t="n">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AC55" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AD55" t="n">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE55" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF55" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="AG55" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AH55" t="n">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AI55" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ55" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AK55" t="n">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AL55" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM55" t="n">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AN55" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AO55" t="n">
         <v>1000</v>
       </c>
       <c r="AP55" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="AQ55" t="n">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="AR55" t="n">
-        <v>2.36</v>
+        <v>1.01</v>
       </c>
       <c r="AS55" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="AT55" t="n">
-        <v>2.18</v>
+        <v>1.01</v>
       </c>
       <c r="AU55" t="n">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="AV55" t="n">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="AW55" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="AX55" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY55" t="n">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="AZ55" t="n">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="BA55" t="n">
-        <v>2.4</v>
+        <v>1.01</v>
       </c>
       <c r="BB55" t="n">
-        <v>2.32</v>
+        <v>1.01</v>
       </c>
       <c r="BC55" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BD55" t="n">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BE55" t="n">
-        <v>2.44</v>
+        <v>1.01</v>
       </c>
       <c r="BF55" t="n">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="BG55" t="n">
-        <v>2.48</v>
+        <v>1.01</v>
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -11224,56 +11224,56 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MVV Maastricht</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>De Graafschap</t>
+          <t>FC Oss</t>
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2.92</v>
+        <v>2.52</v>
       </c>
       <c r="G56" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="H56" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="I56" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="J56" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K56" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L56" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M56" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="N56" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="O56" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="P56" t="n">
+        <v>2.58</v>
+      </c>
+      <c r="Q56" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="R56" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S56" t="n">
         <v>2.06</v>
       </c>
-      <c r="I56" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="J56" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K56" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L56" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M56" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N56" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="O56" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="P56" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="Q56" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="R56" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="S56" t="n">
-        <v>1.84</v>
-      </c>
       <c r="T56" t="n">
         <v>1.01</v>
       </c>
@@ -11281,10 +11281,10 @@
         <v>1.01</v>
       </c>
       <c r="V56" t="n">
-        <v>1.8</v>
+        <v>1.54</v>
       </c>
       <c r="W56" t="n">
-        <v>1.42</v>
+        <v>1.48</v>
       </c>
       <c r="X56" t="n">
         <v>1000</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -11418,31 +11418,31 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Cambuur Leeuwarden</t>
+          <t>RKC Waalwijk</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Vitesse Arnhem</t>
+          <t>Jong PSV Eindhoven</t>
         </is>
       </c>
       <c r="F57" t="n">
-        <v>2.16</v>
+        <v>1.65</v>
       </c>
       <c r="G57" t="n">
-        <v>2.32</v>
+        <v>1.89</v>
       </c>
       <c r="H57" t="n">
-        <v>2.98</v>
+        <v>4.2</v>
       </c>
       <c r="I57" t="n">
-        <v>3.15</v>
+        <v>5.8</v>
       </c>
       <c r="J57" t="n">
         <v>4.3</v>
       </c>
       <c r="K57" t="n">
-        <v>4.7</v>
+        <v>6.6</v>
       </c>
       <c r="L57" t="n">
         <v>1.01</v>
@@ -11451,146 +11451,146 @@
         <v>1.02</v>
       </c>
       <c r="N57" t="n">
-        <v>6.2</v>
+        <v>3.1</v>
       </c>
       <c r="O57" t="n">
-        <v>1.15</v>
+        <v>1.1</v>
       </c>
       <c r="P57" t="n">
-        <v>2.84</v>
+        <v>3.1</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.44</v>
+        <v>1.36</v>
       </c>
       <c r="R57" t="n">
-        <v>1.74</v>
+        <v>1.76</v>
       </c>
       <c r="S57" t="n">
-        <v>2.14</v>
+        <v>1.84</v>
       </c>
       <c r="T57" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="U57" t="n">
-        <v>2.72</v>
+        <v>1.01</v>
       </c>
       <c r="V57" t="n">
-        <v>1.46</v>
+        <v>1.2</v>
       </c>
       <c r="W57" t="n">
-        <v>1.76</v>
+        <v>2.12</v>
       </c>
       <c r="X57" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="Y57" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="Z57" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AA57" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB57" t="n">
-        <v>18.5</v>
+        <v>1000</v>
       </c>
       <c r="AC57" t="n">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD57" t="n">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AE57" t="n">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AF57" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AG57" t="n">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AH57" t="n">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AI57" t="n">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AJ57" t="n">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="AK57" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AL57" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AM57" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AN57" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AO57" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AP57" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AQ57" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR57" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AS57" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AT57" t="n">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU57" t="n">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AV57" t="n">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AW57" t="n">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AX57" t="n">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="AY57" t="n">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ57" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BA57" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BB57" t="n">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BC57" t="n">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD57" t="n">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BE57" t="n">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BF57" t="n">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="BG57" t="n">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -11612,55 +11612,55 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Den Bosch</t>
+          <t>FC Eindhoven</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>ADO Den Haag</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="F58" t="n">
-        <v>10</v>
+        <v>1.95</v>
       </c>
       <c r="G58" t="n">
-        <v>980</v>
+        <v>2.16</v>
       </c>
       <c r="H58" t="n">
-        <v>1.18</v>
+        <v>3.7</v>
       </c>
       <c r="I58" t="n">
-        <v>1.34</v>
+        <v>4.5</v>
       </c>
       <c r="J58" t="n">
-        <v>6.4</v>
+        <v>3.8</v>
       </c>
       <c r="K58" t="n">
-        <v>22</v>
+        <v>4.3</v>
       </c>
       <c r="L58" t="n">
         <v>1.01</v>
       </c>
       <c r="M58" t="n">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N58" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="O58" t="n">
-        <v>1.11</v>
+        <v>1.21</v>
       </c>
       <c r="P58" t="n">
-        <v>1.68</v>
+        <v>2.1</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.32</v>
+        <v>1.56</v>
       </c>
       <c r="R58" t="n">
-        <v>1.68</v>
+        <v>1.25</v>
       </c>
       <c r="S58" t="n">
-        <v>1.87</v>
+        <v>1.56</v>
       </c>
       <c r="T58" t="n">
         <v>1.01</v>
@@ -11669,122 +11669,122 @@
         <v>1.01</v>
       </c>
       <c r="V58" t="n">
-        <v>3.9</v>
+        <v>1.3</v>
       </c>
       <c r="W58" t="n">
-        <v>1.01</v>
+        <v>1.88</v>
       </c>
       <c r="X58" t="n">
         <v>1000</v>
       </c>
       <c r="Y58" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z58" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA58" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AB58" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AC58" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AD58" t="n">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AE58" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF58" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AG58" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH58" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI58" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ58" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK58" t="n">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AL58" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM58" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN58" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AO58" t="n">
         <v>1000</v>
       </c>
       <c r="AP58" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="AQ58" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="AR58" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="AS58" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="AT58" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="AU58" t="n">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="AV58" t="n">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="AW58" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="AX58" t="n">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY58" t="n">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="AZ58" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="BA58" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="BB58" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BC58" t="n">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BD58" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BE58" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BF58" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BG58" t="n">
-        <v>1.01</v>
+        <v>2.48</v>
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -11854,7 +11854,7 @@
         <v>1.47</v>
       </c>
       <c r="S59" t="n">
-        <v>2.38</v>
+        <v>2.2</v>
       </c>
       <c r="T59" t="n">
         <v>1.43</v>
@@ -11920,10 +11920,10 @@
         <v>1000</v>
       </c>
       <c r="AO59" t="n">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AP59" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="AQ59" t="n">
         <v>7.4</v>
@@ -11947,7 +11947,7 @@
         <v>10</v>
       </c>
       <c r="AX59" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="AY59" t="n">
         <v>12</v>
@@ -11959,33 +11959,33 @@
         <v>16.5</v>
       </c>
       <c r="BB59" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="BC59" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="BD59" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="BE59" t="n">
-        <v>1.03</v>
+        <v>2.18</v>
       </c>
       <c r="BF59" t="n">
-        <v>1.01</v>
+        <v>2.18</v>
       </c>
       <c r="BG59" t="n">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Spanish Segunda Division</t>
+          <t>German Bundesliga</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -12000,186 +12000,186 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Albacete</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Eibar</t>
+          <t>Union Berlin</t>
         </is>
       </c>
       <c r="F60" t="n">
-        <v>3.15</v>
+        <v>1.38</v>
       </c>
       <c r="G60" t="n">
-        <v>3.5</v>
+        <v>1.39</v>
       </c>
       <c r="H60" t="n">
-        <v>2.48</v>
+        <v>9.6</v>
       </c>
       <c r="I60" t="n">
-        <v>2.64</v>
+        <v>10.5</v>
       </c>
       <c r="J60" t="n">
-        <v>3.15</v>
+        <v>5.7</v>
       </c>
       <c r="K60" t="n">
-        <v>3.35</v>
+        <v>5.8</v>
       </c>
       <c r="L60" t="n">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M60" t="n">
-        <v>1.1</v>
+        <v>1.03</v>
       </c>
       <c r="N60" t="n">
-        <v>2.96</v>
+        <v>6.2</v>
       </c>
       <c r="O60" t="n">
-        <v>1.44</v>
+        <v>1.17</v>
       </c>
       <c r="P60" t="n">
-        <v>1.64</v>
+        <v>2.76</v>
       </c>
       <c r="Q60" t="n">
-        <v>2.3</v>
+        <v>1.54</v>
       </c>
       <c r="R60" t="n">
-        <v>1.23</v>
+        <v>1.7</v>
       </c>
       <c r="S60" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W60" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="X60" t="n">
+        <v>28</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>40</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>90</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>310</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>24</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>100</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>12</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>32</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>110</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>120</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>24</v>
+      </c>
+      <c r="AQ60" t="n">
+        <v>23</v>
+      </c>
+      <c r="AR60" t="n">
+        <v>36</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>55</v>
+      </c>
+      <c r="AT60" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AU60" t="n">
+        <v>12</v>
+      </c>
+      <c r="AV60" t="n">
+        <v>30</v>
+      </c>
+      <c r="AW60" t="n">
+        <v>40</v>
+      </c>
+      <c r="AX60" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY60" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AZ60" t="n">
+        <v>21</v>
+      </c>
+      <c r="BA60" t="n">
+        <v>38</v>
+      </c>
+      <c r="BB60" t="n">
+        <v>11</v>
+      </c>
+      <c r="BC60" t="n">
+        <v>12</v>
+      </c>
+      <c r="BD60" t="n">
+        <v>26</v>
+      </c>
+      <c r="BE60" t="n">
+        <v>38</v>
+      </c>
+      <c r="BF60" t="n">
         <v>4.5</v>
       </c>
-      <c r="T60" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U60" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="V60" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="W60" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="X60" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>48</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE60" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>23</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH60" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI60" t="n">
-        <v>55</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK60" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL60" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM60" t="n">
-        <v>160</v>
-      </c>
-      <c r="AN60" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO60" t="n">
-        <v>40</v>
-      </c>
-      <c r="AP60" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AQ60" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AR60" t="n">
-        <v>13</v>
-      </c>
-      <c r="AS60" t="n">
-        <v>7</v>
-      </c>
-      <c r="AT60" t="n">
-        <v>9</v>
-      </c>
-      <c r="AU60" t="n">
-        <v>6</v>
-      </c>
-      <c r="AV60" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AW60" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AX60" t="n">
-        <v>18</v>
-      </c>
-      <c r="AY60" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ60" t="n">
-        <v>6</v>
-      </c>
-      <c r="BA60" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="BB60" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BC60" t="n">
-        <v>7</v>
-      </c>
-      <c r="BD60" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BE60" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="BF60" t="n">
-        <v>38</v>
-      </c>
       <c r="BG60" t="n">
-        <v>6.6</v>
+        <v>42</v>
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Polish I Liga</t>
+          <t>Polish Ekstraklasa</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -12194,31 +12194,31 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Wisla Krakow</t>
+          <t>Jagiellonia Bialystock</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Puszcza Niepolomice</t>
+          <t>Gornik Zabrze</t>
         </is>
       </c>
       <c r="F61" t="n">
-        <v>1.51</v>
+        <v>2.36</v>
       </c>
       <c r="G61" t="n">
-        <v>1.67</v>
+        <v>2.64</v>
       </c>
       <c r="H61" t="n">
-        <v>6.4</v>
+        <v>2.96</v>
       </c>
       <c r="I61" t="n">
-        <v>9</v>
+        <v>3.3</v>
       </c>
       <c r="J61" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="K61" t="n">
-        <v>4.9</v>
+        <v>3.85</v>
       </c>
       <c r="L61" t="n">
         <v>1.01</v>
@@ -12227,19 +12227,19 @@
         <v>1.01</v>
       </c>
       <c r="N61" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="O61" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P61" t="n">
-        <v>2.02</v>
+        <v>1.98</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.72</v>
+        <v>1.76</v>
       </c>
       <c r="R61" t="n">
-        <v>1.18</v>
+        <v>1.32</v>
       </c>
       <c r="S61" t="n">
         <v>2.72</v>
@@ -12251,10 +12251,10 @@
         <v>1.01</v>
       </c>
       <c r="V61" t="n">
-        <v>1.12</v>
+        <v>1.43</v>
       </c>
       <c r="W61" t="n">
-        <v>2.48</v>
+        <v>1.61</v>
       </c>
       <c r="X61" t="n">
         <v>1000</v>
@@ -12311,52 +12311,52 @@
         <v>1000</v>
       </c>
       <c r="AP61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AQ61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AR61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AS61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AT61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AU61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AV61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AW61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AX61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AY61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="AZ61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BA61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BB61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BC61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BD61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BE61" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="BF61" t="n">
         <v>1.01</v>
@@ -12366,14 +12366,14 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Austrian Erste Liga</t>
+          <t>Polish I Liga</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -12388,55 +12388,55 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Wisla Krakow</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>St Polten</t>
+          <t>Puszcza Niepolomice</t>
         </is>
       </c>
       <c r="F62" t="n">
-        <v>2.64</v>
+        <v>1.54</v>
       </c>
       <c r="G62" t="n">
-        <v>3</v>
+        <v>1.67</v>
       </c>
       <c r="H62" t="n">
-        <v>2.68</v>
+        <v>6.4</v>
       </c>
       <c r="I62" t="n">
-        <v>3.05</v>
+        <v>9</v>
       </c>
       <c r="J62" t="n">
-        <v>3.15</v>
+        <v>4.1</v>
       </c>
       <c r="K62" t="n">
-        <v>3.7</v>
+        <v>4.9</v>
       </c>
       <c r="L62" t="n">
-        <v>1.34</v>
+        <v>1.01</v>
       </c>
       <c r="M62" t="n">
-        <v>1.08</v>
+        <v>1.01</v>
       </c>
       <c r="N62" t="n">
-        <v>3.15</v>
+        <v>2.02</v>
       </c>
       <c r="O62" t="n">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="P62" t="n">
-        <v>1.76</v>
+        <v>2.02</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.04</v>
+        <v>1.72</v>
       </c>
       <c r="R62" t="n">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="S62" t="n">
-        <v>3.25</v>
+        <v>2.72</v>
       </c>
       <c r="T62" t="n">
         <v>1.01</v>
@@ -12445,43 +12445,43 @@
         <v>1.01</v>
       </c>
       <c r="V62" t="n">
-        <v>1.48</v>
+        <v>1.12</v>
       </c>
       <c r="W62" t="n">
-        <v>1.5</v>
+        <v>2.48</v>
       </c>
       <c r="X62" t="n">
         <v>1000</v>
       </c>
       <c r="Y62" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="Z62" t="n">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AA62" t="n">
         <v>1000</v>
       </c>
       <c r="AB62" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AC62" t="n">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AD62" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AE62" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AF62" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AG62" t="n">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AH62" t="n">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AI62" t="n">
         <v>1000</v>
@@ -12490,7 +12490,7 @@
         <v>1000</v>
       </c>
       <c r="AK62" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AL62" t="n">
         <v>1000</v>
@@ -12508,34 +12508,34 @@
         <v>1.03</v>
       </c>
       <c r="AQ62" t="n">
-        <v>7.2</v>
+        <v>1.03</v>
       </c>
       <c r="AR62" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AS62" t="n">
         <v>1.03</v>
       </c>
       <c r="AT62" t="n">
-        <v>6.8</v>
+        <v>1.03</v>
       </c>
       <c r="AU62" t="n">
-        <v>5.1</v>
+        <v>1.03</v>
       </c>
       <c r="AV62" t="n">
-        <v>8.4</v>
+        <v>1.03</v>
       </c>
       <c r="AW62" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AX62" t="n">
-        <v>12</v>
+        <v>1.03</v>
       </c>
       <c r="AY62" t="n">
-        <v>8</v>
+        <v>1.03</v>
       </c>
       <c r="AZ62" t="n">
-        <v>11.5</v>
+        <v>1.03</v>
       </c>
       <c r="BA62" t="n">
         <v>1.03</v>
@@ -12544,7 +12544,7 @@
         <v>1.03</v>
       </c>
       <c r="BC62" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD62" t="n">
         <v>1.03</v>
@@ -12560,14 +12560,14 @@
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>German Bundesliga</t>
+          <t>Spanish Segunda Division</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -12582,186 +12582,186 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Albacete</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Union Berlin</t>
+          <t>Eibar</t>
         </is>
       </c>
       <c r="F63" t="n">
-        <v>1.38</v>
+        <v>3.15</v>
       </c>
       <c r="G63" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="H63" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="I63" t="n">
+        <v>2.64</v>
+      </c>
+      <c r="J63" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K63" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="L63" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M63" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N63" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="O63" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="P63" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="Q63" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R63" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S63" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="T63" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="V63" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W63" t="n">
         <v>1.4</v>
       </c>
-      <c r="H63" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="I63" t="n">
+      <c r="X63" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="Y63" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="Z63" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AA63" t="n">
+        <v>48</v>
+      </c>
+      <c r="AB63" t="n">
+        <v>11</v>
+      </c>
+      <c r="AC63" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AD63" t="n">
+        <v>13</v>
+      </c>
+      <c r="AE63" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF63" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG63" t="n">
+        <v>15.5</v>
+      </c>
+      <c r="AH63" t="n">
+        <v>22</v>
+      </c>
+      <c r="AI63" t="n">
+        <v>55</v>
+      </c>
+      <c r="AJ63" t="n">
+        <v>65</v>
+      </c>
+      <c r="AK63" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL63" t="n">
+        <v>65</v>
+      </c>
+      <c r="AM63" t="n">
+        <v>160</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>65</v>
+      </c>
+      <c r="AO63" t="n">
+        <v>40</v>
+      </c>
+      <c r="AP63" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AQ63" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR63" t="n">
+        <v>13</v>
+      </c>
+      <c r="AS63" t="n">
+        <v>7</v>
+      </c>
+      <c r="AT63" t="n">
+        <v>9</v>
+      </c>
+      <c r="AU63" t="n">
+        <v>6</v>
+      </c>
+      <c r="AV63" t="n">
         <v>10.5</v>
       </c>
-      <c r="J63" t="n">
-        <v>5.7</v>
-      </c>
-      <c r="K63" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="L63" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="M63" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="N63" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="O63" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="P63" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="Q63" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="R63" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="S63" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="T63" t="n">
-        <v>1.86</v>
-      </c>
-      <c r="U63" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="V63" t="n">
-        <v>1.11</v>
-      </c>
-      <c r="W63" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="X63" t="n">
-        <v>28</v>
-      </c>
-      <c r="Y63" t="n">
-        <v>40</v>
-      </c>
-      <c r="Z63" t="n">
-        <v>90</v>
-      </c>
-      <c r="AA63" t="n">
-        <v>310</v>
-      </c>
-      <c r="AB63" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AC63" t="n">
-        <v>13</v>
-      </c>
-      <c r="AD63" t="n">
-        <v>36</v>
-      </c>
-      <c r="AE63" t="n">
-        <v>140</v>
-      </c>
-      <c r="AF63" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AG63" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AH63" t="n">
-        <v>24</v>
-      </c>
-      <c r="AI63" t="n">
-        <v>100</v>
-      </c>
-      <c r="AJ63" t="n">
-        <v>12</v>
-      </c>
-      <c r="AK63" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AL63" t="n">
-        <v>32</v>
-      </c>
-      <c r="AM63" t="n">
-        <v>110</v>
-      </c>
-      <c r="AN63" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="AO63" t="n">
-        <v>120</v>
-      </c>
-      <c r="AP63" t="n">
-        <v>24</v>
-      </c>
-      <c r="AQ63" t="n">
-        <v>34</v>
-      </c>
-      <c r="AR63" t="n">
-        <v>36</v>
-      </c>
-      <c r="AS63" t="n">
-        <v>55</v>
-      </c>
-      <c r="AT63" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AU63" t="n">
-        <v>12</v>
-      </c>
-      <c r="AV63" t="n">
-        <v>30</v>
-      </c>
       <c r="AW63" t="n">
-        <v>40</v>
+        <v>6.8</v>
       </c>
       <c r="AX63" t="n">
-        <v>8.800000000000001</v>
+        <v>18</v>
       </c>
       <c r="AY63" t="n">
-        <v>9.6</v>
+        <v>12.5</v>
       </c>
       <c r="AZ63" t="n">
-        <v>21</v>
+        <v>6</v>
       </c>
       <c r="BA63" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BB63" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BC63" t="n">
+        <v>7</v>
+      </c>
+      <c r="BD63" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE63" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BF63" t="n">
         <v>38</v>
       </c>
-      <c r="BB63" t="n">
-        <v>11</v>
-      </c>
-      <c r="BC63" t="n">
-        <v>12</v>
-      </c>
-      <c r="BD63" t="n">
-        <v>20</v>
-      </c>
-      <c r="BE63" t="n">
-        <v>38</v>
-      </c>
-      <c r="BF63" t="n">
-        <v>4.3</v>
-      </c>
       <c r="BG63" t="n">
-        <v>42</v>
+        <v>6.8</v>
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Polish Ekstraklasa</t>
+          <t>Austrian Erste Liga</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -12776,55 +12776,55 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Jagiellonia Bialystock</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Gornik Zabrze</t>
+          <t>St Polten</t>
         </is>
       </c>
       <c r="F64" t="n">
-        <v>2.36</v>
+        <v>2.64</v>
       </c>
       <c r="G64" t="n">
-        <v>2.66</v>
+        <v>3</v>
       </c>
       <c r="H64" t="n">
-        <v>2.96</v>
+        <v>2.68</v>
       </c>
       <c r="I64" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="J64" t="n">
-        <v>3.45</v>
+        <v>3.2</v>
       </c>
       <c r="K64" t="n">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L64" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M64" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N64" t="n">
-        <v>2</v>
+        <v>3.15</v>
       </c>
       <c r="O64" t="n">
-        <v>1.27</v>
+        <v>1.35</v>
       </c>
       <c r="P64" t="n">
-        <v>2</v>
+        <v>1.76</v>
       </c>
       <c r="Q64" t="n">
-        <v>1.84</v>
+        <v>2.04</v>
       </c>
       <c r="R64" t="n">
-        <v>1.32</v>
+        <v>1.29</v>
       </c>
       <c r="S64" t="n">
-        <v>2.72</v>
+        <v>3.7</v>
       </c>
       <c r="T64" t="n">
         <v>1.01</v>
@@ -12833,122 +12833,122 @@
         <v>1.01</v>
       </c>
       <c r="V64" t="n">
-        <v>1.43</v>
+        <v>1.48</v>
       </c>
       <c r="W64" t="n">
-        <v>1.61</v>
+        <v>1.5</v>
       </c>
       <c r="X64" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y64" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z64" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA64" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AB64" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC64" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD64" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE64" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF64" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG64" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH64" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI64" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ64" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AK64" t="n">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL64" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM64" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN64" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AO64" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP64" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AQ64" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AR64" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AS64" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AT64" t="n">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AU64" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV64" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AW64" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AX64" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="AY64" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AZ64" t="n">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BA64" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BB64" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BC64" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BD64" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BE64" t="n">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BF64" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BG64" t="n">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -12982,7 +12982,7 @@
         <v>1.61</v>
       </c>
       <c r="G65" t="n">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="H65" t="n">
         <v>6</v>
@@ -12994,13 +12994,13 @@
         <v>4</v>
       </c>
       <c r="K65" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L65" t="n">
         <v>1.01</v>
       </c>
       <c r="M65" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N65" t="n">
         <v>1.92</v>
@@ -13021,7 +13021,7 @@
         <v>2.8</v>
       </c>
       <c r="T65" t="n">
-        <v>1.69</v>
+        <v>1.01</v>
       </c>
       <c r="U65" t="n">
         <v>1.69</v>
@@ -13030,10 +13030,10 @@
         <v>1.17</v>
       </c>
       <c r="W65" t="n">
-        <v>2.52</v>
+        <v>2.42</v>
       </c>
       <c r="X65" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="Y65" t="n">
         <v>26</v>
@@ -13081,22 +13081,22 @@
         <v>1000</v>
       </c>
       <c r="AN65" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AO65" t="n">
         <v>1000</v>
       </c>
       <c r="AP65" t="n">
-        <v>1.03</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AQ65" t="n">
         <v>12</v>
       </c>
       <c r="AR65" t="n">
-        <v>1.03</v>
+        <v>2.66</v>
       </c>
       <c r="AS65" t="n">
-        <v>1.03</v>
+        <v>2.66</v>
       </c>
       <c r="AT65" t="n">
         <v>5.6</v>
@@ -13105,22 +13105,22 @@
         <v>6.2</v>
       </c>
       <c r="AV65" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW65" t="n">
-        <v>1.03</v>
+        <v>2.66</v>
       </c>
       <c r="AX65" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AY65" t="n">
         <v>7</v>
       </c>
       <c r="AZ65" t="n">
-        <v>1.03</v>
+        <v>14</v>
       </c>
       <c r="BA65" t="n">
-        <v>1.03</v>
+        <v>2.66</v>
       </c>
       <c r="BB65" t="n">
         <v>9.6</v>
@@ -13129,27 +13129,27 @@
         <v>12</v>
       </c>
       <c r="BD65" t="n">
-        <v>1.03</v>
+        <v>2.66</v>
       </c>
       <c r="BE65" t="n">
-        <v>1.03</v>
+        <v>2.66</v>
       </c>
       <c r="BF65" t="n">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BG65" t="n">
-        <v>1.01</v>
+        <v>2.66</v>
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Italian Serie A</t>
+          <t>Irish Premier Division</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -13164,186 +13164,186 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>St Patricks</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>US Cremonese</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F66" t="n">
-        <v>1.36</v>
+        <v>2.14</v>
       </c>
       <c r="G66" t="n">
-        <v>1.37</v>
+        <v>2.42</v>
       </c>
       <c r="H66" t="n">
-        <v>11.5</v>
+        <v>3.65</v>
       </c>
       <c r="I66" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J66" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="K66" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L66" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="M66" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="N66" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="O66" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="P66" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Q66" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="R66" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S66" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="U66" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="V66" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="W66" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="X66" t="n">
+        <v>12</v>
+      </c>
+      <c r="Y66" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="Z66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB66" t="n">
+        <v>9</v>
+      </c>
+      <c r="AC66" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AD66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG66" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AH66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO66" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP66" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AQ66" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR66" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AS66" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AT66" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AU66" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AV66" t="n">
         <v>12.5</v>
       </c>
-      <c r="J66" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="K66" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="L66" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M66" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N66" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="O66" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="P66" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="Q66" t="n">
-        <v>1.97</v>
-      </c>
-      <c r="R66" t="n">
-        <v>1.37</v>
-      </c>
-      <c r="S66" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T66" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="U66" t="n">
-        <v>1.64</v>
-      </c>
-      <c r="V66" t="n">
-        <v>1.08</v>
-      </c>
-      <c r="W66" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="X66" t="n">
-        <v>16</v>
-      </c>
-      <c r="Y66" t="n">
-        <v>32</v>
-      </c>
-      <c r="Z66" t="n">
-        <v>120</v>
-      </c>
-      <c r="AA66" t="n">
-        <v>690</v>
-      </c>
-      <c r="AB66" t="n">
-        <v>7</v>
-      </c>
-      <c r="AC66" t="n">
-        <v>12</v>
-      </c>
-      <c r="AD66" t="n">
-        <v>46</v>
-      </c>
-      <c r="AE66" t="n">
-        <v>280</v>
-      </c>
-      <c r="AF66" t="n">
-        <v>7</v>
-      </c>
-      <c r="AG66" t="n">
-        <v>11</v>
-      </c>
-      <c r="AH66" t="n">
-        <v>38</v>
-      </c>
-      <c r="AI66" t="n">
-        <v>240</v>
-      </c>
-      <c r="AJ66" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AK66" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AL66" t="n">
-        <v>55</v>
-      </c>
-      <c r="AM66" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN66" t="n">
-        <v>7</v>
-      </c>
-      <c r="AO66" t="n">
-        <v>480</v>
-      </c>
-      <c r="AP66" t="n">
-        <v>14</v>
-      </c>
-      <c r="AQ66" t="n">
-        <v>25</v>
-      </c>
-      <c r="AR66" t="n">
-        <v>38</v>
-      </c>
-      <c r="AS66" t="n">
-        <v>110</v>
-      </c>
-      <c r="AT66" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU66" t="n">
-        <v>11</v>
-      </c>
-      <c r="AV66" t="n">
-        <v>26</v>
-      </c>
       <c r="AW66" t="n">
-        <v>48</v>
+        <v>4.7</v>
       </c>
       <c r="AX66" t="n">
-        <v>6.4</v>
+        <v>10</v>
       </c>
       <c r="AY66" t="n">
-        <v>10</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ66" t="n">
-        <v>32</v>
+        <v>4.2</v>
       </c>
       <c r="BA66" t="n">
-        <v>48</v>
+        <v>4.7</v>
       </c>
       <c r="BB66" t="n">
-        <v>9.4</v>
+        <v>4.4</v>
       </c>
       <c r="BC66" t="n">
-        <v>15</v>
+        <v>4.4</v>
       </c>
       <c r="BD66" t="n">
-        <v>29</v>
+        <v>4.6</v>
       </c>
       <c r="BE66" t="n">
-        <v>55</v>
+        <v>4.9</v>
       </c>
       <c r="BF66" t="n">
-        <v>6.4</v>
+        <v>4.3</v>
       </c>
       <c r="BG66" t="n">
-        <v>55</v>
+        <v>4.7</v>
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Irish Premier Division</t>
+          <t>Italian Serie A</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -13358,179 +13358,179 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Drogheda</t>
+          <t>US Cremonese</t>
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1.73</v>
+        <v>1.36</v>
       </c>
       <c r="G67" t="n">
-        <v>1.81</v>
+        <v>1.38</v>
       </c>
       <c r="H67" t="n">
-        <v>5.6</v>
+        <v>11.5</v>
       </c>
       <c r="I67" t="n">
-        <v>6.4</v>
+        <v>12.5</v>
       </c>
       <c r="J67" t="n">
-        <v>3.6</v>
+        <v>5.4</v>
       </c>
       <c r="K67" t="n">
-        <v>3.9</v>
+        <v>5.5</v>
       </c>
       <c r="L67" t="n">
-        <v>1.47</v>
+        <v>1.4</v>
       </c>
       <c r="M67" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="N67" t="n">
+        <v>4</v>
+      </c>
+      <c r="O67" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P67" t="n">
+        <v>2</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R67" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="S67" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="V67" t="n">
         <v>1.08</v>
       </c>
-      <c r="N67" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="O67" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="P67" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="Q67" t="n">
-        <v>2.18</v>
-      </c>
-      <c r="R67" t="n">
-        <v>1.27</v>
-      </c>
-      <c r="S67" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="T67" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U67" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="V67" t="n">
-        <v>1.18</v>
-      </c>
       <c r="W67" t="n">
-        <v>2.22</v>
+        <v>3.65</v>
       </c>
       <c r="X67" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="Y67" t="n">
-        <v>20</v>
+        <v>32</v>
       </c>
       <c r="Z67" t="n">
-        <v>60</v>
+        <v>120</v>
       </c>
       <c r="AA67" t="n">
+        <v>660</v>
+      </c>
+      <c r="AB67" t="n">
+        <v>7</v>
+      </c>
+      <c r="AC67" t="n">
+        <v>12</v>
+      </c>
+      <c r="AD67" t="n">
+        <v>46</v>
+      </c>
+      <c r="AE67" t="n">
+        <v>280</v>
+      </c>
+      <c r="AF67" t="n">
+        <v>7</v>
+      </c>
+      <c r="AG67" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH67" t="n">
+        <v>38</v>
+      </c>
+      <c r="AI67" t="n">
         <v>220</v>
       </c>
-      <c r="AB67" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AC67" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD67" t="n">
-        <v>29</v>
-      </c>
-      <c r="AE67" t="n">
-        <v>120</v>
-      </c>
-      <c r="AF67" t="n">
-        <v>12</v>
-      </c>
-      <c r="AG67" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH67" t="n">
-        <v>29</v>
-      </c>
-      <c r="AI67" t="n">
-        <v>130</v>
-      </c>
       <c r="AJ67" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="AK67" t="n">
-        <v>26</v>
+        <v>16.5</v>
       </c>
       <c r="AL67" t="n">
         <v>55</v>
       </c>
       <c r="AM67" t="n">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AN67" t="n">
-        <v>17.5</v>
+        <v>7</v>
       </c>
       <c r="AO67" t="n">
-        <v>180</v>
+        <v>460</v>
       </c>
       <c r="AP67" t="n">
+        <v>15</v>
+      </c>
+      <c r="AQ67" t="n">
+        <v>25</v>
+      </c>
+      <c r="AR67" t="n">
+        <v>38</v>
+      </c>
+      <c r="AS67" t="n">
+        <v>110</v>
+      </c>
+      <c r="AT67" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU67" t="n">
+        <v>11</v>
+      </c>
+      <c r="AV67" t="n">
+        <v>26</v>
+      </c>
+      <c r="AW67" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX67" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY67" t="n">
         <v>10</v>
       </c>
-      <c r="AQ67" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR67" t="n">
-        <v>4</v>
-      </c>
-      <c r="AS67" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AT67" t="n">
+      <c r="AZ67" t="n">
+        <v>32</v>
+      </c>
+      <c r="BA67" t="n">
+        <v>48</v>
+      </c>
+      <c r="BB67" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="BC67" t="n">
+        <v>15</v>
+      </c>
+      <c r="BD67" t="n">
+        <v>44</v>
+      </c>
+      <c r="BE67" t="n">
+        <v>55</v>
+      </c>
+      <c r="BF67" t="n">
         <v>6.4</v>
       </c>
-      <c r="AU67" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV67" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW67" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AX67" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AY67" t="n">
-        <v>9</v>
-      </c>
-      <c r="AZ67" t="n">
-        <v>20</v>
-      </c>
-      <c r="BA67" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BB67" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="BC67" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="BD67" t="n">
-        <v>4</v>
-      </c>
-      <c r="BE67" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="BF67" t="n">
-        <v>10.5</v>
-      </c>
       <c r="BG67" t="n">
-        <v>4.2</v>
+        <v>55</v>
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -13552,179 +13552,179 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>St Patricks</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Drogheda</t>
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2.14</v>
+        <v>1.73</v>
       </c>
       <c r="G68" t="n">
-        <v>2.42</v>
+        <v>1.81</v>
       </c>
       <c r="H68" t="n">
-        <v>3.65</v>
+        <v>5.6</v>
       </c>
       <c r="I68" t="n">
-        <v>4.4</v>
+        <v>6.4</v>
       </c>
       <c r="J68" t="n">
-        <v>3.1</v>
+        <v>3.6</v>
       </c>
       <c r="K68" t="n">
-        <v>3.55</v>
+        <v>3.9</v>
       </c>
       <c r="L68" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="M68" t="n">
-        <v>1.1</v>
+        <v>1.08</v>
       </c>
       <c r="N68" t="n">
-        <v>2.72</v>
+        <v>3.15</v>
       </c>
       <c r="O68" t="n">
-        <v>1.45</v>
+        <v>1.4</v>
       </c>
       <c r="P68" t="n">
-        <v>1.61</v>
+        <v>1.74</v>
       </c>
       <c r="Q68" t="n">
-        <v>2.28</v>
+        <v>2.18</v>
       </c>
       <c r="R68" t="n">
-        <v>1.22</v>
+        <v>1.27</v>
       </c>
       <c r="S68" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="V68" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="W68" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="X68" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y68" t="n">
+        <v>20</v>
+      </c>
+      <c r="Z68" t="n">
+        <v>60</v>
+      </c>
+      <c r="AA68" t="n">
+        <v>220</v>
+      </c>
+      <c r="AB68" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AC68" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AD68" t="n">
+        <v>29</v>
+      </c>
+      <c r="AE68" t="n">
+        <v>120</v>
+      </c>
+      <c r="AF68" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG68" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AH68" t="n">
+        <v>29</v>
+      </c>
+      <c r="AI68" t="n">
+        <v>130</v>
+      </c>
+      <c r="AJ68" t="n">
+        <v>23</v>
+      </c>
+      <c r="AK68" t="n">
+        <v>26</v>
+      </c>
+      <c r="AL68" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM68" t="n">
+        <v>200</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AO68" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP68" t="n">
+        <v>10</v>
+      </c>
+      <c r="AQ68" t="n">
+        <v>12</v>
+      </c>
+      <c r="AR68" t="n">
+        <v>4</v>
+      </c>
+      <c r="AS68" t="n">
         <v>4.2</v>
       </c>
-      <c r="T68" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="U68" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="V68" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="W68" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="X68" t="n">
-        <v>12</v>
-      </c>
-      <c r="Y68" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="Z68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB68" t="n">
+      <c r="AT68" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AU68" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV68" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW68" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AX68" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AY68" t="n">
         <v>9</v>
       </c>
-      <c r="AC68" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="AD68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG68" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO68" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP68" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="AQ68" t="n">
-        <v>9</v>
-      </c>
-      <c r="AR68" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="AS68" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="AT68" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU68" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AV68" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW68" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AX68" t="n">
-        <v>10</v>
-      </c>
-      <c r="AY68" t="n">
-        <v>3.65</v>
-      </c>
       <c r="AZ68" t="n">
+        <v>20</v>
+      </c>
+      <c r="BA68" t="n">
         <v>4.2</v>
       </c>
-      <c r="BA68" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BB68" t="n">
-        <v>4.4</v>
+        <v>16.5</v>
       </c>
       <c r="BC68" t="n">
-        <v>4.4</v>
+        <v>18.5</v>
       </c>
       <c r="BD68" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="BE68" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="BF68" t="n">
-        <v>4.3</v>
+        <v>10.5</v>
       </c>
       <c r="BG68" t="n">
-        <v>4.7</v>
+        <v>4.2</v>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -13758,7 +13758,7 @@
         <v>3.2</v>
       </c>
       <c r="G69" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="H69" t="n">
         <v>2.28</v>
@@ -13773,7 +13773,7 @@
         <v>3.75</v>
       </c>
       <c r="L69" t="n">
-        <v>1.41</v>
+        <v>1.34</v>
       </c>
       <c r="M69" t="n">
         <v>1.07</v>
@@ -13806,7 +13806,7 @@
         <v>1.67</v>
       </c>
       <c r="W69" t="n">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="X69" t="n">
         <v>1000</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -13952,7 +13952,7 @@
         <v>2.48</v>
       </c>
       <c r="G70" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="H70" t="n">
         <v>2.56</v>
@@ -13967,7 +13967,7 @@
         <v>4.1</v>
       </c>
       <c r="L70" t="n">
-        <v>1.38</v>
+        <v>1.41</v>
       </c>
       <c r="M70" t="n">
         <v>1.07</v>
@@ -13988,7 +13988,7 @@
         <v>1.31</v>
       </c>
       <c r="S70" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="T70" t="n">
         <v>1.75</v>
@@ -14000,7 +14000,7 @@
         <v>1.46</v>
       </c>
       <c r="W70" t="n">
-        <v>1.47</v>
+        <v>1.45</v>
       </c>
       <c r="X70" t="n">
         <v>1000</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -14146,7 +14146,7 @@
         <v>3.35</v>
       </c>
       <c r="G71" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="H71" t="n">
         <v>2.26</v>
@@ -14173,10 +14173,10 @@
         <v>1.4</v>
       </c>
       <c r="P71" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q71" t="n">
-        <v>1.96</v>
+        <v>2.14</v>
       </c>
       <c r="R71" t="n">
         <v>1.28</v>
@@ -14191,7 +14191,7 @@
         <v>1.98</v>
       </c>
       <c r="V71" t="n">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="W71" t="n">
         <v>1.36</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -14531,25 +14531,25 @@
         </is>
       </c>
       <c r="F73" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="G73" t="n">
         <v>5.3</v>
       </c>
-      <c r="G73" t="n">
-        <v>5.5</v>
-      </c>
       <c r="H73" t="n">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="I73" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="J73" t="n">
         <v>4.2</v>
       </c>
       <c r="K73" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L73" t="n">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M73" t="n">
         <v>1.05</v>
@@ -14561,28 +14561,28 @@
         <v>1.25</v>
       </c>
       <c r="P73" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="Q73" t="n">
         <v>1.73</v>
       </c>
       <c r="R73" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="S73" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="T73" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="U73" t="n">
         <v>2.24</v>
       </c>
       <c r="V73" t="n">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="W73" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X73" t="n">
         <v>21</v>
@@ -14597,7 +14597,7 @@
         <v>18</v>
       </c>
       <c r="AB73" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC73" t="n">
         <v>9.4</v>
@@ -14618,7 +14618,7 @@
         <v>18</v>
       </c>
       <c r="AI73" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AJ73" t="n">
         <v>130</v>
@@ -14630,7 +14630,7 @@
         <v>65</v>
       </c>
       <c r="AM73" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AN73" t="n">
         <v>60</v>
@@ -14648,7 +14648,7 @@
         <v>10.5</v>
       </c>
       <c r="AS73" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AT73" t="n">
         <v>20</v>
@@ -14657,7 +14657,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AV73" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW73" t="n">
         <v>15.5</v>
@@ -14675,7 +14675,7 @@
         <v>27</v>
       </c>
       <c r="BB73" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="BC73" t="n">
         <v>50</v>
@@ -14684,7 +14684,7 @@
         <v>50</v>
       </c>
       <c r="BE73" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BF73" t="n">
         <v>46</v>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -14725,10 +14725,10 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G74" t="n">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="H74" t="n">
         <v>3.1</v>
@@ -14767,10 +14767,10 @@
         <v>3.55</v>
       </c>
       <c r="T74" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="U74" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="V74" t="n">
         <v>1.37</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -14949,7 +14949,7 @@
         <v>1.41</v>
       </c>
       <c r="P75" t="n">
-        <v>1.79</v>
+        <v>1.78</v>
       </c>
       <c r="Q75" t="n">
         <v>2.22</v>
@@ -14976,7 +14976,7 @@
         <v>11</v>
       </c>
       <c r="Y75" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="Z75" t="n">
         <v>17</v>
@@ -14985,10 +14985,10 @@
         <v>44</v>
       </c>
       <c r="AB75" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC75" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD75" t="n">
         <v>12.5</v>
@@ -14997,7 +14997,7 @@
         <v>34</v>
       </c>
       <c r="AF75" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AG75" t="n">
         <v>12.5</v>
@@ -15006,7 +15006,7 @@
         <v>18</v>
       </c>
       <c r="AI75" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AJ75" t="n">
         <v>44</v>
@@ -15027,22 +15027,22 @@
         <v>34</v>
       </c>
       <c r="AP75" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AQ75" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR75" t="n">
         <v>16.5</v>
       </c>
       <c r="AS75" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AT75" t="n">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="AU75" t="n">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AV75" t="n">
         <v>12</v>
@@ -15051,16 +15051,16 @@
         <v>32</v>
       </c>
       <c r="AX75" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AY75" t="n">
         <v>12</v>
       </c>
       <c r="AZ75" t="n">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="BA75" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BB75" t="n">
         <v>40</v>
@@ -15069,20 +15069,20 @@
         <v>30</v>
       </c>
       <c r="BD75" t="n">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BE75" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="BF75" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BG75" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -15116,13 +15116,13 @@
         <v>3.3</v>
       </c>
       <c r="G76" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="H76" t="n">
         <v>2.36</v>
       </c>
       <c r="I76" t="n">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="J76" t="n">
         <v>3.1</v>
@@ -15221,7 +15221,7 @@
         <v>38</v>
       </c>
       <c r="AP76" t="n">
-        <v>3.2</v>
+        <v>7.6</v>
       </c>
       <c r="AQ76" t="n">
         <v>6.4</v>
@@ -15239,7 +15239,7 @@
         <v>5.5</v>
       </c>
       <c r="AV76" t="n">
-        <v>3.3</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW76" t="n">
         <v>3.85</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -15501,10 +15501,10 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="G78" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="H78" t="n">
         <v>1.93</v>
@@ -15531,10 +15531,10 @@
         <v>0</v>
       </c>
       <c r="P78" t="n">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R78" t="n">
         <v>0</v>
@@ -15543,10 +15543,10 @@
         <v>0</v>
       </c>
       <c r="T78" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="U78" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="V78" t="n">
         <v>0</v>
@@ -15576,7 +15576,7 @@
         <v>10.5</v>
       </c>
       <c r="AE78" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="AF78" t="n">
         <v>34</v>
@@ -15660,11 +15660,11 @@
         <v>19</v>
       </c>
       <c r="BG78" t="n">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -15698,7 +15698,7 @@
         <v>2.32</v>
       </c>
       <c r="G79" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="H79" t="n">
         <v>3.25</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -15898,7 +15898,7 @@
         <v>2.22</v>
       </c>
       <c r="I80" t="n">
-        <v>2.6</v>
+        <v>2.48</v>
       </c>
       <c r="J80" t="n">
         <v>2.78</v>
@@ -15907,19 +15907,19 @@
         <v>3.05</v>
       </c>
       <c r="L80" t="n">
-        <v>1.7</v>
+        <v>1.01</v>
       </c>
       <c r="M80" t="n">
-        <v>1.12</v>
+        <v>1.17</v>
       </c>
       <c r="N80" t="n">
-        <v>1.39</v>
+        <v>2.12</v>
       </c>
       <c r="O80" t="n">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="P80" t="n">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="Q80" t="n">
         <v>3.3</v>
@@ -15928,138 +15928,138 @@
         <v>1.12</v>
       </c>
       <c r="S80" t="n">
-        <v>6</v>
+        <v>7.6</v>
       </c>
       <c r="T80" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="U80" t="n">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="V80" t="n">
-        <v>1.63</v>
+        <v>1.68</v>
       </c>
       <c r="W80" t="n">
         <v>1.28</v>
       </c>
       <c r="X80" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="Y80" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="Z80" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AA80" t="n">
+        <v>40</v>
+      </c>
+      <c r="AB80" t="n">
+        <v>10</v>
+      </c>
+      <c r="AC80" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AD80" t="n">
+        <v>14</v>
+      </c>
+      <c r="AE80" t="n">
+        <v>46</v>
+      </c>
+      <c r="AF80" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG80" t="n">
+        <v>22</v>
+      </c>
+      <c r="AH80" t="n">
+        <v>34</v>
+      </c>
+      <c r="AI80" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ80" t="n">
+        <v>150</v>
+      </c>
+      <c r="AK80" t="n">
+        <v>120</v>
+      </c>
+      <c r="AL80" t="n">
+        <v>170</v>
+      </c>
+      <c r="AM80" t="n">
+        <v>420</v>
+      </c>
+      <c r="AN80" t="n">
+        <v>210</v>
+      </c>
+      <c r="AO80" t="n">
+        <v>55</v>
+      </c>
+      <c r="AP80" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="AQ80" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AR80" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AS80" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT80" t="n">
+        <v>8</v>
+      </c>
+      <c r="AU80" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV80" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AW80" t="n">
         <v>7.6</v>
       </c>
-      <c r="Y80" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="Z80" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AA80" t="n">
-        <v>46</v>
-      </c>
-      <c r="AB80" t="n">
-        <v>11</v>
-      </c>
-      <c r="AC80" t="n">
+      <c r="AX80" t="n">
+        <v>7</v>
+      </c>
+      <c r="AY80" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AZ80" t="n">
+        <v>7</v>
+      </c>
+      <c r="BA80" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BB80" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BC80" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BD80" t="n">
         <v>8.6</v>
       </c>
-      <c r="AD80" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AE80" t="n">
-        <v>50</v>
-      </c>
-      <c r="AF80" t="n">
-        <v>34</v>
-      </c>
-      <c r="AG80" t="n">
-        <v>25</v>
-      </c>
-      <c r="AH80" t="n">
+      <c r="BE80" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BF80" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BG80" t="n">
         <v>38</v>
       </c>
-      <c r="AI80" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ80" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK80" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL80" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM80" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN80" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO80" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP80" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AQ80" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AR80" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AS80" t="n">
-        <v>26</v>
-      </c>
-      <c r="AT80" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="AU80" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AV80" t="n">
-        <v>10</v>
-      </c>
-      <c r="AW80" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="AX80" t="n">
-        <v>19</v>
-      </c>
-      <c r="AY80" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ80" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="BA80" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BB80" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BC80" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BD80" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BE80" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BF80" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BG80" t="n">
-        <v>3.8</v>
-      </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Paraguayan Primera Division</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -16069,191 +16069,191 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>17:45:00</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>Nacional (Par)</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>Deportivo Recoleta</t>
         </is>
       </c>
       <c r="F81" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="G81" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>2.38</v>
+        <v>0</v>
       </c>
       <c r="I81" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="J81" t="n">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="K81" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="L81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N81" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="O81" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P81" t="n">
-        <v>1.85</v>
+        <v>1.24</v>
       </c>
       <c r="Q81" t="n">
-        <v>1.97</v>
+        <v>1.33</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S81" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="T81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO81" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG81" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Colombian Primera A</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -16263,191 +16263,191 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>18:00:00</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Cucuta Deportivo</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Junior FC Barranquilla</t>
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3.75</v>
+        <v>3</v>
       </c>
       <c r="G82" t="n">
-        <v>4.7</v>
+        <v>3.65</v>
       </c>
       <c r="H82" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="I82" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="J82" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K82" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M82" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N82" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="O82" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="P82" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q82" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="R82" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="S82" t="n">
+        <v>3</v>
+      </c>
+      <c r="T82" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="U82" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="V82" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W82" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="X82" t="n">
+        <v>20</v>
+      </c>
+      <c r="Y82" t="n">
+        <v>15</v>
+      </c>
+      <c r="Z82" t="n">
+        <v>24</v>
+      </c>
+      <c r="AA82" t="n">
+        <v>50</v>
+      </c>
+      <c r="AB82" t="n">
+        <v>18</v>
+      </c>
+      <c r="AC82" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD82" t="n">
+        <v>17.5</v>
+      </c>
+      <c r="AE82" t="n">
+        <v>40</v>
+      </c>
+      <c r="AF82" t="n">
+        <v>32</v>
+      </c>
+      <c r="AG82" t="n">
+        <v>20</v>
+      </c>
+      <c r="AH82" t="n">
+        <v>25</v>
+      </c>
+      <c r="AI82" t="n">
+        <v>60</v>
+      </c>
+      <c r="AJ82" t="n">
+        <v>85</v>
+      </c>
+      <c r="AK82" t="n">
+        <v>55</v>
+      </c>
+      <c r="AL82" t="n">
+        <v>70</v>
+      </c>
+      <c r="AM82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO82" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP82" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AQ82" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AR82" t="n">
+        <v>11</v>
+      </c>
+      <c r="AS82" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AT82" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AU82" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV82" t="n">
         <v>2.14</v>
       </c>
-      <c r="I82" t="n">
+      <c r="AW82" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AX82" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="AY82" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AZ82" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="BA82" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="BB82" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="BC82" t="n">
         <v>2.34</v>
       </c>
-      <c r="J82" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="K82" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="L82" t="n">
-        <v>0</v>
-      </c>
-      <c r="M82" t="n">
-        <v>0</v>
-      </c>
-      <c r="N82" t="n">
-        <v>0</v>
-      </c>
-      <c r="O82" t="n">
-        <v>0</v>
-      </c>
-      <c r="P82" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="Q82" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="R82" t="n">
-        <v>0</v>
-      </c>
-      <c r="S82" t="n">
-        <v>0</v>
-      </c>
-      <c r="T82" t="n">
-        <v>0</v>
-      </c>
-      <c r="U82" t="n">
-        <v>0</v>
-      </c>
-      <c r="V82" t="n">
-        <v>0</v>
-      </c>
-      <c r="W82" t="n">
-        <v>0</v>
-      </c>
-      <c r="X82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y82" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY82" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB82" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC82" t="n">
-        <v>0</v>
-      </c>
       <c r="BD82" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="BE82" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BF82" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BG82" t="n">
-        <v>0</v>
+        <v>2.44</v>
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -16457,184 +16457,184 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>19:00:00</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>Union La Calera</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Central Cordoba (SdE)</t>
+          <t>Coquimbo Unido</t>
         </is>
       </c>
       <c r="F83" t="n">
-        <v>1.53</v>
+        <v>3.75</v>
       </c>
       <c r="G83" t="n">
-        <v>1.59</v>
+        <v>4.7</v>
       </c>
       <c r="H83" t="n">
-        <v>8.199999999999999</v>
+        <v>2.14</v>
       </c>
       <c r="I83" t="n">
-        <v>10.5</v>
+        <v>2.34</v>
       </c>
       <c r="J83" t="n">
-        <v>3.85</v>
+        <v>3.15</v>
       </c>
       <c r="K83" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="L83" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M83" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="O83" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="P83" t="n">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="Q83" t="n">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AG83" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AH83" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="AI83" t="n">
-        <v>0</v>
+        <v>70</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK83" t="n">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AL83" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO83" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP83" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="AR83" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AS83" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AT83" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AU83" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AV83" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AW83" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AX83" t="n">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AY83" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AZ83" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BA83" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BB83" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BC83" t="n">
-        <v>0</v>
+        <v>2.62</v>
       </c>
       <c r="BD83" t="n">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="BE83" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BF83" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BG83" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
@@ -16683,16 +16683,16 @@
         <v>3.55</v>
       </c>
       <c r="L84" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="N84" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="O84" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="P84" t="n">
         <v>1.52</v>
@@ -16701,328 +16701,910 @@
         <v>2.68</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="T84" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U84" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V84" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W84" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X84" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AB84" t="n">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AD84" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AG84" t="n">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AH84" t="n">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AI84" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="AJ84" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK84" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL84" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM84" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN84" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO84" t="n">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP84" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="AR84" t="n">
-        <v>0</v>
+        <v>2.86</v>
       </c>
       <c r="AS84" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AT84" t="n">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AU84" t="n">
-        <v>0</v>
+        <v>2.68</v>
       </c>
       <c r="AV84" t="n">
-        <v>0</v>
+        <v>2.94</v>
       </c>
       <c r="AW84" t="n">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="AX84" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AY84" t="n">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="AZ84" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BA84" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="BB84" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BC84" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BD84" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE84" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BF84" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BG84" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-22 17:35:15</t>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
+          <t>Argentinian Primera Division</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>19:15:00</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>Lanus</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Central Cordoba (SdE)</t>
+        </is>
+      </c>
+      <c r="F85" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="G85" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="H85" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I85" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="J85" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="K85" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L85" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M85" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N85" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="O85" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="P85" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="Q85" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="R85" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="S85" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="T85" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U85" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V85" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W85" t="n">
+        <v>2.68</v>
+      </c>
+      <c r="X85" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y85" t="n">
+        <v>29</v>
+      </c>
+      <c r="Z85" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA85" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB85" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AC85" t="n">
+        <v>13</v>
+      </c>
+      <c r="AD85" t="n">
+        <v>50</v>
+      </c>
+      <c r="AE85" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF85" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AG85" t="n">
+        <v>15</v>
+      </c>
+      <c r="AH85" t="n">
+        <v>48</v>
+      </c>
+      <c r="AI85" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ85" t="n">
+        <v>19</v>
+      </c>
+      <c r="AK85" t="n">
+        <v>30</v>
+      </c>
+      <c r="AL85" t="n">
+        <v>85</v>
+      </c>
+      <c r="AM85" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN85" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO85" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP85" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AQ85" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="AR85" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AS85" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AT85" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="AU85" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AV85" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AW85" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AX85" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AY85" t="n">
+        <v>2.18</v>
+      </c>
+      <c r="AZ85" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="BA85" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BB85" t="n">
+        <v>10</v>
+      </c>
+      <c r="BC85" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="BD85" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="BE85" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BF85" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BG85" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="BH85" t="inlineStr">
+        <is>
+          <t>2026-04-22 19:53:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Uruguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>19:30:00</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Torque</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Boston River</t>
+        </is>
+      </c>
+      <c r="F86" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="G86" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="H86" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="I86" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="J86" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K86" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="L86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N86" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="O86" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="P86" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="R86" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="S86" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="T86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V86" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="W86" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="X86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO86" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG86" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH86" t="inlineStr">
+        <is>
+          <t>2026-04-22 19:53:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
           <t>Brazilian Serie B</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B87" t="inlineStr">
         <is>
           <t>2026-04-24</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>20:00:00</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>Ponte Preta</t>
         </is>
       </c>
-      <c r="E85" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>America MG</t>
         </is>
       </c>
-      <c r="F85" t="n">
+      <c r="F87" t="n">
         <v>2.8</v>
       </c>
-      <c r="G85" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="H85" t="n">
+      <c r="G87" t="n">
+        <v>3</v>
+      </c>
+      <c r="H87" t="n">
         <v>2.8</v>
       </c>
-      <c r="I85" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="J85" t="n">
-        <v>2.96</v>
-      </c>
-      <c r="K85" t="n">
+      <c r="I87" t="n">
+        <v>3</v>
+      </c>
+      <c r="J87" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K87" t="n">
         <v>3.35</v>
       </c>
-      <c r="L85" t="n">
-        <v>0</v>
-      </c>
-      <c r="M85" t="n">
-        <v>0</v>
-      </c>
-      <c r="N85" t="n">
-        <v>0</v>
-      </c>
-      <c r="O85" t="n">
-        <v>0</v>
-      </c>
-      <c r="P85" t="n">
+      <c r="L87" t="n">
+        <v>0</v>
+      </c>
+      <c r="M87" t="n">
+        <v>0</v>
+      </c>
+      <c r="N87" t="n">
+        <v>0</v>
+      </c>
+      <c r="O87" t="n">
+        <v>0</v>
+      </c>
+      <c r="P87" t="n">
         <v>1.68</v>
       </c>
-      <c r="Q85" t="n">
+      <c r="Q87" t="n">
         <v>2.28</v>
       </c>
-      <c r="R85" t="n">
-        <v>0</v>
-      </c>
-      <c r="S85" t="n">
-        <v>0</v>
-      </c>
-      <c r="T85" t="n">
-        <v>0</v>
-      </c>
-      <c r="U85" t="n">
-        <v>0</v>
-      </c>
-      <c r="V85" t="n">
-        <v>0</v>
-      </c>
-      <c r="W85" t="n">
-        <v>0</v>
-      </c>
-      <c r="X85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y85" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY85" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG85" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH85" t="inlineStr">
-        <is>
-          <t>2026-04-22 17:35:15</t>
+      <c r="R87" t="n">
+        <v>0</v>
+      </c>
+      <c r="S87" t="n">
+        <v>0</v>
+      </c>
+      <c r="T87" t="n">
+        <v>0</v>
+      </c>
+      <c r="U87" t="n">
+        <v>0</v>
+      </c>
+      <c r="V87" t="n">
+        <v>0</v>
+      </c>
+      <c r="W87" t="n">
+        <v>0</v>
+      </c>
+      <c r="X87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y87" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY87" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG87" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH87" t="inlineStr">
+        <is>
+          <t>2026-04-22 19:53:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Paraguayan Primera Division</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>20:00:00</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Cerro Porteno</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>Club Sportivo Ameliano</t>
+        </is>
+      </c>
+      <c r="F88" t="n">
+        <v>0</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" t="n">
+        <v>0</v>
+      </c>
+      <c r="J88" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" t="n">
+        <v>0</v>
+      </c>
+      <c r="L88" t="n">
+        <v>0</v>
+      </c>
+      <c r="M88" t="n">
+        <v>0</v>
+      </c>
+      <c r="N88" t="n">
+        <v>0</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="Q88" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="R88" t="n">
+        <v>0</v>
+      </c>
+      <c r="S88" t="n">
+        <v>0</v>
+      </c>
+      <c r="T88" t="n">
+        <v>0</v>
+      </c>
+      <c r="U88" t="n">
+        <v>0</v>
+      </c>
+      <c r="V88" t="n">
+        <v>0</v>
+      </c>
+      <c r="W88" t="n">
+        <v>0</v>
+      </c>
+      <c r="X88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY88" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG88" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH88" t="inlineStr">
+        <is>
+          <t>2026-04-22 19:53:12</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-24.xlsx
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="G2" t="n">
         <v>2.12</v>
@@ -766,7 +766,7 @@
         <v>3.4</v>
       </c>
       <c r="I2" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J2" t="n">
         <v>4.3</v>
@@ -781,13 +781,13 @@
         <v>1.03</v>
       </c>
       <c r="N2" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="O2" t="n">
         <v>1.17</v>
       </c>
       <c r="P2" t="n">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="Q2" t="n">
         <v>1.52</v>
@@ -805,10 +805,10 @@
         <v>2.68</v>
       </c>
       <c r="V2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W2" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X2" t="n">
         <v>32</v>
@@ -832,7 +832,7 @@
         <v>16</v>
       </c>
       <c r="AE2" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
         <v>17</v>
@@ -886,7 +886,7 @@
         <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AX2" t="n">
         <v>15</v>
@@ -898,7 +898,7 @@
         <v>13</v>
       </c>
       <c r="BA2" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="BB2" t="n">
         <v>19.5</v>
@@ -913,14 +913,14 @@
         <v>10.5</v>
       </c>
       <c r="BF2" t="n">
-        <v>6.4</v>
+        <v>7.8</v>
       </c>
       <c r="BG2" t="n">
         <v>18.5</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -960,73 +960,73 @@
         <v>2.02</v>
       </c>
       <c r="I3" t="n">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="J3" t="n">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K3" t="n">
         <v>3.95</v>
       </c>
       <c r="L3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="M3" t="n">
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="O3" t="n">
         <v>1.28</v>
       </c>
       <c r="P3" t="n">
-        <v>1.98</v>
+        <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.86</v>
+        <v>1.8</v>
       </c>
       <c r="R3" t="n">
-        <v>1.37</v>
+        <v>1.4</v>
       </c>
       <c r="S3" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.71</v>
+        <v>1.67</v>
       </c>
       <c r="U3" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="V3" t="n">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="W3" t="n">
         <v>1.32</v>
       </c>
       <c r="X3" t="n">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="Y3" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AA3" t="n">
         <v>30</v>
       </c>
       <c r="AB3" t="n">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AD3" t="n">
         <v>12.5</v>
       </c>
       <c r="AE3" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AF3" t="n">
         <v>34</v>
@@ -1035,58 +1035,58 @@
         <v>18.5</v>
       </c>
       <c r="AH3" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AI3" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AJ3" t="n">
         <v>85</v>
       </c>
       <c r="AK3" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL3" t="n">
         <v>60</v>
       </c>
       <c r="AM3" t="n">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AN3" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AO3" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AQ3" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AR3" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AT3" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AV3" t="n">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW3" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AX3" t="n">
         <v>21</v>
       </c>
       <c r="AY3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ3" t="n">
         <v>13</v>
@@ -1095,26 +1095,26 @@
         <v>5</v>
       </c>
       <c r="BB3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="BC3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BE3" t="n">
         <v>4.8</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>4.9</v>
       </c>
       <c r="BF3" t="n">
         <v>4.8</v>
       </c>
       <c r="BG3" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -1160,7 +1160,7 @@
         <v>2.78</v>
       </c>
       <c r="K4" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="L4" t="n">
         <v>1.61</v>
@@ -1169,10 +1169,10 @@
         <v>1.15</v>
       </c>
       <c r="N4" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="O4" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="P4" t="n">
         <v>1.45</v>
@@ -1187,10 +1187,10 @@
         <v>6.6</v>
       </c>
       <c r="T4" t="n">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="U4" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V4" t="n">
         <v>1.46</v>
@@ -1298,17 +1298,17 @@
         <v>5.7</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="BG4" t="n">
         <v>5.6</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -1342,28 +1342,28 @@
         <v>2.28</v>
       </c>
       <c r="G5" t="n">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="H5" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I5" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="J5" t="n">
-        <v>3</v>
+        <v>2.96</v>
       </c>
       <c r="K5" t="n">
         <v>3.35</v>
       </c>
       <c r="L5" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="M5" t="n">
         <v>1.11</v>
       </c>
       <c r="N5" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="O5" t="n">
         <v>1.49</v>
@@ -1381,16 +1381,16 @@
         <v>4.8</v>
       </c>
       <c r="T5" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U5" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="V5" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W5" t="n">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="X5" t="n">
         <v>10.5</v>
@@ -1447,13 +1447,13 @@
         <v>95</v>
       </c>
       <c r="AP5" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AQ5" t="n">
         <v>9.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="AS5" t="n">
         <v>5.3</v>
@@ -1483,10 +1483,10 @@
         <v>5.3</v>
       </c>
       <c r="BB5" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BC5" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BD5" t="n">
         <v>5.2</v>
@@ -1495,14 +1495,14 @@
         <v>5.5</v>
       </c>
       <c r="BF5" t="n">
-        <v>4.8</v>
+        <v>5.4</v>
       </c>
       <c r="BG5" t="n">
         <v>5.3</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -1536,7 +1536,7 @@
         <v>1.72</v>
       </c>
       <c r="G6" t="n">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="H6" t="n">
         <v>5.1</v>
@@ -1578,7 +1578,7 @@
         <v>1.89</v>
       </c>
       <c r="U6" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V6" t="n">
         <v>1.2</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -1730,19 +1730,19 @@
         <v>3.95</v>
       </c>
       <c r="G7" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="H7" t="n">
         <v>1.95</v>
       </c>
       <c r="I7" t="n">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="J7" t="n">
         <v>3.75</v>
       </c>
       <c r="K7" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L7" t="n">
         <v>1.29</v>
@@ -1760,7 +1760,7 @@
         <v>2.16</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="R7" t="n">
         <v>1.45</v>
@@ -1772,13 +1772,13 @@
         <v>1.7</v>
       </c>
       <c r="U7" t="n">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="V7" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="W7" t="n">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="X7" t="n">
         <v>22</v>
@@ -1859,7 +1859,7 @@
         <v>17</v>
       </c>
       <c r="AX7" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AY7" t="n">
         <v>12</v>
@@ -1868,13 +1868,13 @@
         <v>12.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>5.5</v>
+        <v>6.2</v>
       </c>
       <c r="BB7" t="n">
         <v>6.2</v>
       </c>
       <c r="BC7" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BD7" t="n">
         <v>5.9</v>
@@ -1883,14 +1883,14 @@
         <v>6.2</v>
       </c>
       <c r="BF7" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BG7" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -1921,22 +1921,22 @@
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G8" t="n">
-        <v>2.64</v>
+        <v>2.58</v>
       </c>
       <c r="H8" t="n">
-        <v>2.76</v>
+        <v>2.8</v>
       </c>
       <c r="I8" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="J8" t="n">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L8" t="n">
         <v>1.01</v>
@@ -1957,7 +1957,7 @@
         <v>1.75</v>
       </c>
       <c r="R8" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S8" t="n">
         <v>2.88</v>
@@ -1966,13 +1966,13 @@
         <v>1.64</v>
       </c>
       <c r="U8" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="V8" t="n">
         <v>1.51</v>
       </c>
       <c r="W8" t="n">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="X8" t="n">
         <v>19.5</v>
@@ -1990,7 +1990,7 @@
         <v>13.5</v>
       </c>
       <c r="AC8" t="n">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD8" t="n">
         <v>13.5</v>
@@ -2038,19 +2038,19 @@
         <v>17.5</v>
       </c>
       <c r="AS8" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AT8" t="n">
         <v>11</v>
       </c>
       <c r="AU8" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="AV8" t="n">
         <v>10.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AX8" t="n">
         <v>15.5</v>
@@ -2062,19 +2062,19 @@
         <v>13.5</v>
       </c>
       <c r="BA8" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BB8" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BC8" t="n">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BD8" t="n">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="BE8" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF8" t="n">
         <v>13</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>1.01</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O9" t="n">
         <v>1.14</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -2515,31 +2515,31 @@
         <v>3.05</v>
       </c>
       <c r="J11" t="n">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K11" t="n">
         <v>4.3</v>
       </c>
       <c r="L11" t="n">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="M11" t="n">
         <v>1.03</v>
       </c>
       <c r="N11" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O11" t="n">
         <v>1.2</v>
       </c>
       <c r="P11" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="Q11" t="n">
         <v>1.6</v>
       </c>
       <c r="R11" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S11" t="n">
         <v>2.44</v>
@@ -2548,7 +2548,7 @@
         <v>1.56</v>
       </c>
       <c r="U11" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="V11" t="n">
         <v>1.5</v>
@@ -2620,13 +2620,13 @@
         <v>7.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>4.5</v>
+        <v>3.35</v>
       </c>
       <c r="AT11" t="n">
         <v>6.2</v>
       </c>
       <c r="AU11" t="n">
-        <v>5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV11" t="n">
         <v>6</v>
@@ -2638,13 +2638,13 @@
         <v>7</v>
       </c>
       <c r="AY11" t="n">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AZ11" t="n">
         <v>6.2</v>
       </c>
       <c r="BA11" t="n">
-        <v>4.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB11" t="n">
         <v>4.4</v>
@@ -2656,17 +2656,17 @@
         <v>8</v>
       </c>
       <c r="BE11" t="n">
-        <v>2.88</v>
+        <v>3.4</v>
       </c>
       <c r="BF11" t="n">
         <v>11</v>
       </c>
       <c r="BG11" t="n">
-        <v>13.5</v>
+        <v>6.6</v>
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -2700,20 +2700,20 @@
         <v>2.1</v>
       </c>
       <c r="G12" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="H12" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="I12" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J12" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K12" t="n">
         <v>4</v>
       </c>
-      <c r="J12" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.9</v>
-      </c>
       <c r="L12" t="n">
         <v>1.01</v>
       </c>
@@ -2721,22 +2721,22 @@
         <v>1.01</v>
       </c>
       <c r="N12" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="O12" t="n">
         <v>1.29</v>
       </c>
       <c r="P12" t="n">
-        <v>1.93</v>
+        <v>1.95</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="R12" t="n">
         <v>1.18</v>
       </c>
       <c r="S12" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="T12" t="n">
         <v>1.01</v>
@@ -2748,7 +2748,7 @@
         <v>1.3</v>
       </c>
       <c r="W12" t="n">
-        <v>1.73</v>
+        <v>1.66</v>
       </c>
       <c r="X12" t="n">
         <v>1000</v>
@@ -2860,7 +2860,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
         </is>
       </c>
       <c r="F13" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="G13" t="n">
         <v>2.02</v>
@@ -2900,16 +2900,16 @@
         <v>4</v>
       </c>
       <c r="I13" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="J13" t="n">
         <v>3.7</v>
       </c>
       <c r="K13" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L13" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="M13" t="n">
         <v>1.05</v>
@@ -2927,13 +2927,13 @@
         <v>1.76</v>
       </c>
       <c r="R13" t="n">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S13" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="T13" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="U13" t="n">
         <v>2.18</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -3112,19 +3112,19 @@
         <v>1.01</v>
       </c>
       <c r="O14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="P14" t="n">
         <v>1.25</v>
       </c>
       <c r="Q14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="R14" t="n">
         <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -3476,19 +3476,19 @@
         <v>1.78</v>
       </c>
       <c r="G16" t="n">
-        <v>1.85</v>
+        <v>1.88</v>
       </c>
       <c r="H16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I16" t="n">
         <v>4.8</v>
       </c>
       <c r="J16" t="n">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="K16" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L16" t="n">
         <v>1.01</v>
@@ -3497,37 +3497,37 @@
         <v>1.03</v>
       </c>
       <c r="N16" t="n">
-        <v>5.4</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="P16" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="Q16" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="R16" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="S16" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="T16" t="n">
         <v>1.62</v>
       </c>
       <c r="U16" t="n">
-        <v>2.36</v>
+        <v>2.16</v>
       </c>
       <c r="V16" t="n">
         <v>1.26</v>
       </c>
       <c r="W16" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="X16" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="Y16" t="n">
         <v>23</v>
@@ -3575,22 +3575,22 @@
         <v>70</v>
       </c>
       <c r="AN16" t="n">
-        <v>8.199999999999999</v>
+        <v>10</v>
       </c>
       <c r="AO16" t="n">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AP16" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AQ16" t="n">
         <v>18.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="AS16" t="n">
-        <v>7.4</v>
+        <v>6.4</v>
       </c>
       <c r="AT16" t="n">
         <v>10.5</v>
@@ -3602,7 +3602,7 @@
         <v>15.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="AX16" t="n">
         <v>11</v>
@@ -3614,29 +3614,29 @@
         <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="BB16" t="n">
-        <v>5.8</v>
+        <v>17</v>
       </c>
       <c r="BC16" t="n">
         <v>14</v>
       </c>
       <c r="BD16" t="n">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE16" t="n">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="BF16" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BG16" t="n">
         <v>6</v>
       </c>
-      <c r="BG16" t="n">
-        <v>6.8</v>
-      </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -3691,7 +3691,7 @@
         <v>1.01</v>
       </c>
       <c r="N17" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O17" t="n">
         <v>1.04</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -3867,7 +3867,7 @@
         <v>1.72</v>
       </c>
       <c r="H18" t="n">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="I18" t="n">
         <v>7.6</v>
@@ -3876,7 +3876,7 @@
         <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3885,40 +3885,40 @@
         <v>1.06</v>
       </c>
       <c r="N18" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="O18" t="n">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P18" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R18" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="S18" t="n">
+        <v>3</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="U18" t="n">
         <v>2</v>
-      </c>
-      <c r="Q18" t="n">
-        <v>1.87</v>
-      </c>
-      <c r="R18" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="S18" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T18" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="U18" t="n">
-        <v>1.96</v>
       </c>
       <c r="V18" t="n">
         <v>1.16</v>
       </c>
       <c r="W18" t="n">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="X18" t="n">
         <v>19</v>
       </c>
       <c r="Y18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="Z18" t="n">
         <v>60</v>
@@ -3933,7 +3933,7 @@
         <v>11.5</v>
       </c>
       <c r="AD18" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE18" t="n">
         <v>1000</v>
@@ -3963,68 +3963,68 @@
         <v>1000</v>
       </c>
       <c r="AN18" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AO18" t="n">
         <v>1000</v>
       </c>
       <c r="AP18" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="AQ18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AR18" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="AS18" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AT18" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="AU18" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AV18" t="n">
+        <v>4</v>
+      </c>
+      <c r="AW18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="AZ18" t="n">
+        <v>4</v>
+      </c>
+      <c r="BA18" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BB18" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="BC18" t="n">
         <v>3.9</v>
       </c>
-      <c r="AR18" t="n">
+      <c r="BD18" t="n">
         <v>4.3</v>
       </c>
-      <c r="AS18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="AT18" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AU18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AV18" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="AW18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="AX18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AY18" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="AZ18" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="BA18" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BB18" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="BC18" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="BD18" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BE18" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BF18" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="BG18" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -4055,22 +4055,22 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="G19" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="H19" t="n">
-        <v>2.96</v>
+        <v>3.1</v>
       </c>
       <c r="I19" t="n">
         <v>3.7</v>
       </c>
       <c r="J19" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="K19" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4079,16 +4079,16 @@
         <v>1.03</v>
       </c>
       <c r="N19" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="O19" t="n">
         <v>1.3</v>
       </c>
       <c r="P19" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="Q19" t="n">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="R19" t="n">
         <v>1.27</v>
@@ -4106,7 +4106,7 @@
         <v>1.37</v>
       </c>
       <c r="W19" t="n">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="X19" t="n">
         <v>1000</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -4291,7 +4291,7 @@
         <v>2.32</v>
       </c>
       <c r="T20" t="n">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="U20" t="n">
         <v>1.01</v>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -4449,10 +4449,10 @@
         <v>6</v>
       </c>
       <c r="H21" t="n">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="I21" t="n">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="J21" t="n">
         <v>3.55</v>
@@ -4467,13 +4467,13 @@
         <v>1.07</v>
       </c>
       <c r="N21" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="O21" t="n">
         <v>1.33</v>
       </c>
       <c r="P21" t="n">
-        <v>1.81</v>
+        <v>1.82</v>
       </c>
       <c r="Q21" t="n">
         <v>1.98</v>
@@ -4482,16 +4482,16 @@
         <v>1.31</v>
       </c>
       <c r="S21" t="n">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="T21" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="U21" t="n">
         <v>1.92</v>
       </c>
       <c r="V21" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="W21" t="n">
         <v>1.2</v>
@@ -4524,7 +4524,7 @@
         <v>50</v>
       </c>
       <c r="AG21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AH21" t="n">
         <v>26</v>
@@ -4554,19 +4554,19 @@
         <v>10</v>
       </c>
       <c r="AQ21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AR21" t="n">
         <v>7.8</v>
       </c>
       <c r="AS21" t="n">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AT21" t="n">
         <v>12</v>
       </c>
       <c r="AU21" t="n">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AV21" t="n">
         <v>7.6</v>
@@ -4575,16 +4575,16 @@
         <v>14.5</v>
       </c>
       <c r="AX21" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AY21" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AZ21" t="n">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="BA21" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BB21" t="n">
         <v>4.2</v>
@@ -4602,11 +4602,11 @@
         <v>4.1</v>
       </c>
       <c r="BG21" t="n">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -4661,7 +4661,7 @@
         <v>1.05</v>
       </c>
       <c r="N22" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O22" t="n">
         <v>1.25</v>
@@ -4721,7 +4721,7 @@
         <v>17</v>
       </c>
       <c r="AH22" t="n">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="AI22" t="n">
         <v>38</v>
@@ -4733,16 +4733,16 @@
         <v>42</v>
       </c>
       <c r="AL22" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AM22" t="n">
         <v>85</v>
       </c>
       <c r="AN22" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO22" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AP22" t="n">
         <v>13.5</v>
@@ -4754,7 +4754,7 @@
         <v>12</v>
       </c>
       <c r="AS22" t="n">
-        <v>4.5</v>
+        <v>5.1</v>
       </c>
       <c r="AT22" t="n">
         <v>11.5</v>
@@ -4778,29 +4778,29 @@
         <v>12.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BB22" t="n">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BC22" t="n">
-        <v>4.6</v>
+        <v>5.1</v>
       </c>
       <c r="BD22" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="BE22" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="BF22" t="n">
-        <v>4.5</v>
+        <v>5.2</v>
       </c>
       <c r="BG22" t="n">
         <v>11</v>
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -4831,10 +4831,10 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.84</v>
+        <v>1.69</v>
       </c>
       <c r="G23" t="n">
-        <v>2.24</v>
+        <v>2.46</v>
       </c>
       <c r="H23" t="n">
         <v>3</v>
@@ -4846,7 +4846,7 @@
         <v>3.25</v>
       </c>
       <c r="K23" t="n">
-        <v>8</v>
+        <v>13.5</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
@@ -4855,7 +4855,7 @@
         <v>1.03</v>
       </c>
       <c r="N23" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="O23" t="n">
         <v>1.21</v>
@@ -4864,13 +4864,13 @@
         <v>1.41</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R23" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="S23" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T23" t="n">
         <v>1.01</v>
@@ -4882,7 +4882,7 @@
         <v>1.26</v>
       </c>
       <c r="W23" t="n">
-        <v>1.8</v>
+        <v>1.68</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
@@ -4994,7 +4994,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.38</v>
+        <v>2.62</v>
       </c>
       <c r="G24" t="n">
         <v>3.25</v>
       </c>
       <c r="H24" t="n">
-        <v>2.38</v>
+        <v>2.3</v>
       </c>
       <c r="I24" t="n">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="J24" t="n">
         <v>3.55</v>
       </c>
       <c r="K24" t="n">
-        <v>6</v>
+        <v>5.5</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -5058,13 +5058,13 @@
         <v>1.83</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="R24" t="n">
         <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="T24" t="n">
         <v>1.01</v>
@@ -5073,10 +5073,10 @@
         <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.52</v>
+        <v>1.51</v>
       </c>
       <c r="W24" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -5243,7 +5243,7 @@
         <v>1.01</v>
       </c>
       <c r="N25" t="n">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="O25" t="n">
         <v>1.11</v>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>1.86</v>
+        <v>2.12</v>
       </c>
       <c r="G26" t="n">
         <v>1000</v>
@@ -5425,10 +5425,10 @@
         <v>1000</v>
       </c>
       <c r="J26" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K26" t="n">
-        <v>950</v>
+        <v>6.6</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -5610,13 +5610,13 @@
         <v>2.18</v>
       </c>
       <c r="G27" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="H27" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="I27" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J27" t="n">
         <v>3.8</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -5801,10 +5801,10 @@
         </is>
       </c>
       <c r="F28" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G28" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H28" t="n">
         <v>3.05</v>
@@ -5816,7 +5816,7 @@
         <v>3.6</v>
       </c>
       <c r="K28" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L28" t="n">
         <v>1.01</v>
@@ -5828,7 +5828,7 @@
         <v>4.3</v>
       </c>
       <c r="O28" t="n">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P28" t="n">
         <v>2.14</v>
@@ -5837,13 +5837,13 @@
         <v>1.76</v>
       </c>
       <c r="R28" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="S28" t="n">
         <v>2.88</v>
       </c>
       <c r="T28" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="U28" t="n">
         <v>2.32</v>
@@ -5852,7 +5852,7 @@
         <v>1.41</v>
       </c>
       <c r="W28" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="X28" t="n">
         <v>22</v>
@@ -5867,7 +5867,7 @@
         <v>65</v>
       </c>
       <c r="AB28" t="n">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AC28" t="n">
         <v>10.5</v>
@@ -5918,7 +5918,7 @@
         <v>20</v>
       </c>
       <c r="AS28" t="n">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="AT28" t="n">
         <v>10.5</v>
@@ -5930,7 +5930,7 @@
         <v>12</v>
       </c>
       <c r="AW28" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="AX28" t="n">
         <v>14.5</v>
@@ -5942,19 +5942,19 @@
         <v>14</v>
       </c>
       <c r="BA28" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="BB28" t="n">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BC28" t="n">
         <v>20</v>
       </c>
       <c r="BD28" t="n">
-        <v>3.9</v>
+        <v>4.2</v>
       </c>
       <c r="BE28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF28" t="n">
         <v>11</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -6010,7 +6010,7 @@
         <v>4</v>
       </c>
       <c r="K29" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L29" t="n">
         <v>1.01</v>
@@ -6019,13 +6019,13 @@
         <v>1.05</v>
       </c>
       <c r="N29" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="O29" t="n">
         <v>1.25</v>
       </c>
       <c r="P29" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q29" t="n">
         <v>1.73</v>
@@ -6037,16 +6037,16 @@
         <v>2.86</v>
       </c>
       <c r="T29" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="U29" t="n">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V29" t="n">
         <v>1.2</v>
       </c>
       <c r="W29" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="X29" t="n">
         <v>22</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -6428,7 +6428,7 @@
         <v>1.6</v>
       </c>
       <c r="U31" t="n">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="V31" t="n">
         <v>1.17</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -6577,19 +6577,19 @@
         </is>
       </c>
       <c r="F32" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="G32" t="n">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="H32" t="n">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="I32" t="n">
         <v>5.4</v>
       </c>
       <c r="J32" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="K32" t="n">
         <v>3.35</v>
@@ -6622,13 +6622,13 @@
         <v>2.24</v>
       </c>
       <c r="U32" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="V32" t="n">
         <v>1.23</v>
       </c>
       <c r="W32" t="n">
-        <v>1.88</v>
+        <v>1.84</v>
       </c>
       <c r="X32" t="n">
         <v>10</v>
@@ -6640,7 +6640,7 @@
         <v>44</v>
       </c>
       <c r="AA32" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AB32" t="n">
         <v>7.6</v>
@@ -6652,7 +6652,7 @@
         <v>26</v>
       </c>
       <c r="AE32" t="n">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AF32" t="n">
         <v>13.5</v>
@@ -6664,7 +6664,7 @@
         <v>32</v>
       </c>
       <c r="AI32" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ32" t="n">
         <v>32</v>
@@ -6676,13 +6676,13 @@
         <v>80</v>
       </c>
       <c r="AM32" t="n">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AN32" t="n">
         <v>34</v>
       </c>
       <c r="AO32" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="AP32" t="n">
         <v>7.4</v>
@@ -6691,10 +6691,10 @@
         <v>10.5</v>
       </c>
       <c r="AR32" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="AS32" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="AT32" t="n">
         <v>5.7</v>
@@ -6703,7 +6703,7 @@
         <v>6.6</v>
       </c>
       <c r="AV32" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="AW32" t="n">
         <v>4.3</v>
@@ -6715,7 +6715,7 @@
         <v>10</v>
       </c>
       <c r="AZ32" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="BA32" t="n">
         <v>4.3</v>
@@ -6736,11 +6736,11 @@
         <v>20</v>
       </c>
       <c r="BG32" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -6783,7 +6783,7 @@
         <v>2.7</v>
       </c>
       <c r="J33" t="n">
-        <v>2.72</v>
+        <v>2.68</v>
       </c>
       <c r="K33" t="n">
         <v>2.98</v>
@@ -6822,7 +6822,7 @@
         <v>1.59</v>
       </c>
       <c r="W33" t="n">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="X33" t="n">
         <v>6.6</v>
@@ -6837,7 +6837,7 @@
         <v>55</v>
       </c>
       <c r="AB33" t="n">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC33" t="n">
         <v>8.199999999999999</v>
@@ -6849,7 +6849,7 @@
         <v>1000</v>
       </c>
       <c r="AF33" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AG33" t="n">
         <v>23</v>
@@ -6888,7 +6888,7 @@
         <v>12</v>
       </c>
       <c r="AS33" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AT33" t="n">
         <v>7.4</v>
@@ -6900,7 +6900,7 @@
         <v>12</v>
       </c>
       <c r="AW33" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="AX33" t="n">
         <v>21</v>
@@ -6909,32 +6909,32 @@
         <v>16.5</v>
       </c>
       <c r="AZ33" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BA33" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BB33" t="n">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="BC33" t="n">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="BD33" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="BE33" t="n">
+        <v>5.8</v>
+      </c>
+      <c r="BF33" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="BG33" t="n">
         <v>5.4</v>
       </c>
-      <c r="BE33" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="BF33" t="n">
-        <v>5.4</v>
-      </c>
-      <c r="BG33" t="n">
-        <v>5.2</v>
-      </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -6965,13 +6965,13 @@
         </is>
       </c>
       <c r="F34" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="G34" t="n">
         <v>1.78</v>
       </c>
       <c r="H34" t="n">
-        <v>4.9</v>
+        <v>5.2</v>
       </c>
       <c r="I34" t="n">
         <v>5.7</v>
@@ -6980,7 +6980,7 @@
         <v>3.8</v>
       </c>
       <c r="K34" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -7165,16 +7165,16 @@
         <v>4</v>
       </c>
       <c r="H35" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="I35" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="J35" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="K35" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L35" t="n">
         <v>1.01</v>
@@ -7183,16 +7183,16 @@
         <v>1.03</v>
       </c>
       <c r="N35" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="O35" t="n">
         <v>1.2</v>
       </c>
       <c r="P35" t="n">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.64</v>
+        <v>1.59</v>
       </c>
       <c r="R35" t="n">
         <v>1.44</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -7571,13 +7571,13 @@
         <v>1.05</v>
       </c>
       <c r="N37" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O37" t="n">
         <v>1.32</v>
       </c>
       <c r="P37" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="Q37" t="n">
         <v>1.85</v>
@@ -7586,7 +7586,7 @@
         <v>1.35</v>
       </c>
       <c r="S37" t="n">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T37" t="n">
         <v>1.86</v>
@@ -7610,7 +7610,7 @@
         <v>65</v>
       </c>
       <c r="AA37" t="n">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AB37" t="n">
         <v>8</v>
@@ -7622,7 +7622,7 @@
         <v>28</v>
       </c>
       <c r="AE37" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AF37" t="n">
         <v>9</v>
@@ -7664,7 +7664,7 @@
         <v>6.4</v>
       </c>
       <c r="AS37" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT37" t="n">
         <v>5.9</v>
@@ -7685,7 +7685,7 @@
         <v>4.2</v>
       </c>
       <c r="AZ37" t="n">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BA37" t="n">
         <v>6.6</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -7741,19 +7741,19 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="G38" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="H38" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="I38" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="J38" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="K38" t="n">
         <v>4.8</v>
@@ -7774,7 +7774,7 @@
         <v>1.93</v>
       </c>
       <c r="Q38" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R38" t="n">
         <v>1.28</v>
@@ -7789,10 +7789,10 @@
         <v>1.01</v>
       </c>
       <c r="V38" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="W38" t="n">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="X38" t="n">
         <v>1000</v>
@@ -7904,7 +7904,7 @@
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -7938,16 +7938,16 @@
         <v>2.8</v>
       </c>
       <c r="G39" t="n">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="H39" t="n">
         <v>2.32</v>
       </c>
       <c r="I39" t="n">
-        <v>2.86</v>
+        <v>2.8</v>
       </c>
       <c r="J39" t="n">
-        <v>2.92</v>
+        <v>3.3</v>
       </c>
       <c r="K39" t="n">
         <v>3.7</v>
@@ -7980,13 +7980,13 @@
         <v>1.01</v>
       </c>
       <c r="U39" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="V39" t="n">
-        <v>1.64</v>
+        <v>1.55</v>
       </c>
       <c r="W39" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -8129,19 +8129,19 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="G40" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="H40" t="n">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="I40" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="J40" t="n">
-        <v>3.15</v>
+        <v>2.88</v>
       </c>
       <c r="K40" t="n">
         <v>3.55</v>
@@ -8153,16 +8153,16 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="O40" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="P40" t="n">
         <v>1.73</v>
       </c>
       <c r="Q40" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="R40" t="n">
         <v>1.22</v>
@@ -8177,10 +8177,10 @@
         <v>1.11</v>
       </c>
       <c r="V40" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="W40" t="n">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -8326,7 +8326,7 @@
         <v>1.44</v>
       </c>
       <c r="G41" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="H41" t="n">
         <v>7</v>
@@ -8347,16 +8347,16 @@
         <v>1.04</v>
       </c>
       <c r="N41" t="n">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="O41" t="n">
         <v>1.29</v>
       </c>
       <c r="P41" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="Q41" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="R41" t="n">
         <v>1.29</v>
@@ -8374,7 +8374,7 @@
         <v>1.11</v>
       </c>
       <c r="W41" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="X41" t="n">
         <v>1000</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -8520,7 +8520,7 @@
         <v>1.6</v>
       </c>
       <c r="G42" t="n">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H42" t="n">
         <v>5</v>
@@ -8550,19 +8550,19 @@
         <v>1.9</v>
       </c>
       <c r="Q42" t="n">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="R42" t="n">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="S42" t="n">
         <v>3.25</v>
       </c>
       <c r="T42" t="n">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="U42" t="n">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="V42" t="n">
         <v>1.16</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -8714,16 +8714,16 @@
         <v>2.84</v>
       </c>
       <c r="G43" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H43" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="I43" t="n">
         <v>2.64</v>
       </c>
       <c r="J43" t="n">
-        <v>3.2</v>
+        <v>3.5</v>
       </c>
       <c r="K43" t="n">
         <v>3.95</v>
@@ -8762,7 +8762,7 @@
         <v>1.6</v>
       </c>
       <c r="W43" t="n">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="X43" t="n">
         <v>1000</v>
@@ -8874,7 +8874,7 @@
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -8905,22 +8905,22 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.74</v>
+        <v>1.8</v>
       </c>
       <c r="G44" t="n">
-        <v>1.98</v>
+        <v>2.06</v>
       </c>
       <c r="H44" t="n">
-        <v>3.95</v>
+        <v>4.2</v>
       </c>
       <c r="I44" t="n">
-        <v>6.2</v>
+        <v>5.8</v>
       </c>
       <c r="J44" t="n">
         <v>3.35</v>
       </c>
       <c r="K44" t="n">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="L44" t="n">
         <v>1.01</v>
@@ -8935,10 +8935,10 @@
         <v>1.31</v>
       </c>
       <c r="P44" t="n">
-        <v>1.74</v>
+        <v>1.7</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R44" t="n">
         <v>1.27</v>
@@ -8956,7 +8956,7 @@
         <v>1.22</v>
       </c>
       <c r="W44" t="n">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="X44" t="n">
         <v>1000</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -9102,7 +9102,7 @@
         <v>2.1</v>
       </c>
       <c r="G45" t="n">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="H45" t="n">
         <v>3.85</v>
@@ -9147,7 +9147,7 @@
         <v>1.94</v>
       </c>
       <c r="V45" t="n">
-        <v>1.31</v>
+        <v>1.3</v>
       </c>
       <c r="W45" t="n">
         <v>1.8</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -9296,19 +9296,19 @@
         <v>3.35</v>
       </c>
       <c r="G46" t="n">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="H46" t="n">
-        <v>1.92</v>
+        <v>2</v>
       </c>
       <c r="I46" t="n">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="J46" t="n">
         <v>2.9</v>
       </c>
       <c r="K46" t="n">
-        <v>5.5</v>
+        <v>4.9</v>
       </c>
       <c r="L46" t="n">
         <v>1.01</v>
@@ -9320,31 +9320,31 @@
         <v>1.6</v>
       </c>
       <c r="O46" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P46" t="n">
         <v>1.6</v>
       </c>
       <c r="Q46" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R46" t="n">
         <v>1.22</v>
       </c>
       <c r="S46" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T46" t="n">
         <v>1.01</v>
       </c>
       <c r="U46" t="n">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="V46" t="n">
-        <v>1.74</v>
+        <v>1.62</v>
       </c>
       <c r="W46" t="n">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="X46" t="n">
         <v>1000</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -9490,7 +9490,7 @@
         <v>2.64</v>
       </c>
       <c r="G47" t="n">
-        <v>2.9</v>
+        <v>3.05</v>
       </c>
       <c r="H47" t="n">
         <v>2.34</v>
@@ -9502,7 +9502,7 @@
         <v>4.1</v>
       </c>
       <c r="K47" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="L47" t="n">
         <v>1.01</v>
@@ -9511,13 +9511,13 @@
         <v>1.02</v>
       </c>
       <c r="N47" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O47" t="n">
         <v>1.11</v>
       </c>
       <c r="P47" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="Q47" t="n">
         <v>1.44</v>
@@ -9538,7 +9538,7 @@
         <v>1.65</v>
       </c>
       <c r="W47" t="n">
-        <v>1.52</v>
+        <v>1.48</v>
       </c>
       <c r="X47" t="n">
         <v>1000</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -9681,22 +9681,22 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="G48" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="H48" t="n">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="I48" t="n">
         <v>1.99</v>
       </c>
       <c r="J48" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K48" t="n">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="L48" t="n">
         <v>1.01</v>
@@ -9705,13 +9705,13 @@
         <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="O48" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="P48" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q48" t="n">
         <v>1.51</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -9881,7 +9881,7 @@
         <v>3.85</v>
       </c>
       <c r="H49" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="I49" t="n">
         <v>2.26</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -10069,22 +10069,22 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="G50" t="n">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="H50" t="n">
-        <v>3.6</v>
+        <v>3.8</v>
       </c>
       <c r="I50" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J50" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="K50" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L50" t="n">
         <v>1.36</v>
@@ -10093,28 +10093,28 @@
         <v>1.07</v>
       </c>
       <c r="N50" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O50" t="n">
-        <v>1.29</v>
+        <v>1.34</v>
       </c>
       <c r="P50" t="n">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="Q50" t="n">
-        <v>1.98</v>
+        <v>2.02</v>
       </c>
       <c r="R50" t="n">
         <v>1.33</v>
       </c>
       <c r="S50" t="n">
-        <v>3.25</v>
+        <v>3.55</v>
       </c>
       <c r="T50" t="n">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="U50" t="n">
-        <v>2</v>
+        <v>2.08</v>
       </c>
       <c r="V50" t="n">
         <v>1.32</v>
@@ -10123,116 +10123,116 @@
         <v>1.84</v>
       </c>
       <c r="X50" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y50" t="n">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="Z50" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA50" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AB50" t="n">
-        <v>12</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC50" t="n">
-        <v>9.4</v>
+        <v>7.8</v>
       </c>
       <c r="AD50" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AE50" t="n">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF50" t="n">
-        <v>18</v>
+        <v>970</v>
       </c>
       <c r="AG50" t="n">
+        <v>11</v>
+      </c>
+      <c r="AH50" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI50" t="n">
+        <v>65</v>
+      </c>
+      <c r="AJ50" t="n">
+        <v>28</v>
+      </c>
+      <c r="AK50" t="n">
+        <v>23</v>
+      </c>
+      <c r="AL50" t="n">
+        <v>38</v>
+      </c>
+      <c r="AM50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO50" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP50" t="n">
+        <v>5.9</v>
+      </c>
+      <c r="AQ50" t="n">
         <v>12.5</v>
       </c>
-      <c r="AH50" t="n">
-        <v>21</v>
-      </c>
-      <c r="AI50" t="n">
-        <v>75</v>
-      </c>
-      <c r="AJ50" t="n">
+      <c r="AR50" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AS50" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AT50" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AU50" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AV50" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW50" t="n">
+        <v>8</v>
+      </c>
+      <c r="AX50" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AY50" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AZ50" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="BA50" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB50" t="n">
+        <v>7</v>
+      </c>
+      <c r="BC50" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="BD50" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="BE50" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BF50" t="n">
+        <v>13</v>
+      </c>
+      <c r="BG50" t="n">
         <v>36</v>
       </c>
-      <c r="AK50" t="n">
-        <v>30</v>
-      </c>
-      <c r="AL50" t="n">
-        <v>50</v>
-      </c>
-      <c r="AM50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO50" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP50" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AQ50" t="n">
-        <v>10</v>
-      </c>
-      <c r="AR50" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AS50" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AT50" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AU50" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV50" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW50" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AX50" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AY50" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AZ50" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="BA50" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="BB50" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BC50" t="n">
-        <v>17</v>
-      </c>
-      <c r="BD50" t="n">
-        <v>2.48</v>
-      </c>
-      <c r="BE50" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BF50" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="BG50" t="n">
-        <v>2.6</v>
-      </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -10263,16 +10263,16 @@
         </is>
       </c>
       <c r="F51" t="n">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="G51" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="H51" t="n">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="I51" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="J51" t="n">
         <v>3.2</v>
@@ -10368,13 +10368,13 @@
         <v>46</v>
       </c>
       <c r="AO51" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AP51" t="n">
         <v>9.800000000000001</v>
       </c>
       <c r="AQ51" t="n">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AR51" t="n">
         <v>13</v>
@@ -10389,7 +10389,7 @@
         <v>6.4</v>
       </c>
       <c r="AV51" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW51" t="n">
         <v>3.9</v>
@@ -10398,7 +10398,7 @@
         <v>14</v>
       </c>
       <c r="AY51" t="n">
-        <v>9.800000000000001</v>
+        <v>11</v>
       </c>
       <c r="AZ51" t="n">
         <v>16</v>
@@ -10410,7 +10410,7 @@
         <v>4</v>
       </c>
       <c r="BC51" t="n">
-        <v>3.9</v>
+        <v>26</v>
       </c>
       <c r="BD51" t="n">
         <v>4</v>
@@ -10422,11 +10422,11 @@
         <v>3.9</v>
       </c>
       <c r="BG51" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -10457,16 +10457,16 @@
         </is>
       </c>
       <c r="F52" t="n">
-        <v>2.54</v>
+        <v>2.6</v>
       </c>
       <c r="G52" t="n">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="H52" t="n">
-        <v>2.74</v>
+        <v>2.68</v>
       </c>
       <c r="I52" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="J52" t="n">
         <v>3.4</v>
@@ -10481,13 +10481,13 @@
         <v>1.07</v>
       </c>
       <c r="N52" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="O52" t="n">
         <v>1.3</v>
       </c>
       <c r="P52" t="n">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="Q52" t="n">
         <v>1.89</v>
@@ -10499,16 +10499,16 @@
         <v>3.25</v>
       </c>
       <c r="T52" t="n">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="U52" t="n">
         <v>2.2</v>
       </c>
       <c r="V52" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="W52" t="n">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="X52" t="n">
         <v>16</v>
@@ -10520,13 +10520,13 @@
         <v>21</v>
       </c>
       <c r="AA52" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="AB52" t="n">
         <v>12.5</v>
       </c>
       <c r="AC52" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD52" t="n">
         <v>13.5</v>
@@ -10562,7 +10562,7 @@
         <v>24</v>
       </c>
       <c r="AO52" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP52" t="n">
         <v>12.5</v>
@@ -10574,7 +10574,7 @@
         <v>17</v>
       </c>
       <c r="AS52" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AT52" t="n">
         <v>9.800000000000001</v>
@@ -10586,7 +10586,7 @@
         <v>11</v>
       </c>
       <c r="AW52" t="n">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX52" t="n">
         <v>15</v>
@@ -10598,19 +10598,19 @@
         <v>14</v>
       </c>
       <c r="BA52" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BB52" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BC52" t="n">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="BD52" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="BE52" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF52" t="n">
         <v>16.5</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -10651,16 +10651,16 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>2.06</v>
+        <v>1.99</v>
       </c>
       <c r="G53" t="n">
-        <v>2.22</v>
+        <v>2.14</v>
       </c>
       <c r="H53" t="n">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="I53" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="J53" t="n">
         <v>3.7</v>
@@ -10675,7 +10675,7 @@
         <v>1.06</v>
       </c>
       <c r="N53" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="O53" t="n">
         <v>1.31</v>
@@ -10693,16 +10693,16 @@
         <v>3.25</v>
       </c>
       <c r="T53" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="U53" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="V53" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W53" t="n">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="X53" t="n">
         <v>19</v>
@@ -10711,7 +10711,7 @@
         <v>970</v>
       </c>
       <c r="Z53" t="n">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AA53" t="n">
         <v>85</v>
@@ -10759,28 +10759,28 @@
         <v>60</v>
       </c>
       <c r="AP53" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AQ53" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="AR53" t="n">
         <v>6.8</v>
       </c>
       <c r="AS53" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AT53" t="n">
-        <v>4.8</v>
+        <v>8.4</v>
       </c>
       <c r="AU53" t="n">
         <v>4.6</v>
       </c>
       <c r="AV53" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AW53" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AX53" t="n">
         <v>5.4</v>
@@ -10789,22 +10789,22 @@
         <v>9</v>
       </c>
       <c r="AZ53" t="n">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="BA53" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BB53" t="n">
         <v>6.6</v>
       </c>
       <c r="BC53" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BD53" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BE53" t="n">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF53" t="n">
         <v>11.5</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -10851,13 +10851,13 @@
         <v>2.96</v>
       </c>
       <c r="H54" t="n">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="I54" t="n">
         <v>2.76</v>
       </c>
       <c r="J54" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K54" t="n">
         <v>4.3</v>
@@ -10893,7 +10893,7 @@
         <v>1.01</v>
       </c>
       <c r="V54" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="W54" t="n">
         <v>1.51</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -11039,7 +11039,7 @@
         </is>
       </c>
       <c r="F55" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="G55" t="n">
         <v>2.32</v>
@@ -11048,7 +11048,7 @@
         <v>2.98</v>
       </c>
       <c r="I55" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J55" t="n">
         <v>4.3</v>
@@ -11069,25 +11069,25 @@
         <v>1.15</v>
       </c>
       <c r="P55" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="Q55" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R55" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="S55" t="n">
-        <v>2.14</v>
+        <v>2.32</v>
       </c>
       <c r="T55" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="U55" t="n">
         <v>2.78</v>
       </c>
       <c r="V55" t="n">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W55" t="n">
         <v>1.76</v>
@@ -11102,7 +11102,7 @@
         <v>32</v>
       </c>
       <c r="AA55" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB55" t="n">
         <v>18.5</v>
@@ -11111,7 +11111,7 @@
         <v>11.5</v>
       </c>
       <c r="AD55" t="n">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AE55" t="n">
         <v>29</v>
@@ -11156,7 +11156,7 @@
         <v>23</v>
       </c>
       <c r="AS55" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT55" t="n">
         <v>15.5</v>
@@ -11168,7 +11168,7 @@
         <v>12</v>
       </c>
       <c r="AW55" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX55" t="n">
         <v>17</v>
@@ -11192,7 +11192,7 @@
         <v>21</v>
       </c>
       <c r="BE55" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF55" t="n">
         <v>8</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -11257,13 +11257,13 @@
         <v>1.02</v>
       </c>
       <c r="N56" t="n">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="O56" t="n">
         <v>1.13</v>
       </c>
       <c r="P56" t="n">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="Q56" t="n">
         <v>1.46</v>
@@ -11281,10 +11281,10 @@
         <v>1.11</v>
       </c>
       <c r="V56" t="n">
-        <v>1.56</v>
+        <v>1.64</v>
       </c>
       <c r="W56" t="n">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="X56" t="n">
         <v>1000</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -11436,7 +11436,7 @@
         <v>4.2</v>
       </c>
       <c r="I57" t="n">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J57" t="n">
         <v>4.3</v>
@@ -11451,16 +11451,16 @@
         <v>1.02</v>
       </c>
       <c r="N57" t="n">
-        <v>3.1</v>
+        <v>2.68</v>
       </c>
       <c r="O57" t="n">
         <v>1.1</v>
       </c>
       <c r="P57" t="n">
-        <v>3.1</v>
+        <v>2.68</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.36</v>
+        <v>1.33</v>
       </c>
       <c r="R57" t="n">
         <v>1.76</v>
@@ -11475,7 +11475,7 @@
         <v>1.01</v>
       </c>
       <c r="V57" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W57" t="n">
         <v>2.12</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -11621,19 +11621,19 @@
         </is>
       </c>
       <c r="F58" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="G58" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="H58" t="n">
         <v>2.52</v>
       </c>
-      <c r="G58" t="n">
-        <v>3</v>
-      </c>
-      <c r="H58" t="n">
-        <v>2.5</v>
-      </c>
       <c r="I58" t="n">
-        <v>3.05</v>
+        <v>2.84</v>
       </c>
       <c r="J58" t="n">
-        <v>3.5</v>
+        <v>3.8</v>
       </c>
       <c r="K58" t="n">
         <v>4.5</v>
@@ -11669,10 +11669,10 @@
         <v>1.11</v>
       </c>
       <c r="V58" t="n">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="W58" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="X58" t="n">
         <v>1000</v>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -11815,19 +11815,19 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.95</v>
+        <v>1.9</v>
       </c>
       <c r="G59" t="n">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="H59" t="n">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="I59" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="J59" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K59" t="n">
         <v>4.3</v>
@@ -11866,7 +11866,7 @@
         <v>1.3</v>
       </c>
       <c r="W59" t="n">
-        <v>1.87</v>
+        <v>1.92</v>
       </c>
       <c r="X59" t="n">
         <v>1000</v>
@@ -11978,7 +11978,7 @@
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -12033,16 +12033,16 @@
         <v>1.02</v>
       </c>
       <c r="N60" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="O60" t="n">
         <v>1.1</v>
       </c>
       <c r="P60" t="n">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="R60" t="n">
         <v>1.75</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -12203,22 +12203,22 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="G61" t="n">
         <v>2.82</v>
       </c>
       <c r="H61" t="n">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="I61" t="n">
-        <v>2.64</v>
+        <v>2.6</v>
       </c>
       <c r="J61" t="n">
         <v>4.1</v>
       </c>
       <c r="K61" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="L61" t="n">
         <v>1.01</v>
@@ -12227,16 +12227,16 @@
         <v>1.02</v>
       </c>
       <c r="N61" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O61" t="n">
         <v>1.11</v>
       </c>
       <c r="P61" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="Q61" t="n">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="R61" t="n">
         <v>1.75</v>
@@ -12251,7 +12251,7 @@
         <v>1.01</v>
       </c>
       <c r="V61" t="n">
-        <v>1.6</v>
+        <v>1.62</v>
       </c>
       <c r="W61" t="n">
         <v>1.54</v>
@@ -12366,7 +12366,7 @@
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -12406,13 +12406,13 @@
         <v>1.19</v>
       </c>
       <c r="I62" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="J62" t="n">
         <v>6.4</v>
       </c>
       <c r="K62" t="n">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="L62" t="n">
         <v>1.01</v>
@@ -12445,122 +12445,122 @@
         <v>1.11</v>
       </c>
       <c r="V62" t="n">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="W62" t="n">
         <v>1.01</v>
       </c>
       <c r="X62" t="n">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="Y62" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z62" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AA62" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AB62" t="n">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AC62" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AD62" t="n">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AE62" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AF62" t="n">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="AG62" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AH62" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AI62" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ62" t="n">
         <v>1000</v>
       </c>
       <c r="AK62" t="n">
-        <v>1000</v>
+        <v>620</v>
       </c>
       <c r="AL62" t="n">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AM62" t="n">
-        <v>1000</v>
+        <v>430</v>
       </c>
       <c r="AN62" t="n">
-        <v>1000</v>
+        <v>880</v>
       </c>
       <c r="AO62" t="n">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="AP62" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="AQ62" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="AR62" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="AS62" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="AT62" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="AU62" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AV62" t="n">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AW62" t="n">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AX62" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="AY62" t="n">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="AZ62" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BA62" t="n">
-        <v>1.01</v>
+        <v>2.36</v>
       </c>
       <c r="BB62" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BC62" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BD62" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BE62" t="n">
-        <v>1.01</v>
+        <v>2.44</v>
       </c>
       <c r="BF62" t="n">
-        <v>1.01</v>
+        <v>2.46</v>
       </c>
       <c r="BG62" t="n">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -12627,7 +12627,7 @@
         <v>1.58</v>
       </c>
       <c r="R63" t="n">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="S63" t="n">
         <v>2.2</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -12785,10 +12785,10 @@
         </is>
       </c>
       <c r="F64" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="G64" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="H64" t="n">
         <v>2.48</v>
@@ -12821,7 +12821,7 @@
         <v>2.3</v>
       </c>
       <c r="R64" t="n">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="S64" t="n">
         <v>4.5</v>
@@ -12836,10 +12836,10 @@
         <v>1.6</v>
       </c>
       <c r="W64" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X64" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y64" t="n">
         <v>9.199999999999999</v>
@@ -12884,7 +12884,7 @@
         <v>65</v>
       </c>
       <c r="AM64" t="n">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AN64" t="n">
         <v>60</v>
@@ -12902,13 +12902,13 @@
         <v>13</v>
       </c>
       <c r="AS64" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AT64" t="n">
         <v>9</v>
       </c>
       <c r="AU64" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV64" t="n">
         <v>10.5</v>
@@ -12923,22 +12923,22 @@
         <v>12.5</v>
       </c>
       <c r="AZ64" t="n">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BA64" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="BB64" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="BC64" t="n">
         <v>7.4</v>
       </c>
-      <c r="BB64" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BC64" t="n">
-        <v>7.2</v>
-      </c>
       <c r="BD64" t="n">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE64" t="n">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="BF64" t="n">
         <v>38</v>
@@ -12948,7 +12948,7 @@
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -12979,22 +12979,22 @@
         </is>
       </c>
       <c r="F65" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="G65" t="n">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="H65" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="I65" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J65" t="n">
         <v>4.1</v>
       </c>
       <c r="K65" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L65" t="n">
         <v>1.01</v>
@@ -13003,22 +13003,22 @@
         <v>1.01</v>
       </c>
       <c r="N65" t="n">
-        <v>2.02</v>
+        <v>1.97</v>
       </c>
       <c r="O65" t="n">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P65" t="n">
-        <v>2.02</v>
+        <v>1.95</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="R65" t="n">
         <v>1.31</v>
       </c>
       <c r="S65" t="n">
-        <v>2.72</v>
+        <v>2.88</v>
       </c>
       <c r="T65" t="n">
         <v>1.01</v>
@@ -13030,7 +13030,7 @@
         <v>1.12</v>
       </c>
       <c r="W65" t="n">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="X65" t="n">
         <v>1000</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -13227,7 +13227,7 @@
         <v>1.5</v>
       </c>
       <c r="X66" t="n">
-        <v>14.5</v>
+        <v>970</v>
       </c>
       <c r="Y66" t="n">
         <v>970</v>
@@ -13275,7 +13275,7 @@
         <v>120</v>
       </c>
       <c r="AN66" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AO66" t="n">
         <v>34</v>
@@ -13284,59 +13284,59 @@
         <v>9.6</v>
       </c>
       <c r="AQ66" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="AR66" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AS66" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AT66" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="AU66" t="n">
         <v>6.4</v>
       </c>
       <c r="AV66" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AW66" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX66" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="AY66" t="n">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AZ66" t="n">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BA66" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BB66" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BC66" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BD66" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="BE66" t="n">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BF66" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BG66" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -13367,7 +13367,7 @@
         </is>
       </c>
       <c r="F67" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="G67" t="n">
         <v>1.4</v>
@@ -13430,7 +13430,7 @@
         <v>90</v>
       </c>
       <c r="AA67" t="n">
-        <v>300</v>
+        <v>310</v>
       </c>
       <c r="AB67" t="n">
         <v>11.5</v>
@@ -13475,7 +13475,7 @@
         <v>110</v>
       </c>
       <c r="AP67" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AQ67" t="n">
         <v>23</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -13585,16 +13585,16 @@
         <v>1.01</v>
       </c>
       <c r="N68" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="O68" t="n">
         <v>1.27</v>
       </c>
       <c r="P68" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R68" t="n">
         <v>1.32</v>
@@ -13724,7 +13724,7 @@
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -13770,7 +13770,7 @@
         <v>4</v>
       </c>
       <c r="K69" t="n">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L69" t="n">
         <v>1.01</v>
@@ -13918,7 +13918,7 @@
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -13952,7 +13952,7 @@
         <v>1.36</v>
       </c>
       <c r="G70" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="H70" t="n">
         <v>11.5</v>
@@ -14045,7 +14045,7 @@
         <v>16.5</v>
       </c>
       <c r="AL70" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AM70" t="n">
         <v>1000</v>
@@ -14075,7 +14075,7 @@
         <v>11</v>
       </c>
       <c r="AV70" t="n">
-        <v>26</v>
+        <v>38</v>
       </c>
       <c r="AW70" t="n">
         <v>50</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -14152,13 +14152,13 @@
         <v>5.6</v>
       </c>
       <c r="I71" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="J71" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K71" t="n">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L71" t="n">
         <v>1.47</v>
@@ -14185,7 +14185,7 @@
         <v>4.1</v>
       </c>
       <c r="T71" t="n">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U71" t="n">
         <v>1.81</v>
@@ -14221,7 +14221,7 @@
         <v>120</v>
       </c>
       <c r="AF71" t="n">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG71" t="n">
         <v>12.5</v>
@@ -14272,7 +14272,7 @@
         <v>17</v>
       </c>
       <c r="AW71" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AX71" t="n">
         <v>8.6</v>
@@ -14284,7 +14284,7 @@
         <v>20</v>
       </c>
       <c r="BA71" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BB71" t="n">
         <v>16.5</v>
@@ -14293,20 +14293,20 @@
         <v>18.5</v>
       </c>
       <c r="BD71" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE71" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BF71" t="n">
         <v>10.5</v>
       </c>
       <c r="BG71" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -14337,25 +14337,25 @@
         </is>
       </c>
       <c r="F72" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="G72" t="n">
-        <v>3.55</v>
+        <v>3.95</v>
       </c>
       <c r="H72" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="I72" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="J72" t="n">
         <v>3.35</v>
       </c>
       <c r="K72" t="n">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="L72" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="M72" t="n">
         <v>1.07</v>
@@ -14364,31 +14364,31 @@
         <v>3.85</v>
       </c>
       <c r="O72" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="P72" t="n">
         <v>1.9</v>
       </c>
       <c r="Q72" t="n">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="R72" t="n">
         <v>1.35</v>
       </c>
       <c r="S72" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="T72" t="n">
-        <v>1.76</v>
+        <v>1.73</v>
       </c>
       <c r="U72" t="n">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="V72" t="n">
         <v>1.67</v>
       </c>
       <c r="W72" t="n">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="X72" t="n">
         <v>1000</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -14531,16 +14531,16 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="G73" t="n">
         <v>2.42</v>
       </c>
       <c r="H73" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I73" t="n">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="J73" t="n">
         <v>3.15</v>
@@ -14549,37 +14549,37 @@
         <v>3.55</v>
       </c>
       <c r="L73" t="n">
-        <v>1.45</v>
+        <v>1.44</v>
       </c>
       <c r="M73" t="n">
         <v>1.1</v>
       </c>
       <c r="N73" t="n">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="O73" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="P73" t="n">
         <v>1.63</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="R73" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="S73" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="T73" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U73" t="n">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="V73" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="W73" t="n">
         <v>1.7</v>
@@ -14597,7 +14597,7 @@
         <v>1000</v>
       </c>
       <c r="AB73" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC73" t="n">
         <v>8.6</v>
@@ -14612,7 +14612,7 @@
         <v>15.5</v>
       </c>
       <c r="AG73" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH73" t="n">
         <v>1000</v>
@@ -14642,59 +14642,59 @@
         <v>7.8</v>
       </c>
       <c r="AQ73" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="AR73" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AS73" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AT73" t="n">
-        <v>6.6</v>
+        <v>3.5</v>
       </c>
       <c r="AU73" t="n">
         <v>5.8</v>
       </c>
       <c r="AV73" t="n">
-        <v>4.1</v>
+        <v>12.5</v>
       </c>
       <c r="AW73" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AX73" t="n">
         <v>4.1</v>
       </c>
       <c r="AY73" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="AZ73" t="n">
-        <v>4.3</v>
+        <v>15.5</v>
       </c>
       <c r="BA73" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BB73" t="n">
         <v>4.6</v>
       </c>
       <c r="BC73" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="BD73" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE73" t="n">
+        <v>5</v>
+      </c>
+      <c r="BF73" t="n">
         <v>4.5</v>
       </c>
-      <c r="BD73" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="BE73" t="n">
+      <c r="BG73" t="n">
         <v>4.9</v>
       </c>
-      <c r="BF73" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="BG73" t="n">
-        <v>4.7</v>
-      </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -14725,13 +14725,13 @@
         </is>
       </c>
       <c r="F74" t="n">
-        <v>2.48</v>
+        <v>2.6</v>
       </c>
       <c r="G74" t="n">
-        <v>3.25</v>
+        <v>3</v>
       </c>
       <c r="H74" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="I74" t="n">
         <v>3.2</v>
@@ -14740,43 +14740,43 @@
         <v>3.15</v>
       </c>
       <c r="K74" t="n">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L74" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="M74" t="n">
         <v>1.07</v>
       </c>
       <c r="N74" t="n">
-        <v>3.35</v>
+        <v>3.5</v>
       </c>
       <c r="O74" t="n">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P74" t="n">
         <v>1.83</v>
       </c>
       <c r="Q74" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="R74" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="S74" t="n">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="T74" t="n">
-        <v>1.75</v>
+        <v>1.72</v>
       </c>
       <c r="U74" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="V74" t="n">
         <v>1.46</v>
       </c>
       <c r="W74" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="X74" t="n">
         <v>1000</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -14919,19 +14919,19 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="G75" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="H75" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="I75" t="n">
-        <v>2.48</v>
+        <v>2.46</v>
       </c>
       <c r="J75" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="K75" t="n">
         <v>3.55</v>
@@ -14943,40 +14943,40 @@
         <v>1.09</v>
       </c>
       <c r="N75" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="O75" t="n">
         <v>1.39</v>
       </c>
       <c r="P75" t="n">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="Q75" t="n">
-        <v>2.02</v>
+        <v>2.16</v>
       </c>
       <c r="R75" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="S75" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="T75" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U75" t="n">
-        <v>1.98</v>
+        <v>1.96</v>
       </c>
       <c r="V75" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W75" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="X75" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="Y75" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z75" t="n">
         <v>17.5</v>
@@ -14997,19 +14997,19 @@
         <v>34</v>
       </c>
       <c r="AF75" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AG75" t="n">
         <v>18.5</v>
       </c>
       <c r="AH75" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI75" t="n">
         <v>55</v>
       </c>
       <c r="AJ75" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AK75" t="n">
         <v>60</v>
@@ -15021,68 +15021,68 @@
         <v>150</v>
       </c>
       <c r="AN75" t="n">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AO75" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AP75" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AQ75" t="n">
-        <v>6.6</v>
+        <v>7.6</v>
       </c>
       <c r="AR75" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AS75" t="n">
         <v>4.2</v>
       </c>
       <c r="AT75" t="n">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AU75" t="n">
         <v>6.6</v>
       </c>
       <c r="AV75" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW75" t="n">
         <v>20</v>
       </c>
       <c r="AX75" t="n">
-        <v>4.1</v>
+        <v>18</v>
       </c>
       <c r="AY75" t="n">
         <v>13</v>
       </c>
       <c r="AZ75" t="n">
-        <v>13.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA75" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB75" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BC75" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BD75" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE75" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BF75" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BG75" t="n">
-        <v>4.1</v>
+        <v>17.5</v>
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -15143,7 +15143,7 @@
         <v>1.28</v>
       </c>
       <c r="P76" t="n">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="Q76" t="n">
         <v>1.82</v>
@@ -15155,7 +15155,7 @@
         <v>3.1</v>
       </c>
       <c r="T76" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="U76" t="n">
         <v>2.02</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -15313,10 +15313,10 @@
         <v>5.4</v>
       </c>
       <c r="H77" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="I77" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="J77" t="n">
         <v>4.2</v>
@@ -15325,7 +15325,7 @@
         <v>4.3</v>
       </c>
       <c r="L77" t="n">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="M77" t="n">
         <v>1.05</v>
@@ -15355,13 +15355,13 @@
         <v>2.24</v>
       </c>
       <c r="V77" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="W77" t="n">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="X77" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Y77" t="n">
         <v>10.5</v>
@@ -15373,7 +15373,7 @@
         <v>18</v>
       </c>
       <c r="AB77" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AC77" t="n">
         <v>9.4</v>
@@ -15397,13 +15397,13 @@
         <v>29</v>
       </c>
       <c r="AJ77" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AK77" t="n">
         <v>65</v>
       </c>
       <c r="AL77" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM77" t="n">
         <v>85</v>
@@ -15445,13 +15445,13 @@
         <v>18</v>
       </c>
       <c r="AZ77" t="n">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BA77" t="n">
         <v>27</v>
       </c>
       <c r="BB77" t="n">
-        <v>15.5</v>
+        <v>18</v>
       </c>
       <c r="BC77" t="n">
         <v>50</v>
@@ -15460,7 +15460,7 @@
         <v>50</v>
       </c>
       <c r="BE77" t="n">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BF77" t="n">
         <v>46</v>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -15501,22 +15501,22 @@
         </is>
       </c>
       <c r="F78" t="n">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="G78" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="H78" t="n">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I78" t="n">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="J78" t="n">
         <v>3.25</v>
       </c>
       <c r="K78" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="L78" t="n">
         <v>1.41</v>
@@ -15534,7 +15534,7 @@
         <v>1.85</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="R78" t="n">
         <v>1.32</v>
@@ -15543,16 +15543,16 @@
         <v>3.55</v>
       </c>
       <c r="T78" t="n">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U78" t="n">
         <v>2.08</v>
       </c>
       <c r="V78" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W78" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X78" t="n">
         <v>16.5</v>
@@ -15594,7 +15594,7 @@
         <v>40</v>
       </c>
       <c r="AK78" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AL78" t="n">
         <v>50</v>
@@ -15609,40 +15609,40 @@
         <v>50</v>
       </c>
       <c r="AP78" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AQ78" t="n">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AR78" t="n">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="AS78" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="AT78" t="n">
-        <v>7.4</v>
+        <v>8.4</v>
       </c>
       <c r="AU78" t="n">
-        <v>5.9</v>
+        <v>6.8</v>
       </c>
       <c r="AV78" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="AW78" t="n">
         <v>4.2</v>
       </c>
       <c r="AX78" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AY78" t="n">
-        <v>8.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ78" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="BA78" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BB78" t="n">
         <v>4.3</v>
@@ -15657,14 +15657,14 @@
         <v>4.2</v>
       </c>
       <c r="BF78" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BG78" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -15803,7 +15803,7 @@
         <v>34</v>
       </c>
       <c r="AP79" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AQ79" t="n">
         <v>9.4</v>
@@ -15815,7 +15815,7 @@
         <v>42</v>
       </c>
       <c r="AT79" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AU79" t="n">
         <v>6.8</v>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -15889,7 +15889,7 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="G80" t="n">
         <v>3.7</v>
@@ -15898,37 +15898,37 @@
         <v>2.36</v>
       </c>
       <c r="I80" t="n">
-        <v>2.58</v>
+        <v>2.64</v>
       </c>
       <c r="J80" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="K80" t="n">
         <v>3.45</v>
       </c>
       <c r="L80" t="n">
-        <v>1.42</v>
+        <v>1.5</v>
       </c>
       <c r="M80" t="n">
         <v>1.1</v>
       </c>
       <c r="N80" t="n">
-        <v>2.6</v>
+        <v>2.76</v>
       </c>
       <c r="O80" t="n">
         <v>1.44</v>
       </c>
       <c r="P80" t="n">
-        <v>1.65</v>
+        <v>1.62</v>
       </c>
       <c r="Q80" t="n">
         <v>2.3</v>
       </c>
       <c r="R80" t="n">
-        <v>1.24</v>
+        <v>1.23</v>
       </c>
       <c r="S80" t="n">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T80" t="n">
         <v>1.77</v>
@@ -15952,10 +15952,10 @@
         <v>970</v>
       </c>
       <c r="AA80" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AB80" t="n">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC80" t="n">
         <v>8.800000000000001</v>
@@ -15964,10 +15964,10 @@
         <v>14.5</v>
       </c>
       <c r="AE80" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AF80" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG80" t="n">
         <v>970</v>
@@ -15991,16 +15991,16 @@
         <v>170</v>
       </c>
       <c r="AN80" t="n">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AO80" t="n">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AP80" t="n">
-        <v>3.2</v>
+        <v>7.4</v>
       </c>
       <c r="AQ80" t="n">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AR80" t="n">
         <v>11</v>
@@ -16009,40 +16009,40 @@
         <v>3.9</v>
       </c>
       <c r="AT80" t="n">
-        <v>3.25</v>
+        <v>7.8</v>
       </c>
       <c r="AU80" t="n">
         <v>5.5</v>
       </c>
       <c r="AV80" t="n">
-        <v>8.800000000000001</v>
+        <v>3.3</v>
       </c>
       <c r="AW80" t="n">
         <v>3.85</v>
       </c>
       <c r="AX80" t="n">
-        <v>3.75</v>
+        <v>16.5</v>
       </c>
       <c r="AY80" t="n">
         <v>11</v>
       </c>
       <c r="AZ80" t="n">
-        <v>3.65</v>
+        <v>14.5</v>
       </c>
       <c r="BA80" t="n">
         <v>4</v>
       </c>
       <c r="BB80" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BC80" t="n">
         <v>4</v>
       </c>
       <c r="BD80" t="n">
+        <v>4</v>
+      </c>
+      <c r="BE80" t="n">
         <v>4.1</v>
-      </c>
-      <c r="BE80" t="n">
-        <v>4.2</v>
       </c>
       <c r="BF80" t="n">
         <v>4</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -16107,7 +16107,7 @@
         <v>1.09</v>
       </c>
       <c r="N81" t="n">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O81" t="n">
         <v>1.39</v>
@@ -16125,7 +16125,7 @@
         <v>3.9</v>
       </c>
       <c r="T81" t="n">
-        <v>1.94</v>
+        <v>1.92</v>
       </c>
       <c r="U81" t="n">
         <v>1.92</v>
@@ -16246,7 +16246,7 @@
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -16277,10 +16277,10 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="G82" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="H82" t="n">
         <v>1.92</v>
@@ -16307,7 +16307,7 @@
         <v>0</v>
       </c>
       <c r="P82" t="n">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="Q82" t="n">
         <v>1.56</v>
@@ -16340,7 +16340,7 @@
         <v>15</v>
       </c>
       <c r="AA82" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB82" t="n">
         <v>22</v>
@@ -16370,7 +16370,7 @@
         <v>80</v>
       </c>
       <c r="AK82" t="n">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL82" t="n">
         <v>40</v>
@@ -16385,7 +16385,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="AP82" t="n">
-        <v>18.5</v>
+        <v>23</v>
       </c>
       <c r="AQ82" t="n">
         <v>13</v>
@@ -16412,13 +16412,13 @@
         <v>30</v>
       </c>
       <c r="AY82" t="n">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ82" t="n">
         <v>14</v>
       </c>
       <c r="BA82" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB82" t="n">
         <v>34</v>
@@ -16427,20 +16427,20 @@
         <v>34</v>
       </c>
       <c r="BD82" t="n">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BE82" t="n">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="BF82" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BG82" t="n">
         <v>7.8</v>
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -16692,7 +16692,7 @@
         <v>2.12</v>
       </c>
       <c r="O84" t="n">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="P84" t="n">
         <v>1.36</v>
@@ -16710,7 +16710,7 @@
         <v>2.44</v>
       </c>
       <c r="U84" t="n">
-        <v>1.57</v>
+        <v>1.55</v>
       </c>
       <c r="V84" t="n">
         <v>1.68</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -17053,7 +17053,7 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>3</v>
+        <v>2.98</v>
       </c>
       <c r="G86" t="n">
         <v>3.45</v>
@@ -17062,13 +17062,13 @@
         <v>2.38</v>
       </c>
       <c r="I86" t="n">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="J86" t="n">
         <v>3.3</v>
       </c>
       <c r="K86" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L86" t="n">
         <v>1.01</v>
@@ -17101,7 +17101,7 @@
         <v>1.75</v>
       </c>
       <c r="V86" t="n">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="W86" t="n">
         <v>1.38</v>
@@ -17167,7 +17167,7 @@
         <v>2.1</v>
       </c>
       <c r="AR86" t="n">
-        <v>11</v>
+        <v>2.22</v>
       </c>
       <c r="AS86" t="n">
         <v>2.34</v>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -17247,22 +17247,22 @@
         </is>
       </c>
       <c r="F87" t="n">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="G87" t="n">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="H87" t="n">
-        <v>2.14</v>
+        <v>2.22</v>
       </c>
       <c r="I87" t="n">
-        <v>2.34</v>
+        <v>2.44</v>
       </c>
       <c r="J87" t="n">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K87" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L87" t="n">
         <v>1.01</v>
@@ -17271,22 +17271,22 @@
         <v>1.1</v>
       </c>
       <c r="N87" t="n">
-        <v>2.96</v>
+        <v>2.88</v>
       </c>
       <c r="O87" t="n">
         <v>1.43</v>
       </c>
       <c r="P87" t="n">
-        <v>1.56</v>
+        <v>1.65</v>
       </c>
       <c r="Q87" t="n">
         <v>2.28</v>
       </c>
       <c r="R87" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="S87" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="T87" t="n">
         <v>1.94</v>
@@ -17295,16 +17295,16 @@
         <v>1.9</v>
       </c>
       <c r="V87" t="n">
-        <v>1.75</v>
+        <v>1.7</v>
       </c>
       <c r="W87" t="n">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="X87" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="Y87" t="n">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z87" t="n">
         <v>16</v>
@@ -17313,7 +17313,7 @@
         <v>38</v>
       </c>
       <c r="AB87" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AC87" t="n">
         <v>7.6</v>
@@ -17325,10 +17325,10 @@
         <v>34</v>
       </c>
       <c r="AF87" t="n">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AG87" t="n">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AH87" t="n">
         <v>25</v>
@@ -17337,37 +17337,37 @@
         <v>60</v>
       </c>
       <c r="AJ87" t="n">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AK87" t="n">
         <v>70</v>
       </c>
       <c r="AL87" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AM87" t="n">
         <v>1000</v>
       </c>
       <c r="AN87" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AO87" t="n">
         <v>30</v>
       </c>
       <c r="AP87" t="n">
-        <v>3.55</v>
+        <v>9</v>
       </c>
       <c r="AQ87" t="n">
         <v>6</v>
       </c>
       <c r="AR87" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AS87" t="n">
         <v>21</v>
       </c>
       <c r="AT87" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AU87" t="n">
         <v>6.6</v>
@@ -17382,35 +17382,35 @@
         <v>20</v>
       </c>
       <c r="AY87" t="n">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AZ87" t="n">
         <v>18</v>
       </c>
       <c r="BA87" t="n">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BB87" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BC87" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BD87" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BE87" t="n">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BF87" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="BG87" t="n">
         <v>17.5</v>
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -17441,7 +17441,7 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="G88" t="n">
         <v>5.4</v>
@@ -17450,61 +17450,61 @@
         <v>1.96</v>
       </c>
       <c r="I88" t="n">
-        <v>1.99</v>
+        <v>2.06</v>
       </c>
       <c r="J88" t="n">
         <v>3.3</v>
       </c>
       <c r="K88" t="n">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="L88" t="n">
         <v>1.54</v>
       </c>
       <c r="M88" t="n">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="N88" t="n">
-        <v>2.54</v>
+        <v>2.5</v>
       </c>
       <c r="O88" t="n">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="P88" t="n">
-        <v>1.52</v>
+        <v>1.5</v>
       </c>
       <c r="Q88" t="n">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="R88" t="n">
         <v>1.17</v>
       </c>
       <c r="S88" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="T88" t="n">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="U88" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V88" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="W88" t="n">
         <v>1.22</v>
       </c>
       <c r="X88" t="n">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="Y88" t="n">
         <v>6.4</v>
       </c>
       <c r="Z88" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AA88" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AB88" t="n">
         <v>13</v>
@@ -17516,10 +17516,10 @@
         <v>12</v>
       </c>
       <c r="AE88" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AF88" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AG88" t="n">
         <v>23</v>
@@ -17531,25 +17531,25 @@
         <v>70</v>
       </c>
       <c r="AJ88" t="n">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AK88" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AL88" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AM88" t="n">
         <v>300</v>
       </c>
       <c r="AN88" t="n">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="AO88" t="n">
         <v>26</v>
       </c>
       <c r="AP88" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ88" t="n">
         <v>5.6</v>
@@ -17564,47 +17564,47 @@
         <v>10</v>
       </c>
       <c r="AU88" t="n">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AV88" t="n">
         <v>9.6</v>
       </c>
       <c r="AW88" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX88" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AY88" t="n">
         <v>18.5</v>
       </c>
       <c r="AZ88" t="n">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="BA88" t="n">
+        <v>8</v>
+      </c>
+      <c r="BB88" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="BC88" t="n">
         <v>8.4</v>
       </c>
-      <c r="BB88" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="BC88" t="n">
+      <c r="BD88" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="BE88" t="n">
         <v>8.800000000000001</v>
       </c>
-      <c r="BD88" t="n">
-        <v>9</v>
-      </c>
-      <c r="BE88" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BF88" t="n">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="BG88" t="n">
         <v>18.5</v>
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -17638,19 +17638,19 @@
         <v>1.51</v>
       </c>
       <c r="G89" t="n">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="H89" t="n">
-        <v>8.6</v>
+        <v>7.6</v>
       </c>
       <c r="I89" t="n">
         <v>11</v>
       </c>
       <c r="J89" t="n">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K89" t="n">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="L89" t="n">
         <v>1.01</v>
@@ -17659,34 +17659,34 @@
         <v>1.01</v>
       </c>
       <c r="N89" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="O89" t="n">
         <v>1.02</v>
       </c>
       <c r="P89" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="Q89" t="n">
-        <v>2.16</v>
+        <v>2.34</v>
       </c>
       <c r="R89" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S89" t="n">
         <v>3.9</v>
       </c>
       <c r="T89" t="n">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="U89" t="n">
-        <v>1.43</v>
+        <v>1.5</v>
       </c>
       <c r="V89" t="n">
         <v>1.1</v>
       </c>
       <c r="W89" t="n">
-        <v>2.68</v>
+        <v>2.74</v>
       </c>
       <c r="X89" t="n">
         <v>14.5</v>
@@ -17713,7 +17713,7 @@
         <v>1000</v>
       </c>
       <c r="AF89" t="n">
-        <v>970</v>
+        <v>10</v>
       </c>
       <c r="AG89" t="n">
         <v>970</v>
@@ -17728,7 +17728,7 @@
         <v>19</v>
       </c>
       <c r="AK89" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AL89" t="n">
         <v>85</v>
@@ -17737,68 +17737,68 @@
         <v>1000</v>
       </c>
       <c r="AN89" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO89" t="n">
         <v>1000</v>
       </c>
       <c r="AP89" t="n">
-        <v>2.18</v>
+        <v>2.54</v>
       </c>
       <c r="AQ89" t="n">
         <v>14.5</v>
       </c>
       <c r="AR89" t="n">
-        <v>2.56</v>
+        <v>3.05</v>
       </c>
       <c r="AS89" t="n">
-        <v>2.56</v>
+        <v>3.05</v>
       </c>
       <c r="AT89" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="AU89" t="n">
-        <v>2.14</v>
+        <v>2.48</v>
       </c>
       <c r="AV89" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="AW89" t="n">
-        <v>2.56</v>
+        <v>3.05</v>
       </c>
       <c r="AX89" t="n">
-        <v>2.06</v>
+        <v>2.34</v>
       </c>
       <c r="AY89" t="n">
-        <v>2.18</v>
+        <v>2.54</v>
       </c>
       <c r="AZ89" t="n">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="BA89" t="n">
-        <v>2.56</v>
+        <v>3.05</v>
       </c>
       <c r="BB89" t="n">
         <v>10</v>
       </c>
       <c r="BC89" t="n">
-        <v>2.36</v>
+        <v>2.78</v>
       </c>
       <c r="BD89" t="n">
-        <v>2.5</v>
+        <v>2.96</v>
       </c>
       <c r="BE89" t="n">
-        <v>2.56</v>
+        <v>3.05</v>
       </c>
       <c r="BF89" t="n">
-        <v>2.56</v>
+        <v>8.4</v>
       </c>
       <c r="BG89" t="n">
-        <v>2.56</v>
+        <v>3.05</v>
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -18023,7 +18023,7 @@
         </is>
       </c>
       <c r="F91" t="n">
-        <v>2.8</v>
+        <v>2.76</v>
       </c>
       <c r="G91" t="n">
         <v>3</v>
@@ -18038,7 +18038,7 @@
         <v>3.1</v>
       </c>
       <c r="K91" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="L91" t="n">
         <v>1.01</v>
@@ -18047,19 +18047,19 @@
         <v>1.01</v>
       </c>
       <c r="N91" t="n">
-        <v>1.74</v>
+        <v>2.38</v>
       </c>
       <c r="O91" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="P91" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="Q91" t="n">
-        <v>2.28</v>
+        <v>2.22</v>
       </c>
       <c r="R91" t="n">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S91" t="n">
         <v>3.55</v>
@@ -18186,7 +18186,7 @@
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -18574,7 +18574,7 @@
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>
@@ -18614,7 +18614,7 @@
         <v>2.86</v>
       </c>
       <c r="I94" t="n">
-        <v>3.95</v>
+        <v>990</v>
       </c>
       <c r="J94" t="n">
         <v>2.22</v>
@@ -18653,7 +18653,7 @@
         <v>1.11</v>
       </c>
       <c r="V94" t="n">
-        <v>1.39</v>
+        <v>1.38</v>
       </c>
       <c r="W94" t="n">
         <v>1.49</v>
@@ -18768,7 +18768,7 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-04-23 00:30:51</t>
+          <t>2026-04-23 02:50:35</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH94"/>
+  <dimension ref="A1:BH95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -757,7 +757,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="G2" t="n">
         <v>2.12</v>
@@ -769,10 +769,10 @@
         <v>3.7</v>
       </c>
       <c r="J2" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="K2" t="n">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L2" t="n">
         <v>1.01</v>
@@ -802,22 +802,22 @@
         <v>1.52</v>
       </c>
       <c r="U2" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="V2" t="n">
         <v>1.37</v>
       </c>
       <c r="W2" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X2" t="n">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="Y2" t="n">
         <v>22</v>
       </c>
       <c r="Z2" t="n">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA2" t="n">
         <v>1000</v>
@@ -841,7 +841,7 @@
         <v>11.5</v>
       </c>
       <c r="AH2" t="n">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="AI2" t="n">
         <v>38</v>
@@ -874,7 +874,7 @@
         <v>24</v>
       </c>
       <c r="AS2" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT2" t="n">
         <v>13.5</v>
@@ -886,7 +886,7 @@
         <v>13.5</v>
       </c>
       <c r="AW2" t="n">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AX2" t="n">
         <v>15</v>
@@ -920,7 +920,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -975,16 +975,16 @@
         <v>1.06</v>
       </c>
       <c r="N3" t="n">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O3" t="n">
-        <v>1.28</v>
+        <v>1.27</v>
       </c>
       <c r="P3" t="n">
         <v>2.04</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="R3" t="n">
         <v>1.4</v>
@@ -993,10 +993,10 @@
         <v>3.05</v>
       </c>
       <c r="T3" t="n">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="U3" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V3" t="n">
         <v>1.83</v>
@@ -1059,62 +1059,62 @@
         <v>16</v>
       </c>
       <c r="AP3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AQ3" t="n">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AR3" t="n">
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AT3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU3" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV3" t="n">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AW3" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AX3" t="n">
         <v>21</v>
       </c>
       <c r="AY3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="BA3" t="n">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="BB3" t="n">
         <v>4.8</v>
       </c>
       <c r="BC3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BD3" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="BE3" t="n">
         <v>4.8</v>
       </c>
       <c r="BF3" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="BG3" t="n">
         <v>11.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -1145,13 +1145,13 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="G4" t="n">
         <v>3.15</v>
       </c>
       <c r="H4" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="I4" t="n">
         <v>3.2</v>
@@ -1160,7 +1160,7 @@
         <v>2.78</v>
       </c>
       <c r="K4" t="n">
-        <v>3.05</v>
+        <v>3</v>
       </c>
       <c r="L4" t="n">
         <v>1.61</v>
@@ -1214,7 +1214,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AC4" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AD4" t="n">
         <v>17.5</v>
@@ -1256,13 +1256,13 @@
         <v>6.4</v>
       </c>
       <c r="AQ4" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AS4" t="n">
         <v>6.2</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>14</v>
-      </c>
-      <c r="AS4" t="n">
-        <v>5.6</v>
       </c>
       <c r="AT4" t="n">
         <v>7</v>
@@ -1271,44 +1271,44 @@
         <v>6.2</v>
       </c>
       <c r="AV4" t="n">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AW4" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="AX4" t="n">
         <v>16</v>
       </c>
       <c r="AY4" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AZ4" t="n">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA4" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BB4" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BC4" t="n">
-        <v>5.5</v>
+        <v>6</v>
       </c>
       <c r="BD4" t="n">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BE4" t="n">
-        <v>5.9</v>
+        <v>6.4</v>
       </c>
       <c r="BF4" t="n">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BG4" t="n">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -1339,7 +1339,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="G5" t="n">
         <v>2.48</v>
@@ -1381,61 +1381,61 @@
         <v>4.8</v>
       </c>
       <c r="T5" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="U5" t="n">
         <v>1.81</v>
       </c>
       <c r="V5" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W5" t="n">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="X5" t="n">
         <v>10.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="Z5" t="n">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AA5" t="n">
         <v>100</v>
       </c>
       <c r="AB5" t="n">
-        <v>8.800000000000001</v>
+        <v>8</v>
       </c>
       <c r="AC5" t="n">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="AD5" t="n">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AE5" t="n">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF5" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AH5" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI5" t="n">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AJ5" t="n">
         <v>38</v>
       </c>
       <c r="AK5" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL5" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM5" t="n">
         <v>190</v>
@@ -1444,7 +1444,7 @@
         <v>34</v>
       </c>
       <c r="AO5" t="n">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AP5" t="n">
         <v>8</v>
@@ -1453,10 +1453,10 @@
         <v>9.6</v>
       </c>
       <c r="AR5" t="n">
-        <v>5.2</v>
+        <v>6.6</v>
       </c>
       <c r="AS5" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="AT5" t="n">
         <v>6.6</v>
@@ -1468,7 +1468,7 @@
         <v>14</v>
       </c>
       <c r="AW5" t="n">
-        <v>5.2</v>
+        <v>7.4</v>
       </c>
       <c r="AX5" t="n">
         <v>11</v>
@@ -1480,29 +1480,29 @@
         <v>18</v>
       </c>
       <c r="BA5" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="BB5" t="n">
-        <v>5</v>
+        <v>6.8</v>
       </c>
       <c r="BC5" t="n">
-        <v>5.1</v>
+        <v>25</v>
       </c>
       <c r="BD5" t="n">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="BE5" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="BF5" t="n">
-        <v>5.4</v>
+        <v>22</v>
       </c>
       <c r="BG5" t="n">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="G6" t="n">
         <v>1.85</v>
@@ -1545,13 +1545,13 @@
         <v>6</v>
       </c>
       <c r="J6" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K6" t="n">
         <v>4.2</v>
       </c>
       <c r="L6" t="n">
-        <v>1.36</v>
+        <v>1.4</v>
       </c>
       <c r="M6" t="n">
         <v>1.07</v>
@@ -1563,7 +1563,7 @@
         <v>1.33</v>
       </c>
       <c r="P6" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q6" t="n">
         <v>1.96</v>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -1890,7 +1890,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -1966,7 +1966,7 @@
         <v>1.64</v>
       </c>
       <c r="U8" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="V8" t="n">
         <v>1.51</v>
@@ -2050,7 +2050,7 @@
         <v>10.5</v>
       </c>
       <c r="AW8" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AX8" t="n">
         <v>15.5</v>
@@ -2068,10 +2068,10 @@
         <v>7</v>
       </c>
       <c r="BC8" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="BD8" t="n">
         <v>7</v>
-      </c>
-      <c r="BD8" t="n">
-        <v>7.2</v>
       </c>
       <c r="BE8" t="n">
         <v>7.6</v>
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -2115,31 +2115,31 @@
         </is>
       </c>
       <c r="F9" t="n">
-        <v>1.04</v>
+        <v>1.66</v>
       </c>
       <c r="G9" t="n">
-        <v>1000</v>
+        <v>1.75</v>
       </c>
       <c r="H9" t="n">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="I9" t="n">
         <v>1000</v>
       </c>
       <c r="J9" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="K9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="L9" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M9" t="n">
         <v>1.02</v>
       </c>
-      <c r="K9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.01</v>
-      </c>
       <c r="N9" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O9" t="n">
         <v>1.14</v>
@@ -2163,10 +2163,10 @@
         <v>1.01</v>
       </c>
       <c r="V9" t="n">
-        <v>1.01</v>
+        <v>1.17</v>
       </c>
       <c r="W9" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="X9" t="n">
         <v>1000</v>
@@ -2278,7 +2278,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -2312,16 +2312,16 @@
         <v>1.04</v>
       </c>
       <c r="G10" t="n">
-        <v>1000</v>
+        <v>1.8</v>
       </c>
       <c r="H10" t="n">
-        <v>1.04</v>
+        <v>2.3</v>
       </c>
       <c r="I10" t="n">
         <v>1000</v>
       </c>
       <c r="J10" t="n">
-        <v>1.02</v>
+        <v>2.3</v>
       </c>
       <c r="K10" t="n">
         <v>1000</v>
@@ -2333,7 +2333,7 @@
         <v>1.01</v>
       </c>
       <c r="N10" t="n">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="O10" t="n">
         <v>1.11</v>
@@ -2360,7 +2360,7 @@
         <v>1.01</v>
       </c>
       <c r="W10" t="n">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="X10" t="n">
         <v>1000</v>
@@ -2472,7 +2472,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -2536,13 +2536,13 @@
         <v>2.4</v>
       </c>
       <c r="Q11" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="R11" t="n">
         <v>1.56</v>
       </c>
       <c r="S11" t="n">
-        <v>2.44</v>
+        <v>2.5</v>
       </c>
       <c r="T11" t="n">
         <v>1.56</v>
@@ -2620,7 +2620,7 @@
         <v>7.2</v>
       </c>
       <c r="AS11" t="n">
-        <v>3.35</v>
+        <v>4.5</v>
       </c>
       <c r="AT11" t="n">
         <v>6.2</v>
@@ -2656,7 +2656,7 @@
         <v>8</v>
       </c>
       <c r="BE11" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="BF11" t="n">
         <v>11</v>
@@ -2666,7 +2666,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -2697,10 +2697,10 @@
         </is>
       </c>
       <c r="F12" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="G12" t="n">
-        <v>2.48</v>
+        <v>2.3</v>
       </c>
       <c r="H12" t="n">
         <v>3.35</v>
@@ -2715,152 +2715,152 @@
         <v>4</v>
       </c>
       <c r="L12" t="n">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="M12" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N12" t="n">
-        <v>1.95</v>
+        <v>3.85</v>
       </c>
       <c r="O12" t="n">
         <v>1.29</v>
       </c>
       <c r="P12" t="n">
-        <v>1.95</v>
+        <v>1.98</v>
       </c>
       <c r="Q12" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="R12" t="n">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="S12" t="n">
-        <v>1.84</v>
+        <v>3.2</v>
       </c>
       <c r="T12" t="n">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="U12" t="n">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V12" t="n">
         <v>1.3</v>
       </c>
       <c r="W12" t="n">
-        <v>1.66</v>
+        <v>1.76</v>
       </c>
       <c r="X12" t="n">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Y12" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Z12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA12" t="n">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AB12" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC12" t="n">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD12" t="n">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AE12" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AF12" t="n">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AG12" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH12" t="n">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI12" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ12" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK12" t="n">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL12" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM12" t="n">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN12" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AO12" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP12" t="n">
-        <v>1.03</v>
+        <v>12</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.03</v>
+        <v>20</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="AT12" t="n">
-        <v>1.03</v>
+        <v>8</v>
       </c>
       <c r="AU12" t="n">
-        <v>1.03</v>
+        <v>6.4</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="AW12" t="n">
-        <v>1.03</v>
+        <v>4.8</v>
       </c>
       <c r="AX12" t="n">
-        <v>1.03</v>
+        <v>11</v>
       </c>
       <c r="AY12" t="n">
-        <v>1.03</v>
+        <v>8.4</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.03</v>
+        <v>13</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.03</v>
+        <v>4.9</v>
       </c>
       <c r="BB12" t="n">
-        <v>1.03</v>
+        <v>21</v>
       </c>
       <c r="BC12" t="n">
-        <v>1.03</v>
+        <v>17.5</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.03</v>
+        <v>4.7</v>
       </c>
       <c r="BE12" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BG12" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -2921,10 +2921,10 @@
         <v>1.26</v>
       </c>
       <c r="P13" t="n">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q13" t="n">
-        <v>1.76</v>
+        <v>1.79</v>
       </c>
       <c r="R13" t="n">
         <v>1.43</v>
@@ -3054,7 +3054,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -3109,13 +3109,13 @@
         <v>1.01</v>
       </c>
       <c r="N14" t="n">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="O14" t="n">
         <v>1.3</v>
       </c>
       <c r="P14" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="Q14" t="n">
         <v>1.3</v>
@@ -3124,7 +3124,7 @@
         <v>1.24</v>
       </c>
       <c r="S14" t="n">
-        <v>1.3</v>
+        <v>1.81</v>
       </c>
       <c r="T14" t="n">
         <v>1.01</v>
@@ -3248,7 +3248,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -3300,7 +3300,7 @@
         <v>1.01</v>
       </c>
       <c r="M15" t="n">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N15" t="n">
         <v>1.01</v>
@@ -3442,7 +3442,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -3473,19 +3473,19 @@
         </is>
       </c>
       <c r="F16" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="G16" t="n">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="H16" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I16" t="n">
         <v>4.8</v>
       </c>
       <c r="J16" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="K16" t="n">
         <v>4.4</v>
@@ -3494,37 +3494,37 @@
         <v>1.01</v>
       </c>
       <c r="M16" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N16" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="O16" t="n">
         <v>1.21</v>
       </c>
       <c r="P16" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="R16" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="U16" t="n">
         <v>2.36</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="R16" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="S16" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="T16" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="U16" t="n">
-        <v>2.16</v>
       </c>
       <c r="V16" t="n">
         <v>1.26</v>
       </c>
       <c r="W16" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="X16" t="n">
         <v>27</v>
@@ -3539,10 +3539,10 @@
         <v>110</v>
       </c>
       <c r="AB16" t="n">
-        <v>13.5</v>
+        <v>12.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AD16" t="n">
         <v>19.5</v>
@@ -3554,7 +3554,7 @@
         <v>14</v>
       </c>
       <c r="AG16" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH16" t="n">
         <v>17.5</v>
@@ -3575,34 +3575,34 @@
         <v>70</v>
       </c>
       <c r="AN16" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AO16" t="n">
         <v>46</v>
       </c>
       <c r="AP16" t="n">
-        <v>19</v>
+        <v>6.4</v>
       </c>
       <c r="AQ16" t="n">
         <v>18.5</v>
       </c>
       <c r="AR16" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AS16" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AT16" t="n">
         <v>10.5</v>
       </c>
       <c r="AU16" t="n">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV16" t="n">
         <v>15.5</v>
       </c>
       <c r="AW16" t="n">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AX16" t="n">
         <v>11</v>
@@ -3614,7 +3614,7 @@
         <v>14</v>
       </c>
       <c r="BA16" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BB16" t="n">
         <v>17</v>
@@ -3623,20 +3623,20 @@
         <v>14</v>
       </c>
       <c r="BD16" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BE16" t="n">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="BF16" t="n">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="BG16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="F17" t="n">
-        <v>1.04</v>
+        <v>1.81</v>
       </c>
       <c r="G17" t="n">
         <v>1000</v>
@@ -3676,10 +3676,10 @@
         <v>1.04</v>
       </c>
       <c r="I17" t="n">
-        <v>1000</v>
+        <v>2.3</v>
       </c>
       <c r="J17" t="n">
-        <v>1.02</v>
+        <v>1.8</v>
       </c>
       <c r="K17" t="n">
         <v>1000</v>
@@ -3694,19 +3694,19 @@
         <v>1.01</v>
       </c>
       <c r="O17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="P17" t="n">
         <v>1.25</v>
       </c>
       <c r="Q17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="R17" t="n">
         <v>1.24</v>
       </c>
       <c r="S17" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="T17" t="n">
         <v>1.01</v>
@@ -3715,7 +3715,7 @@
         <v>1.01</v>
       </c>
       <c r="V17" t="n">
-        <v>1.01</v>
+        <v>1.77</v>
       </c>
       <c r="W17" t="n">
         <v>1.01</v>
@@ -3830,7 +3830,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -3864,10 +3864,10 @@
         <v>1.61</v>
       </c>
       <c r="G18" t="n">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="H18" t="n">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="I18" t="n">
         <v>7.6</v>
@@ -3876,7 +3876,7 @@
         <v>4</v>
       </c>
       <c r="K18" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="L18" t="n">
         <v>1.01</v>
@@ -3912,7 +3912,7 @@
         <v>1.16</v>
       </c>
       <c r="W18" t="n">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="X18" t="n">
         <v>19</v>
@@ -4024,7 +4024,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -4055,7 +4055,7 @@
         </is>
       </c>
       <c r="F19" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G19" t="n">
         <v>2.36</v>
@@ -4064,13 +4064,13 @@
         <v>3.1</v>
       </c>
       <c r="I19" t="n">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="J19" t="n">
         <v>3.7</v>
       </c>
       <c r="K19" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L19" t="n">
         <v>1.01</v>
@@ -4079,13 +4079,13 @@
         <v>1.03</v>
       </c>
       <c r="N19" t="n">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="O19" t="n">
         <v>1.3</v>
       </c>
       <c r="P19" t="n">
-        <v>1.81</v>
+        <v>1.98</v>
       </c>
       <c r="Q19" t="n">
         <v>1.81</v>
@@ -4097,13 +4097,13 @@
         <v>2.92</v>
       </c>
       <c r="T19" t="n">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="U19" t="n">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V19" t="n">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="W19" t="n">
         <v>1.73</v>
@@ -4218,7 +4218,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -4249,170 +4249,170 @@
         </is>
       </c>
       <c r="F20" t="n">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="G20" t="n">
-        <v>1.91</v>
+        <v>1.89</v>
       </c>
       <c r="H20" t="n">
-        <v>3.75</v>
+        <v>4.3</v>
       </c>
       <c r="I20" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="J20" t="n">
+        <v>3.95</v>
+      </c>
+      <c r="K20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="M20" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="N20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="O20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="P20" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="U20" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="W20" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="X20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG20" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO20" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AQ20" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="AR20" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="AS20" t="n">
+        <v>5</v>
+      </c>
+      <c r="AT20" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU20" t="n">
+        <v>7.8</v>
+      </c>
+      <c r="AV20" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="AW20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AX20" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY20" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ20" t="n">
+        <v>13</v>
+      </c>
+      <c r="BA20" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BB20" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="BC20" t="n">
+        <v>13</v>
+      </c>
+      <c r="BD20" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="BE20" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="BF20" t="n">
         <v>6.6</v>
       </c>
-      <c r="J20" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="K20" t="n">
-        <v>7.8</v>
-      </c>
-      <c r="L20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M20" t="n">
-        <v>1.02</v>
-      </c>
-      <c r="N20" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="O20" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="P20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="S20" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="T20" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="W20" t="n">
-        <v>2.08</v>
-      </c>
-      <c r="X20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO20" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BC20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BD20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BE20" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BF20" t="n">
-        <v>1.01</v>
-      </c>
       <c r="BG20" t="n">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -4449,7 +4449,7 @@
         <v>6</v>
       </c>
       <c r="H21" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="I21" t="n">
         <v>1.9</v>
@@ -4470,22 +4470,22 @@
         <v>3.4</v>
       </c>
       <c r="O21" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P21" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="Q21" t="n">
         <v>1.98</v>
       </c>
       <c r="R21" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="S21" t="n">
         <v>3.55</v>
       </c>
       <c r="T21" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="U21" t="n">
         <v>1.92</v>
@@ -4524,10 +4524,10 @@
         <v>50</v>
       </c>
       <c r="AG21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH21" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AI21" t="n">
         <v>48</v>
@@ -4587,26 +4587,26 @@
         <v>4.2</v>
       </c>
       <c r="BB21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BC21" t="n">
         <v>4.2</v>
       </c>
-      <c r="BC21" t="n">
-        <v>4.1</v>
-      </c>
       <c r="BD21" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="BE21" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="BF21" t="n">
         <v>4.2</v>
-      </c>
-      <c r="BF21" t="n">
-        <v>4.1</v>
       </c>
       <c r="BG21" t="n">
         <v>9.6</v>
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -4670,7 +4670,7 @@
         <v>2.14</v>
       </c>
       <c r="Q22" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R22" t="n">
         <v>1.44</v>
@@ -4754,7 +4754,7 @@
         <v>12</v>
       </c>
       <c r="AS22" t="n">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AT22" t="n">
         <v>11.5</v>
@@ -4778,16 +4778,16 @@
         <v>12.5</v>
       </c>
       <c r="BA22" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BB22" t="n">
         <v>5</v>
       </c>
       <c r="BC22" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="BD22" t="n">
         <v>5.1</v>
-      </c>
-      <c r="BD22" t="n">
-        <v>5</v>
       </c>
       <c r="BE22" t="n">
         <v>5</v>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -4831,64 +4831,64 @@
         </is>
       </c>
       <c r="F23" t="n">
-        <v>1.69</v>
+        <v>1.93</v>
       </c>
       <c r="G23" t="n">
-        <v>2.46</v>
+        <v>2.16</v>
       </c>
       <c r="H23" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="I23" t="n">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="J23" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="K23" t="n">
-        <v>13.5</v>
+        <v>950</v>
       </c>
       <c r="L23" t="n">
         <v>1.01</v>
       </c>
       <c r="M23" t="n">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N23" t="n">
-        <v>1.42</v>
+        <v>2.24</v>
       </c>
       <c r="O23" t="n">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P23" t="n">
-        <v>1.41</v>
+        <v>2.22</v>
       </c>
       <c r="Q23" t="n">
-        <v>1.55</v>
+        <v>1.64</v>
       </c>
       <c r="R23" t="n">
-        <v>1.41</v>
+        <v>1.49</v>
       </c>
       <c r="S23" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="T23" t="n">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="U23" t="n">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="V23" t="n">
-        <v>1.26</v>
+        <v>1.32</v>
       </c>
       <c r="W23" t="n">
-        <v>1.68</v>
+        <v>1.86</v>
       </c>
       <c r="X23" t="n">
         <v>1000</v>
       </c>
       <c r="Y23" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="Z23" t="n">
         <v>40</v>
@@ -4903,19 +4903,19 @@
         <v>970</v>
       </c>
       <c r="AD23" t="n">
-        <v>22</v>
+        <v>970</v>
       </c>
       <c r="AE23" t="n">
         <v>1000</v>
       </c>
       <c r="AF23" t="n">
-        <v>20</v>
+        <v>970</v>
       </c>
       <c r="AG23" t="n">
         <v>970</v>
       </c>
       <c r="AH23" t="n">
-        <v>23</v>
+        <v>970</v>
       </c>
       <c r="AI23" t="n">
         <v>1000</v>
@@ -4939,62 +4939,62 @@
         <v>1000</v>
       </c>
       <c r="AP23" t="n">
-        <v>2.2</v>
+        <v>2.36</v>
       </c>
       <c r="AQ23" t="n">
-        <v>2.02</v>
+        <v>2.36</v>
       </c>
       <c r="AR23" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="AS23" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="AT23" t="n">
-        <v>1.94</v>
+        <v>2.26</v>
       </c>
       <c r="AU23" t="n">
-        <v>1.88</v>
+        <v>3.2</v>
       </c>
       <c r="AV23" t="n">
-        <v>2</v>
+        <v>2.36</v>
       </c>
       <c r="AW23" t="n">
-        <v>2.2</v>
+        <v>2.5</v>
       </c>
       <c r="AX23" t="n">
-        <v>1.99</v>
+        <v>2.3</v>
       </c>
       <c r="AY23" t="n">
-        <v>1.94</v>
+        <v>3.1</v>
       </c>
       <c r="AZ23" t="n">
-        <v>2.02</v>
+        <v>2.36</v>
       </c>
       <c r="BA23" t="n">
-        <v>2.2</v>
+        <v>2.48</v>
       </c>
       <c r="BB23" t="n">
-        <v>2.08</v>
+        <v>2.42</v>
       </c>
       <c r="BC23" t="n">
-        <v>2.06</v>
+        <v>2.38</v>
       </c>
       <c r="BD23" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="BE23" t="n">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="BF23" t="n">
-        <v>1.94</v>
+        <v>3.05</v>
       </c>
       <c r="BG23" t="n">
-        <v>2.2</v>
+        <v>3.7</v>
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -5025,22 +5025,22 @@
         </is>
       </c>
       <c r="F24" t="n">
-        <v>2.62</v>
+        <v>2.26</v>
       </c>
       <c r="G24" t="n">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="H24" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="I24" t="n">
-        <v>2.96</v>
+        <v>3.15</v>
       </c>
       <c r="J24" t="n">
         <v>3.55</v>
       </c>
       <c r="K24" t="n">
-        <v>5.5</v>
+        <v>950</v>
       </c>
       <c r="L24" t="n">
         <v>1.01</v>
@@ -5055,16 +5055,16 @@
         <v>1.27</v>
       </c>
       <c r="P24" t="n">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="Q24" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="R24" t="n">
         <v>1.18</v>
       </c>
       <c r="S24" t="n">
-        <v>1.76</v>
+        <v>2.74</v>
       </c>
       <c r="T24" t="n">
         <v>1.01</v>
@@ -5073,10 +5073,10 @@
         <v>1.01</v>
       </c>
       <c r="V24" t="n">
-        <v>1.51</v>
+        <v>1.47</v>
       </c>
       <c r="W24" t="n">
-        <v>1.45</v>
+        <v>1.47</v>
       </c>
       <c r="X24" t="n">
         <v>1000</v>
@@ -5188,7 +5188,7 @@
       </c>
       <c r="BH24" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -5382,7 +5382,7 @@
       </c>
       <c r="BH25" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -5413,22 +5413,22 @@
         </is>
       </c>
       <c r="F26" t="n">
-        <v>2.12</v>
+        <v>2.36</v>
       </c>
       <c r="G26" t="n">
-        <v>1000</v>
+        <v>2.9</v>
       </c>
       <c r="H26" t="n">
-        <v>1.04</v>
+        <v>2.86</v>
       </c>
       <c r="I26" t="n">
-        <v>1000</v>
+        <v>3.15</v>
       </c>
       <c r="J26" t="n">
         <v>3.65</v>
       </c>
       <c r="K26" t="n">
-        <v>6.6</v>
+        <v>4</v>
       </c>
       <c r="L26" t="n">
         <v>0</v>
@@ -5576,7 +5576,7 @@
       </c>
       <c r="BH26" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -5607,22 +5607,22 @@
         </is>
       </c>
       <c r="F27" t="n">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="G27" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="H27" t="n">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="I27" t="n">
         <v>3.45</v>
       </c>
       <c r="J27" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="K27" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L27" t="n">
         <v>0</v>
@@ -5770,7 +5770,7 @@
       </c>
       <c r="BH27" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -5837,7 +5837,7 @@
         <v>1.76</v>
       </c>
       <c r="R28" t="n">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="S28" t="n">
         <v>2.88</v>
@@ -5951,7 +5951,7 @@
         <v>20</v>
       </c>
       <c r="BD28" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE28" t="n">
         <v>4.2</v>
@@ -5964,7 +5964,7 @@
       </c>
       <c r="BH28" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -5995,7 +5995,7 @@
         </is>
       </c>
       <c r="F29" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="G29" t="n">
         <v>1.76</v>
@@ -6046,7 +6046,7 @@
         <v>1.2</v>
       </c>
       <c r="W29" t="n">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="X29" t="n">
         <v>22</v>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="BH29" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
         <v>1.01</v>
       </c>
       <c r="M30" t="n">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N30" t="n">
         <v>1.01</v>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="BH30" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -6386,34 +6386,34 @@
         <v>1.63</v>
       </c>
       <c r="G31" t="n">
-        <v>2.04</v>
+        <v>1.95</v>
       </c>
       <c r="H31" t="n">
-        <v>3.9</v>
+        <v>4.3</v>
       </c>
       <c r="I31" t="n">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="J31" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K31" t="n">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="L31" t="n">
         <v>1.01</v>
       </c>
       <c r="M31" t="n">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N31" t="n">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="O31" t="n">
         <v>1.22</v>
       </c>
       <c r="P31" t="n">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="Q31" t="n">
         <v>1.66</v>
@@ -6425,16 +6425,16 @@
         <v>2.58</v>
       </c>
       <c r="T31" t="n">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="U31" t="n">
         <v>1.94</v>
       </c>
       <c r="V31" t="n">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W31" t="n">
-        <v>1.96</v>
+        <v>2.04</v>
       </c>
       <c r="X31" t="n">
         <v>1000</v>
@@ -6546,7 +6546,7 @@
       </c>
       <c r="BH31" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -6740,7 +6740,7 @@
       </c>
       <c r="BH32" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -6774,7 +6774,7 @@
         <v>3.6</v>
       </c>
       <c r="G33" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H33" t="n">
         <v>2.48</v>
@@ -6801,7 +6801,7 @@
         <v>1.78</v>
       </c>
       <c r="P33" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="Q33" t="n">
         <v>3.4</v>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="BH33" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -6968,13 +6968,13 @@
         <v>1.75</v>
       </c>
       <c r="G34" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H34" t="n">
         <v>5.2</v>
       </c>
       <c r="I34" t="n">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="J34" t="n">
         <v>3.8</v>
@@ -7128,7 +7128,7 @@
       </c>
       <c r="BH34" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -7192,7 +7192,7 @@
         <v>2.26</v>
       </c>
       <c r="Q35" t="n">
-        <v>1.59</v>
+        <v>1.67</v>
       </c>
       <c r="R35" t="n">
         <v>1.44</v>
@@ -7207,7 +7207,7 @@
         <v>1.01</v>
       </c>
       <c r="V35" t="n">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="W35" t="n">
         <v>1.33</v>
@@ -7322,7 +7322,7 @@
       </c>
       <c r="BH35" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -7516,7 +7516,7 @@
       </c>
       <c r="BH36" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -7550,7 +7550,7 @@
         <v>1.48</v>
       </c>
       <c r="G37" t="n">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="H37" t="n">
         <v>6.2</v>
@@ -7559,31 +7559,31 @@
         <v>8</v>
       </c>
       <c r="J37" t="n">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="K37" t="n">
-        <v>6.2</v>
+        <v>5.6</v>
       </c>
       <c r="L37" t="n">
         <v>1.01</v>
       </c>
       <c r="M37" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N37" t="n">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="O37" t="n">
         <v>1.32</v>
       </c>
       <c r="P37" t="n">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="Q37" t="n">
         <v>1.85</v>
       </c>
       <c r="R37" t="n">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="S37" t="n">
         <v>3.35</v>
@@ -7592,7 +7592,7 @@
         <v>1.86</v>
       </c>
       <c r="U37" t="n">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="V37" t="n">
         <v>1.14</v>
@@ -7601,7 +7601,7 @@
         <v>2.72</v>
       </c>
       <c r="X37" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="Y37" t="n">
         <v>22</v>
@@ -7625,7 +7625,7 @@
         <v>120</v>
       </c>
       <c r="AF37" t="n">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AG37" t="n">
         <v>10.5</v>
@@ -7652,10 +7652,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AO37" t="n">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="AP37" t="n">
-        <v>15.5</v>
+        <v>5.3</v>
       </c>
       <c r="AQ37" t="n">
         <v>5.4</v>
@@ -7676,13 +7676,13 @@
         <v>5.7</v>
       </c>
       <c r="AW37" t="n">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AX37" t="n">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AY37" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="AZ37" t="n">
         <v>6</v>
@@ -7710,7 +7710,7 @@
       </c>
       <c r="BH37" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -7741,170 +7741,170 @@
         </is>
       </c>
       <c r="F38" t="n">
-        <v>1.47</v>
+        <v>1.52</v>
       </c>
       <c r="G38" t="n">
-        <v>1.56</v>
+        <v>1.61</v>
       </c>
       <c r="H38" t="n">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="I38" t="n">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="J38" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K38" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M38" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="N38" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="O38" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="P38" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Q38" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="R38" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S38" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="V38" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="W38" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="X38" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="Y38" t="n">
+        <v>25</v>
+      </c>
+      <c r="Z38" t="n">
+        <v>80</v>
+      </c>
+      <c r="AA38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB38" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AC38" t="n">
+        <v>11</v>
+      </c>
+      <c r="AD38" t="n">
+        <v>36</v>
+      </c>
+      <c r="AE38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF38" t="n">
+        <v>9.4</v>
+      </c>
+      <c r="AG38" t="n">
+        <v>12</v>
+      </c>
+      <c r="AH38" t="n">
+        <v>32</v>
+      </c>
+      <c r="AI38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ38" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AK38" t="n">
+        <v>22</v>
+      </c>
+      <c r="AL38" t="n">
+        <v>55</v>
+      </c>
+      <c r="AM38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>12.5</v>
+      </c>
+      <c r="AO38" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP38" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AQ38" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AR38" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="AS38" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AT38" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AU38" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AV38" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="AW38" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="AX38" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AY38" t="n">
+        <v>8</v>
+      </c>
+      <c r="AZ38" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="BA38" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="BB38" t="n">
         <v>10.5</v>
       </c>
-      <c r="J38" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K38" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="L38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="M38" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="N38" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="O38" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="P38" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q38" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="R38" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="S38" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="U38" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="V38" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="W38" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="X38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Y38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="Z38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AA38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AB38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AC38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AD38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AE38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AF38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AG38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AH38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AI38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AJ38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AK38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AL38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AM38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AN38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AO38" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AQ38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AR38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AS38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AT38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AU38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AV38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AW38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AX38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AY38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AZ38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BA38" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="BB38" t="n">
-        <v>1.03</v>
-      </c>
       <c r="BC38" t="n">
-        <v>1.03</v>
+        <v>14.5</v>
       </c>
       <c r="BD38" t="n">
-        <v>1.03</v>
+        <v>5</v>
       </c>
       <c r="BE38" t="n">
-        <v>1.03</v>
+        <v>5.3</v>
       </c>
       <c r="BF38" t="n">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BG38" t="n">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BH38" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -7935,22 +7935,22 @@
         </is>
       </c>
       <c r="F39" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="G39" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="H39" t="n">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="I39" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="J39" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="K39" t="n">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="L39" t="n">
         <v>1.01</v>
@@ -7959,34 +7959,34 @@
         <v>1.01</v>
       </c>
       <c r="N39" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="O39" t="n">
-        <v>1.29</v>
+        <v>1.38</v>
       </c>
       <c r="P39" t="n">
-        <v>1.85</v>
+        <v>1.69</v>
       </c>
       <c r="Q39" t="n">
-        <v>1.99</v>
+        <v>2.22</v>
       </c>
       <c r="R39" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="S39" t="n">
-        <v>1.99</v>
+        <v>3.5</v>
       </c>
       <c r="T39" t="n">
-        <v>1.01</v>
+        <v>1.74</v>
       </c>
       <c r="U39" t="n">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="V39" t="n">
-        <v>1.55</v>
+        <v>1.61</v>
       </c>
       <c r="W39" t="n">
-        <v>1.36</v>
+        <v>1.34</v>
       </c>
       <c r="X39" t="n">
         <v>1000</v>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="BH39" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -8129,19 +8129,19 @@
         </is>
       </c>
       <c r="F40" t="n">
-        <v>2.28</v>
+        <v>2.42</v>
       </c>
       <c r="G40" t="n">
-        <v>2.8</v>
+        <v>2.72</v>
       </c>
       <c r="H40" t="n">
         <v>3.1</v>
       </c>
       <c r="I40" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J40" t="n">
-        <v>2.88</v>
+        <v>3.05</v>
       </c>
       <c r="K40" t="n">
         <v>3.55</v>
@@ -8153,7 +8153,7 @@
         <v>1.01</v>
       </c>
       <c r="N40" t="n">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="O40" t="n">
         <v>1.38</v>
@@ -8177,10 +8177,10 @@
         <v>1.11</v>
       </c>
       <c r="V40" t="n">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="W40" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="X40" t="n">
         <v>1000</v>
@@ -8292,7 +8292,7 @@
       </c>
       <c r="BH40" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -8323,10 +8323,10 @@
         </is>
       </c>
       <c r="F41" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="G41" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="H41" t="n">
         <v>7</v>
@@ -8338,7 +8338,7 @@
         <v>4</v>
       </c>
       <c r="K41" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L41" t="n">
         <v>1.01</v>
@@ -8486,7 +8486,7 @@
       </c>
       <c r="BH41" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -8523,7 +8523,7 @@
         <v>1.75</v>
       </c>
       <c r="H42" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="I42" t="n">
         <v>7</v>
@@ -8559,10 +8559,10 @@
         <v>3.25</v>
       </c>
       <c r="T42" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="U42" t="n">
         <v>1.77</v>
-      </c>
-      <c r="U42" t="n">
-        <v>1.78</v>
       </c>
       <c r="V42" t="n">
         <v>1.16</v>
@@ -8577,7 +8577,7 @@
         <v>24</v>
       </c>
       <c r="Z42" t="n">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AA42" t="n">
         <v>210</v>
@@ -8634,7 +8634,7 @@
         <v>4.1</v>
       </c>
       <c r="AS42" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT42" t="n">
         <v>6</v>
@@ -8680,7 +8680,7 @@
       </c>
       <c r="BH42" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -8732,31 +8732,31 @@
         <v>1.01</v>
       </c>
       <c r="M43" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N43" t="n">
-        <v>2.06</v>
+        <v>4.1</v>
       </c>
       <c r="O43" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P43" t="n">
         <v>2.06</v>
       </c>
       <c r="Q43" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="R43" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="S43" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T43" t="n">
         <v>1.66</v>
       </c>
-      <c r="R43" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="S43" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="T43" t="n">
-        <v>1.01</v>
-      </c>
       <c r="U43" t="n">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="V43" t="n">
         <v>1.6</v>
@@ -8765,116 +8765,116 @@
         <v>1.46</v>
       </c>
       <c r="X43" t="n">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y43" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Z43" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA43" t="n">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AB43" t="n">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AC43" t="n">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD43" t="n">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE43" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AF43" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AG43" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH43" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI43" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AJ43" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK43" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL43" t="n">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM43" t="n">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN43" t="n">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AO43" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AP43" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AQ43" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR43" t="n">
-        <v>1.03</v>
+        <v>12.5</v>
       </c>
       <c r="AS43" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="AT43" t="n">
-        <v>1.03</v>
+        <v>10</v>
       </c>
       <c r="AU43" t="n">
-        <v>1.03</v>
+        <v>6.2</v>
       </c>
       <c r="AV43" t="n">
-        <v>1.03</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AW43" t="n">
-        <v>1.03</v>
+        <v>18.5</v>
       </c>
       <c r="AX43" t="n">
-        <v>1.03</v>
+        <v>15.5</v>
       </c>
       <c r="AY43" t="n">
-        <v>1.03</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ43" t="n">
-        <v>1.03</v>
+        <v>11.5</v>
       </c>
       <c r="BA43" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BB43" t="n">
-        <v>1.03</v>
+        <v>3.95</v>
       </c>
       <c r="BC43" t="n">
-        <v>1.03</v>
+        <v>3.85</v>
       </c>
       <c r="BD43" t="n">
-        <v>1.03</v>
+        <v>3.9</v>
       </c>
       <c r="BE43" t="n">
-        <v>1.03</v>
+        <v>4</v>
       </c>
       <c r="BF43" t="n">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BG43" t="n">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BH43" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -8905,7 +8905,7 @@
         </is>
       </c>
       <c r="F44" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="G44" t="n">
         <v>2.06</v>
@@ -8914,31 +8914,31 @@
         <v>4.2</v>
       </c>
       <c r="I44" t="n">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="J44" t="n">
         <v>3.35</v>
       </c>
       <c r="K44" t="n">
-        <v>4.9</v>
+        <v>5.4</v>
       </c>
       <c r="L44" t="n">
         <v>1.01</v>
       </c>
       <c r="M44" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N44" t="n">
-        <v>2.52</v>
+        <v>2.62</v>
       </c>
       <c r="O44" t="n">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P44" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q44" t="n">
-        <v>1.84</v>
+        <v>1.9</v>
       </c>
       <c r="R44" t="n">
         <v>1.27</v>
@@ -8953,7 +8953,7 @@
         <v>1.11</v>
       </c>
       <c r="V44" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="W44" t="n">
         <v>1.94</v>
@@ -9068,7 +9068,7 @@
       </c>
       <c r="BH44" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -9114,16 +9114,16 @@
         <v>3.25</v>
       </c>
       <c r="K45" t="n">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="L45" t="n">
         <v>1.01</v>
       </c>
       <c r="M45" t="n">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N45" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="O45" t="n">
         <v>1.4</v>
@@ -9132,19 +9132,19 @@
         <v>1.73</v>
       </c>
       <c r="Q45" t="n">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="R45" t="n">
         <v>1.27</v>
       </c>
       <c r="S45" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="T45" t="n">
         <v>1.89</v>
       </c>
       <c r="U45" t="n">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="V45" t="n">
         <v>1.3</v>
@@ -9198,7 +9198,7 @@
         <v>44</v>
       </c>
       <c r="AM45" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AN45" t="n">
         <v>24</v>
@@ -9262,7 +9262,7 @@
       </c>
       <c r="BH45" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -9302,7 +9302,7 @@
         <v>2</v>
       </c>
       <c r="I46" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="J46" t="n">
         <v>2.9</v>
@@ -9338,10 +9338,10 @@
         <v>1.01</v>
       </c>
       <c r="U46" t="n">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="V46" t="n">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="W46" t="n">
         <v>1.25</v>
@@ -9456,7 +9456,7 @@
       </c>
       <c r="BH46" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -9487,16 +9487,16 @@
         </is>
       </c>
       <c r="F47" t="n">
-        <v>2.64</v>
+        <v>2.7</v>
       </c>
       <c r="G47" t="n">
-        <v>3.05</v>
+        <v>2.96</v>
       </c>
       <c r="H47" t="n">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="I47" t="n">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="J47" t="n">
         <v>4.1</v>
@@ -9511,22 +9511,22 @@
         <v>1.02</v>
       </c>
       <c r="N47" t="n">
-        <v>2.92</v>
+        <v>1.01</v>
       </c>
       <c r="O47" t="n">
         <v>1.11</v>
       </c>
       <c r="P47" t="n">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="Q47" t="n">
         <v>1.44</v>
       </c>
       <c r="R47" t="n">
-        <v>1.7</v>
+        <v>1.75</v>
       </c>
       <c r="S47" t="n">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="T47" t="n">
         <v>1.01</v>
@@ -9535,10 +9535,10 @@
         <v>1.01</v>
       </c>
       <c r="V47" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="W47" t="n">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="X47" t="n">
         <v>1000</v>
@@ -9650,7 +9650,7 @@
       </c>
       <c r="BH47" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -9681,22 +9681,22 @@
         </is>
       </c>
       <c r="F48" t="n">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="G48" t="n">
-        <v>6.2</v>
+        <v>5.1</v>
       </c>
       <c r="H48" t="n">
-        <v>1.67</v>
+        <v>1.73</v>
       </c>
       <c r="I48" t="n">
-        <v>1.99</v>
+        <v>1.88</v>
       </c>
       <c r="J48" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K48" t="n">
-        <v>7.4</v>
+        <v>5.2</v>
       </c>
       <c r="L48" t="n">
         <v>1.01</v>
@@ -9705,22 +9705,22 @@
         <v>1.01</v>
       </c>
       <c r="N48" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="O48" t="n">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P48" t="n">
-        <v>2.18</v>
+        <v>2.12</v>
       </c>
       <c r="Q48" t="n">
-        <v>1.51</v>
+        <v>1.57</v>
       </c>
       <c r="R48" t="n">
-        <v>1.49</v>
+        <v>1.4</v>
       </c>
       <c r="S48" t="n">
-        <v>2.16</v>
+        <v>2.36</v>
       </c>
       <c r="T48" t="n">
         <v>1.01</v>
@@ -9729,10 +9729,10 @@
         <v>1.01</v>
       </c>
       <c r="V48" t="n">
-        <v>2</v>
+        <v>2.12</v>
       </c>
       <c r="W48" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="X48" t="n">
         <v>1000</v>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="BH48" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -9875,7 +9875,7 @@
         </is>
       </c>
       <c r="F49" t="n">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="G49" t="n">
         <v>3.85</v>
@@ -9884,7 +9884,7 @@
         <v>2.06</v>
       </c>
       <c r="I49" t="n">
-        <v>2.26</v>
+        <v>2.22</v>
       </c>
       <c r="J49" t="n">
         <v>3.7</v>
@@ -9911,19 +9911,19 @@
         <v>1.76</v>
       </c>
       <c r="R49" t="n">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="S49" t="n">
         <v>2.92</v>
       </c>
       <c r="T49" t="n">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="U49" t="n">
         <v>2.24</v>
       </c>
       <c r="V49" t="n">
-        <v>1.79</v>
+        <v>1.82</v>
       </c>
       <c r="W49" t="n">
         <v>1.35</v>
@@ -10038,7 +10038,7 @@
       </c>
       <c r="BH49" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -10069,19 +10069,19 @@
         </is>
       </c>
       <c r="F50" t="n">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G50" t="n">
         <v>2.2</v>
       </c>
       <c r="H50" t="n">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="I50" t="n">
         <v>4.2</v>
       </c>
       <c r="J50" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="K50" t="n">
         <v>3.7</v>
@@ -10093,7 +10093,7 @@
         <v>1.07</v>
       </c>
       <c r="N50" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O50" t="n">
         <v>1.34</v>
@@ -10120,7 +10120,7 @@
         <v>1.32</v>
       </c>
       <c r="W50" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="X50" t="n">
         <v>16</v>
@@ -10232,7 +10232,7 @@
       </c>
       <c r="BH50" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -10269,7 +10269,7 @@
         <v>3.1</v>
       </c>
       <c r="H51" t="n">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="I51" t="n">
         <v>2.96</v>
@@ -10278,7 +10278,7 @@
         <v>3.2</v>
       </c>
       <c r="K51" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="L51" t="n">
         <v>1.01</v>
@@ -10293,13 +10293,13 @@
         <v>1.4</v>
       </c>
       <c r="P51" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q51" t="n">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="R51" t="n">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="S51" t="n">
         <v>4</v>
@@ -10308,7 +10308,7 @@
         <v>1.86</v>
       </c>
       <c r="U51" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="V51" t="n">
         <v>1.52</v>
@@ -10326,7 +10326,7 @@
         <v>22</v>
       </c>
       <c r="AA51" t="n">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AB51" t="n">
         <v>12.5</v>
@@ -10371,62 +10371,62 @@
         <v>44</v>
       </c>
       <c r="AP51" t="n">
-        <v>9.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AQ51" t="n">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AR51" t="n">
         <v>13</v>
       </c>
       <c r="AS51" t="n">
+        <v>32</v>
+      </c>
+      <c r="AT51" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU51" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AV51" t="n">
+        <v>9.6</v>
+      </c>
+      <c r="AW51" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="AX51" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AY51" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="AZ51" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="BA51" t="n">
         <v>3.95</v>
       </c>
-      <c r="AT51" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AU51" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV51" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW51" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AX51" t="n">
-        <v>14</v>
-      </c>
-      <c r="AY51" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ51" t="n">
-        <v>16</v>
-      </c>
-      <c r="BA51" t="n">
-        <v>4</v>
-      </c>
       <c r="BB51" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BC51" t="n">
-        <v>26</v>
+        <v>3.85</v>
       </c>
       <c r="BD51" t="n">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="BE51" t="n">
         <v>4.1</v>
       </c>
       <c r="BF51" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BG51" t="n">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="BH51" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -10460,19 +10460,19 @@
         <v>2.6</v>
       </c>
       <c r="G52" t="n">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="H52" t="n">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="I52" t="n">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="J52" t="n">
         <v>3.4</v>
       </c>
       <c r="K52" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L52" t="n">
         <v>1.01</v>
@@ -10505,7 +10505,7 @@
         <v>2.2</v>
       </c>
       <c r="V52" t="n">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="W52" t="n">
         <v>1.53</v>
@@ -10620,7 +10620,7 @@
       </c>
       <c r="BH52" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -10651,7 +10651,7 @@
         </is>
       </c>
       <c r="F53" t="n">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G53" t="n">
         <v>2.14</v>
@@ -10666,7 +10666,7 @@
         <v>3.7</v>
       </c>
       <c r="K53" t="n">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L53" t="n">
         <v>1.34</v>
@@ -10681,7 +10681,7 @@
         <v>1.31</v>
       </c>
       <c r="P53" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q53" t="n">
         <v>1.9</v>
@@ -10699,10 +10699,10 @@
         <v>2.1</v>
       </c>
       <c r="V53" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W53" t="n">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="X53" t="n">
         <v>19</v>
@@ -10814,7 +10814,7 @@
       </c>
       <c r="BH53" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -10845,13 +10845,13 @@
         </is>
       </c>
       <c r="F54" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="G54" t="n">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="H54" t="n">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="I54" t="n">
         <v>2.76</v>
@@ -10860,7 +10860,7 @@
         <v>3.65</v>
       </c>
       <c r="K54" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L54" t="n">
         <v>1.01</v>
@@ -10878,16 +10878,16 @@
         <v>2.34</v>
       </c>
       <c r="Q54" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="R54" t="n">
         <v>1.46</v>
       </c>
       <c r="S54" t="n">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="T54" t="n">
-        <v>1.01</v>
+        <v>1.44</v>
       </c>
       <c r="U54" t="n">
         <v>1.01</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="BH54" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -11102,7 +11102,7 @@
         <v>32</v>
       </c>
       <c r="AA55" t="n">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AB55" t="n">
         <v>18.5</v>
@@ -11202,7 +11202,7 @@
       </c>
       <c r="BH55" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -11233,19 +11233,19 @@
         </is>
       </c>
       <c r="F56" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="G56" t="n">
         <v>3.5</v>
       </c>
       <c r="H56" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="I56" t="n">
-        <v>2.76</v>
+        <v>2.44</v>
       </c>
       <c r="J56" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="K56" t="n">
         <v>4.6</v>
@@ -11257,34 +11257,34 @@
         <v>1.02</v>
       </c>
       <c r="N56" t="n">
-        <v>2.82</v>
+        <v>2.84</v>
       </c>
       <c r="O56" t="n">
         <v>1.13</v>
       </c>
       <c r="P56" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="Q56" t="n">
         <v>1.46</v>
       </c>
       <c r="R56" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S56" t="n">
         <v>1.98</v>
       </c>
       <c r="T56" t="n">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="U56" t="n">
         <v>1.11</v>
       </c>
       <c r="V56" t="n">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="W56" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="X56" t="n">
         <v>1000</v>
@@ -11396,7 +11396,7 @@
       </c>
       <c r="BH56" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -11427,22 +11427,22 @@
         </is>
       </c>
       <c r="F57" t="n">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="G57" t="n">
-        <v>1.89</v>
+        <v>1.87</v>
       </c>
       <c r="H57" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I57" t="n">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J57" t="n">
         <v>4.3</v>
       </c>
       <c r="K57" t="n">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="L57" t="n">
         <v>1.01</v>
@@ -11451,22 +11451,22 @@
         <v>1.02</v>
       </c>
       <c r="N57" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="O57" t="n">
         <v>1.1</v>
       </c>
       <c r="P57" t="n">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="Q57" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="R57" t="n">
         <v>1.76</v>
       </c>
       <c r="S57" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="T57" t="n">
         <v>1.01</v>
@@ -11475,10 +11475,10 @@
         <v>1.01</v>
       </c>
       <c r="V57" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="W57" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="X57" t="n">
         <v>1000</v>
@@ -11590,7 +11590,7 @@
       </c>
       <c r="BH57" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -11621,19 +11621,19 @@
         </is>
       </c>
       <c r="F58" t="n">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="G58" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="H58" t="n">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="I58" t="n">
-        <v>2.84</v>
+        <v>3.05</v>
       </c>
       <c r="J58" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="K58" t="n">
         <v>4.5</v>
@@ -11654,7 +11654,7 @@
         <v>2.54</v>
       </c>
       <c r="Q58" t="n">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="R58" t="n">
         <v>1.55</v>
@@ -11669,11 +11669,11 @@
         <v>1.11</v>
       </c>
       <c r="V58" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="W58" t="n">
         <v>1.54</v>
       </c>
-      <c r="W58" t="n">
-        <v>1.51</v>
-      </c>
       <c r="X58" t="n">
         <v>1000</v>
       </c>
@@ -11784,7 +11784,7 @@
       </c>
       <c r="BH58" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -11815,16 +11815,16 @@
         </is>
       </c>
       <c r="F59" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="G59" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="H59" t="n">
         <v>3.85</v>
       </c>
       <c r="I59" t="n">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="J59" t="n">
         <v>3.85</v>
@@ -11839,22 +11839,22 @@
         <v>1.04</v>
       </c>
       <c r="N59" t="n">
-        <v>2.1</v>
+        <v>4</v>
       </c>
       <c r="O59" t="n">
         <v>1.21</v>
       </c>
       <c r="P59" t="n">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="Q59" t="n">
-        <v>1.56</v>
+        <v>1.66</v>
       </c>
       <c r="R59" t="n">
-        <v>1.25</v>
+        <v>1.51</v>
       </c>
       <c r="S59" t="n">
-        <v>1.56</v>
+        <v>2.66</v>
       </c>
       <c r="T59" t="n">
         <v>1.01</v>
@@ -11866,119 +11866,119 @@
         <v>1.3</v>
       </c>
       <c r="W59" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="X59" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y59" t="n">
-        <v>26</v>
+        <v>970</v>
       </c>
       <c r="Z59" t="n">
+        <v>34</v>
+      </c>
+      <c r="AA59" t="n">
+        <v>80</v>
+      </c>
+      <c r="AB59" t="n">
+        <v>970</v>
+      </c>
+      <c r="AC59" t="n">
+        <v>970</v>
+      </c>
+      <c r="AD59" t="n">
+        <v>970</v>
+      </c>
+      <c r="AE59" t="n">
+        <v>44</v>
+      </c>
+      <c r="AF59" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG59" t="n">
+        <v>970</v>
+      </c>
+      <c r="AH59" t="n">
+        <v>970</v>
+      </c>
+      <c r="AI59" t="n">
         <v>46</v>
       </c>
-      <c r="AA59" t="n">
-        <v>100</v>
-      </c>
-      <c r="AB59" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AC59" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AD59" t="n">
-        <v>24</v>
-      </c>
-      <c r="AE59" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF59" t="n">
-        <v>20</v>
-      </c>
-      <c r="AG59" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AH59" t="n">
+      <c r="AJ59" t="n">
         <v>23</v>
       </c>
-      <c r="AI59" t="n">
-        <v>65</v>
-      </c>
-      <c r="AJ59" t="n">
-        <v>34</v>
-      </c>
       <c r="AK59" t="n">
-        <v>28</v>
+        <v>970</v>
       </c>
       <c r="AL59" t="n">
-        <v>44</v>
+        <v>29</v>
       </c>
       <c r="AM59" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AN59" t="n">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="AO59" t="n">
         <v>1000</v>
       </c>
       <c r="AP59" t="n">
-        <v>2.48</v>
+        <v>8</v>
       </c>
       <c r="AQ59" t="n">
-        <v>2.28</v>
+        <v>7.2</v>
       </c>
       <c r="AR59" t="n">
-        <v>2.36</v>
+        <v>4.5</v>
       </c>
       <c r="AS59" t="n">
-        <v>2.44</v>
+        <v>2.22</v>
       </c>
       <c r="AT59" t="n">
-        <v>2.18</v>
+        <v>5.9</v>
       </c>
       <c r="AU59" t="n">
-        <v>2.1</v>
+        <v>5.3</v>
       </c>
       <c r="AV59" t="n">
-        <v>2.26</v>
+        <v>6.8</v>
       </c>
       <c r="AW59" t="n">
-        <v>2.4</v>
+        <v>4.6</v>
       </c>
       <c r="AX59" t="n">
-        <v>9.800000000000001</v>
+        <v>6.4</v>
       </c>
       <c r="AY59" t="n">
-        <v>2.14</v>
+        <v>5.7</v>
       </c>
       <c r="AZ59" t="n">
-        <v>2.24</v>
+        <v>6.8</v>
       </c>
       <c r="BA59" t="n">
-        <v>2.4</v>
+        <v>3.75</v>
       </c>
       <c r="BB59" t="n">
-        <v>2.32</v>
+        <v>7.6</v>
       </c>
       <c r="BC59" t="n">
-        <v>13</v>
+        <v>7.2</v>
       </c>
       <c r="BD59" t="n">
-        <v>19.5</v>
+        <v>5.2</v>
       </c>
       <c r="BE59" t="n">
-        <v>2.44</v>
+        <v>10</v>
       </c>
       <c r="BF59" t="n">
-        <v>6.8</v>
+        <v>5.5</v>
       </c>
       <c r="BG59" t="n">
-        <v>2.48</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH59" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -12009,19 +12009,19 @@
         </is>
       </c>
       <c r="F60" t="n">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="G60" t="n">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="H60" t="n">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="I60" t="n">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="J60" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="K60" t="n">
         <v>4.9</v>
@@ -12033,16 +12033,16 @@
         <v>1.02</v>
       </c>
       <c r="N60" t="n">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="O60" t="n">
         <v>1.1</v>
       </c>
       <c r="P60" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q60" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="R60" t="n">
         <v>1.75</v>
@@ -12057,7 +12057,7 @@
         <v>1.01</v>
       </c>
       <c r="V60" t="n">
-        <v>1.79</v>
+        <v>1.76</v>
       </c>
       <c r="W60" t="n">
         <v>1.36</v>
@@ -12172,7 +12172,7 @@
       </c>
       <c r="BH60" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -12203,22 +12203,22 @@
         </is>
       </c>
       <c r="F61" t="n">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="G61" t="n">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="H61" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="I61" t="n">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="J61" t="n">
         <v>4.1</v>
       </c>
       <c r="K61" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="L61" t="n">
         <v>1.01</v>
@@ -12227,13 +12227,13 @@
         <v>1.02</v>
       </c>
       <c r="N61" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="O61" t="n">
         <v>1.11</v>
       </c>
       <c r="P61" t="n">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="Q61" t="n">
         <v>1.4</v>
@@ -12251,10 +12251,10 @@
         <v>1.01</v>
       </c>
       <c r="V61" t="n">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="W61" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="X61" t="n">
         <v>48</v>
@@ -12308,34 +12308,34 @@
         <v>1000</v>
       </c>
       <c r="AO61" t="n">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AP61" t="n">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="AQ61" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="AR61" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AS61" t="n">
+        <v>2.42</v>
+      </c>
+      <c r="AT61" t="n">
         <v>2.34</v>
       </c>
-      <c r="AS61" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AT61" t="n">
-        <v>2.32</v>
-      </c>
       <c r="AU61" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AV61" t="n">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="AW61" t="n">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="AX61" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="AY61" t="n">
         <v>9.4</v>
@@ -12347,26 +12347,26 @@
         <v>16</v>
       </c>
       <c r="BB61" t="n">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="BC61" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="BD61" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="BE61" t="n">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="BF61" t="n">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="BG61" t="n">
         <v>7</v>
       </c>
       <c r="BH61" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -12400,19 +12400,19 @@
         <v>10</v>
       </c>
       <c r="G62" t="n">
-        <v>990</v>
+        <v>17</v>
       </c>
       <c r="H62" t="n">
-        <v>1.19</v>
+        <v>1.25</v>
       </c>
       <c r="I62" t="n">
-        <v>1.34</v>
+        <v>1.32</v>
       </c>
       <c r="J62" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="K62" t="n">
-        <v>16.5</v>
+        <v>10.5</v>
       </c>
       <c r="L62" t="n">
         <v>1.01</v>
@@ -12430,7 +12430,7 @@
         <v>2.56</v>
       </c>
       <c r="Q62" t="n">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="R62" t="n">
         <v>1.74</v>
@@ -12439,128 +12439,128 @@
         <v>1.92</v>
       </c>
       <c r="T62" t="n">
-        <v>1.11</v>
+        <v>1.68</v>
       </c>
       <c r="U62" t="n">
         <v>1.11</v>
       </c>
       <c r="V62" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="W62" t="n">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="X62" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="Y62" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="Z62" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AA62" t="n">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="AB62" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AC62" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="AD62" t="n">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="AE62" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AF62" t="n">
-        <v>310</v>
+        <v>200</v>
       </c>
       <c r="AG62" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="AH62" t="n">
-        <v>60</v>
+        <v>44</v>
       </c>
       <c r="AI62" t="n">
-        <v>60</v>
+        <v>48</v>
       </c>
       <c r="AJ62" t="n">
-        <v>1000</v>
+        <v>990</v>
       </c>
       <c r="AK62" t="n">
-        <v>620</v>
+        <v>350</v>
       </c>
       <c r="AL62" t="n">
-        <v>460</v>
+        <v>270</v>
       </c>
       <c r="AM62" t="n">
+        <v>270</v>
+      </c>
+      <c r="AN62" t="n">
         <v>430</v>
       </c>
-      <c r="AN62" t="n">
-        <v>880</v>
-      </c>
       <c r="AO62" t="n">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="AP62" t="n">
-        <v>2.36</v>
+        <v>2.76</v>
       </c>
       <c r="AQ62" t="n">
-        <v>2.2</v>
+        <v>2.54</v>
       </c>
       <c r="AR62" t="n">
-        <v>2.12</v>
+        <v>2.4</v>
       </c>
       <c r="AS62" t="n">
-        <v>2.12</v>
+        <v>2.42</v>
       </c>
       <c r="AT62" t="n">
-        <v>2.4</v>
+        <v>2.84</v>
       </c>
       <c r="AU62" t="n">
         <v>10.5</v>
       </c>
       <c r="AV62" t="n">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AW62" t="n">
         <v>9.6</v>
       </c>
       <c r="AX62" t="n">
-        <v>2.44</v>
+        <v>2.88</v>
       </c>
       <c r="AY62" t="n">
-        <v>2.4</v>
+        <v>2.8</v>
       </c>
       <c r="AZ62" t="n">
-        <v>2.36</v>
+        <v>2.74</v>
       </c>
       <c r="BA62" t="n">
-        <v>2.36</v>
+        <v>2.76</v>
       </c>
       <c r="BB62" t="n">
-        <v>2.46</v>
+        <v>2.92</v>
       </c>
       <c r="BC62" t="n">
-        <v>2.46</v>
+        <v>2.9</v>
       </c>
       <c r="BD62" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="BE62" t="n">
-        <v>2.44</v>
+        <v>2.9</v>
       </c>
       <c r="BF62" t="n">
-        <v>2.46</v>
+        <v>2.9</v>
       </c>
       <c r="BG62" t="n">
-        <v>2.2</v>
+        <v>2.42</v>
       </c>
       <c r="BH62" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -12597,10 +12597,10 @@
         <v>5.2</v>
       </c>
       <c r="H63" t="n">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="I63" t="n">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="J63" t="n">
         <v>4</v>
@@ -12627,7 +12627,7 @@
         <v>1.58</v>
       </c>
       <c r="R63" t="n">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="S63" t="n">
         <v>2.2</v>
@@ -12639,7 +12639,7 @@
         <v>1.94</v>
       </c>
       <c r="V63" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="W63" t="n">
         <v>1.23</v>
@@ -12754,7 +12754,7 @@
       </c>
       <c r="BH63" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -12788,10 +12788,10 @@
         <v>3.05</v>
       </c>
       <c r="G64" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="H64" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="I64" t="n">
         <v>2.64</v>
@@ -12800,7 +12800,7 @@
         <v>3.15</v>
       </c>
       <c r="K64" t="n">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="L64" t="n">
         <v>1.01</v>
@@ -12830,13 +12830,13 @@
         <v>1.91</v>
       </c>
       <c r="U64" t="n">
-        <v>1.92</v>
+        <v>1.94</v>
       </c>
       <c r="V64" t="n">
         <v>1.6</v>
       </c>
       <c r="W64" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="X64" t="n">
         <v>12</v>
@@ -12854,7 +12854,7 @@
         <v>11</v>
       </c>
       <c r="AC64" t="n">
-        <v>7.2</v>
+        <v>6.8</v>
       </c>
       <c r="AD64" t="n">
         <v>13</v>
@@ -12902,19 +12902,19 @@
         <v>13</v>
       </c>
       <c r="AS64" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT64" t="n">
         <v>9</v>
       </c>
       <c r="AU64" t="n">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV64" t="n">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW64" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AX64" t="n">
         <v>18</v>
@@ -12923,32 +12923,32 @@
         <v>12.5</v>
       </c>
       <c r="AZ64" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA64" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="BB64" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC64" t="n">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="BD64" t="n">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BE64" t="n">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF64" t="n">
         <v>38</v>
       </c>
       <c r="BG64" t="n">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BH64" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -13000,10 +13000,10 @@
         <v>1.01</v>
       </c>
       <c r="M65" t="n">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N65" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="O65" t="n">
         <v>1.27</v>
@@ -13012,7 +13012,7 @@
         <v>1.95</v>
       </c>
       <c r="Q65" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="R65" t="n">
         <v>1.31</v>
@@ -13142,7 +13142,7 @@
       </c>
       <c r="BH65" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -13188,7 +13188,7 @@
         <v>3.2</v>
       </c>
       <c r="K66" t="n">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L66" t="n">
         <v>1.34</v>
@@ -13215,7 +13215,7 @@
         <v>3.7</v>
       </c>
       <c r="T66" t="n">
-        <v>1.01</v>
+        <v>1.66</v>
       </c>
       <c r="U66" t="n">
         <v>1.01</v>
@@ -13336,7 +13336,7 @@
       </c>
       <c r="BH66" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -13370,13 +13370,13 @@
         <v>1.38</v>
       </c>
       <c r="G67" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="H67" t="n">
         <v>9.4</v>
       </c>
       <c r="I67" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J67" t="n">
         <v>5.7</v>
@@ -13400,7 +13400,7 @@
         <v>2.76</v>
       </c>
       <c r="Q67" t="n">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="R67" t="n">
         <v>1.7</v>
@@ -13430,7 +13430,7 @@
         <v>90</v>
       </c>
       <c r="AA67" t="n">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="AB67" t="n">
         <v>11.5</v>
@@ -13469,7 +13469,7 @@
         <v>110</v>
       </c>
       <c r="AN67" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="AO67" t="n">
         <v>110</v>
@@ -13514,7 +13514,7 @@
         <v>11</v>
       </c>
       <c r="BC67" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="BD67" t="n">
         <v>26</v>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="BH67" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -13561,91 +13561,91 @@
         </is>
       </c>
       <c r="F68" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="G68" t="n">
         <v>2.64</v>
       </c>
       <c r="H68" t="n">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I68" t="n">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="J68" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K68" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L68" t="n">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M68" t="n">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N68" t="n">
-        <v>1.98</v>
+        <v>3.95</v>
       </c>
       <c r="O68" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P68" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="Q68" t="n">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="R68" t="n">
-        <v>1.32</v>
+        <v>1.38</v>
       </c>
       <c r="S68" t="n">
-        <v>2.72</v>
+        <v>3.05</v>
       </c>
       <c r="T68" t="n">
-        <v>1.01</v>
+        <v>1.67</v>
       </c>
       <c r="U68" t="n">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="V68" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="W68" t="n">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X68" t="n">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="Y68" t="n">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z68" t="n">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA68" t="n">
         <v>1000</v>
       </c>
       <c r="AB68" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AC68" t="n">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD68" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE68" t="n">
         <v>1000</v>
       </c>
       <c r="AF68" t="n">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG68" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH68" t="n">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI68" t="n">
         <v>1000</v>
@@ -13654,7 +13654,7 @@
         <v>1000</v>
       </c>
       <c r="AK68" t="n">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AL68" t="n">
         <v>1000</v>
@@ -13663,68 +13663,68 @@
         <v>1000</v>
       </c>
       <c r="AN68" t="n">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AO68" t="n">
         <v>1000</v>
       </c>
       <c r="AP68" t="n">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AQ68" t="n">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AR68" t="n">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AS68" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="AT68" t="n">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU68" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV68" t="n">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AW68" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="AX68" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AY68" t="n">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AZ68" t="n">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BA68" t="n">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BB68" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BC68" t="n">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BD68" t="n">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BE68" t="n">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BF68" t="n">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BG68" t="n">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH68" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -13755,64 +13755,64 @@
         </is>
       </c>
       <c r="F69" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="G69" t="n">
         <v>1.61</v>
       </c>
-      <c r="G69" t="n">
-        <v>1.68</v>
-      </c>
       <c r="H69" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I69" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J69" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="K69" t="n">
-        <v>4.7</v>
+        <v>5.2</v>
       </c>
       <c r="L69" t="n">
         <v>1.01</v>
       </c>
       <c r="M69" t="n">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N69" t="n">
-        <v>1.92</v>
+        <v>4.1</v>
       </c>
       <c r="O69" t="n">
         <v>1.29</v>
       </c>
       <c r="P69" t="n">
-        <v>1.92</v>
+        <v>2.04</v>
       </c>
       <c r="Q69" t="n">
-        <v>1.9</v>
+        <v>1.78</v>
       </c>
       <c r="R69" t="n">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="S69" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="T69" t="n">
-        <v>1.01</v>
+        <v>2</v>
       </c>
       <c r="U69" t="n">
-        <v>1.69</v>
+        <v>1.8</v>
       </c>
       <c r="V69" t="n">
         <v>1.17</v>
       </c>
       <c r="W69" t="n">
-        <v>2.46</v>
+        <v>2.64</v>
       </c>
       <c r="X69" t="n">
-        <v>20</v>
+        <v>1000</v>
       </c>
       <c r="Y69" t="n">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="Z69" t="n">
         <v>1000</v>
@@ -13821,22 +13821,22 @@
         <v>1000</v>
       </c>
       <c r="AB69" t="n">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="AC69" t="n">
-        <v>13</v>
+        <v>970</v>
       </c>
       <c r="AD69" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="AE69" t="n">
         <v>1000</v>
       </c>
       <c r="AF69" t="n">
-        <v>13</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG69" t="n">
-        <v>15</v>
+        <v>970</v>
       </c>
       <c r="AH69" t="n">
         <v>30</v>
@@ -13845,10 +13845,10 @@
         <v>1000</v>
       </c>
       <c r="AJ69" t="n">
-        <v>20</v>
+        <v>13.5</v>
       </c>
       <c r="AK69" t="n">
-        <v>25</v>
+        <v>970</v>
       </c>
       <c r="AL69" t="n">
         <v>1000</v>
@@ -13857,68 +13857,68 @@
         <v>1000</v>
       </c>
       <c r="AN69" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AO69" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP69" t="n">
         <v>13</v>
       </c>
-      <c r="AO69" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP69" t="n">
+      <c r="AQ69" t="n">
+        <v>16</v>
+      </c>
+      <c r="AR69" t="n">
+        <v>6</v>
+      </c>
+      <c r="AS69" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AT69" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AU69" t="n">
+        <v>8.6</v>
+      </c>
+      <c r="AV69" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AW69" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AX69" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AY69" t="n">
         <v>9.6</v>
       </c>
-      <c r="AQ69" t="n">
-        <v>12</v>
-      </c>
-      <c r="AR69" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AS69" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AT69" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AU69" t="n">
+      <c r="AZ69" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="BA69" t="n">
         <v>6.2</v>
       </c>
-      <c r="AV69" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AW69" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AX69" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AY69" t="n">
-        <v>7</v>
-      </c>
-      <c r="AZ69" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="BA69" t="n">
-        <v>2.7</v>
-      </c>
       <c r="BB69" t="n">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="BC69" t="n">
-        <v>11.5</v>
+        <v>4.9</v>
       </c>
       <c r="BD69" t="n">
-        <v>2.7</v>
+        <v>6</v>
       </c>
       <c r="BE69" t="n">
-        <v>2.7</v>
+        <v>6.4</v>
       </c>
       <c r="BF69" t="n">
         <v>6.2</v>
       </c>
       <c r="BG69" t="n">
-        <v>2.7</v>
+        <v>6.4</v>
       </c>
       <c r="BH69" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -13949,13 +13949,13 @@
         </is>
       </c>
       <c r="F70" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="G70" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="H70" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="I70" t="n">
         <v>12.5</v>
@@ -13988,19 +13988,19 @@
         <v>1.37</v>
       </c>
       <c r="S70" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="T70" t="n">
         <v>2.44</v>
       </c>
       <c r="U70" t="n">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="V70" t="n">
         <v>1.08</v>
       </c>
       <c r="W70" t="n">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="X70" t="n">
         <v>16</v>
@@ -14012,7 +14012,7 @@
         <v>120</v>
       </c>
       <c r="AA70" t="n">
-        <v>660</v>
+        <v>640</v>
       </c>
       <c r="AB70" t="n">
         <v>7</v>
@@ -14024,19 +14024,19 @@
         <v>46</v>
       </c>
       <c r="AE70" t="n">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="AF70" t="n">
         <v>7</v>
       </c>
       <c r="AG70" t="n">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH70" t="n">
         <v>38</v>
       </c>
       <c r="AI70" t="n">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="AJ70" t="n">
         <v>10.5</v>
@@ -14048,13 +14048,13 @@
         <v>50</v>
       </c>
       <c r="AM70" t="n">
-        <v>1000</v>
+        <v>270</v>
       </c>
       <c r="AN70" t="n">
         <v>7</v>
       </c>
       <c r="AO70" t="n">
-        <v>460</v>
+        <v>430</v>
       </c>
       <c r="AP70" t="n">
         <v>15</v>
@@ -14066,7 +14066,7 @@
         <v>38</v>
       </c>
       <c r="AS70" t="n">
-        <v>110</v>
+        <v>19</v>
       </c>
       <c r="AT70" t="n">
         <v>6.6</v>
@@ -14075,25 +14075,25 @@
         <v>11</v>
       </c>
       <c r="AV70" t="n">
-        <v>38</v>
+        <v>26</v>
       </c>
       <c r="AW70" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AX70" t="n">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AY70" t="n">
         <v>10</v>
       </c>
       <c r="AZ70" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BA70" t="n">
         <v>48</v>
       </c>
       <c r="BB70" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BC70" t="n">
         <v>15</v>
@@ -14102,7 +14102,7 @@
         <v>44</v>
       </c>
       <c r="BE70" t="n">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="BF70" t="n">
         <v>6.4</v>
@@ -14112,7 +14112,7 @@
       </c>
       <c r="BH70" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -14143,7 +14143,7 @@
         </is>
       </c>
       <c r="F71" t="n">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="G71" t="n">
         <v>1.81</v>
@@ -14306,7 +14306,7 @@
       </c>
       <c r="BH71" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -14346,13 +14346,13 @@
         <v>2.24</v>
       </c>
       <c r="I72" t="n">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="J72" t="n">
         <v>3.35</v>
       </c>
       <c r="K72" t="n">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L72" t="n">
         <v>1.33</v>
@@ -14367,7 +14367,7 @@
         <v>1.31</v>
       </c>
       <c r="P72" t="n">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="Q72" t="n">
         <v>1.92</v>
@@ -14385,7 +14385,7 @@
         <v>2.12</v>
       </c>
       <c r="V72" t="n">
-        <v>1.67</v>
+        <v>1.68</v>
       </c>
       <c r="W72" t="n">
         <v>1.35</v>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="BH72" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -14531,7 +14531,7 @@
         </is>
       </c>
       <c r="F73" t="n">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="G73" t="n">
         <v>2.42</v>
@@ -14540,7 +14540,7 @@
         <v>3.6</v>
       </c>
       <c r="I73" t="n">
-        <v>4.3</v>
+        <v>4.6</v>
       </c>
       <c r="J73" t="n">
         <v>3.15</v>
@@ -14555,16 +14555,16 @@
         <v>1.1</v>
       </c>
       <c r="N73" t="n">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O73" t="n">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="P73" t="n">
         <v>1.63</v>
       </c>
       <c r="Q73" t="n">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="R73" t="n">
         <v>1.23</v>
@@ -14579,7 +14579,7 @@
         <v>1.84</v>
       </c>
       <c r="V73" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="W73" t="n">
         <v>1.7</v>
@@ -14639,19 +14639,19 @@
         <v>1000</v>
       </c>
       <c r="AP73" t="n">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AQ73" t="n">
         <v>9</v>
       </c>
       <c r="AR73" t="n">
-        <v>4.9</v>
+        <v>4.7</v>
       </c>
       <c r="AS73" t="n">
         <v>4.9</v>
       </c>
       <c r="AT73" t="n">
-        <v>3.5</v>
+        <v>6.2</v>
       </c>
       <c r="AU73" t="n">
         <v>5.8</v>
@@ -14663,10 +14663,10 @@
         <v>4.8</v>
       </c>
       <c r="AX73" t="n">
-        <v>4.1</v>
+        <v>10</v>
       </c>
       <c r="AY73" t="n">
-        <v>3.9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ73" t="n">
         <v>15.5</v>
@@ -14687,14 +14687,14 @@
         <v>5</v>
       </c>
       <c r="BF73" t="n">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="BG73" t="n">
         <v>4.9</v>
       </c>
       <c r="BH73" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -14734,7 +14734,7 @@
         <v>2.6</v>
       </c>
       <c r="I74" t="n">
-        <v>3.2</v>
+        <v>3.05</v>
       </c>
       <c r="J74" t="n">
         <v>3.15</v>
@@ -14743,13 +14743,13 @@
         <v>4.3</v>
       </c>
       <c r="L74" t="n">
-        <v>1.4</v>
+        <v>1.36</v>
       </c>
       <c r="M74" t="n">
         <v>1.07</v>
       </c>
       <c r="N74" t="n">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O74" t="n">
         <v>1.31</v>
@@ -14761,7 +14761,7 @@
         <v>1.91</v>
       </c>
       <c r="R74" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S74" t="n">
         <v>3.35</v>
@@ -14770,10 +14770,10 @@
         <v>1.72</v>
       </c>
       <c r="U74" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="V74" t="n">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="W74" t="n">
         <v>1.5</v>
@@ -14888,7 +14888,7 @@
       </c>
       <c r="BH74" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -14919,7 +14919,7 @@
         </is>
       </c>
       <c r="F75" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="G75" t="n">
         <v>3.85</v>
@@ -14928,10 +14928,10 @@
         <v>2.22</v>
       </c>
       <c r="I75" t="n">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="J75" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="K75" t="n">
         <v>3.55</v>
@@ -14946,10 +14946,10 @@
         <v>3.1</v>
       </c>
       <c r="O75" t="n">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="P75" t="n">
-        <v>1.73</v>
+        <v>1.72</v>
       </c>
       <c r="Q75" t="n">
         <v>2.16</v>
@@ -14967,7 +14967,7 @@
         <v>1.96</v>
       </c>
       <c r="V75" t="n">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="W75" t="n">
         <v>1.35</v>
@@ -14988,7 +14988,7 @@
         <v>14.5</v>
       </c>
       <c r="AC75" t="n">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD75" t="n">
         <v>14</v>
@@ -15000,7 +15000,7 @@
         <v>32</v>
       </c>
       <c r="AG75" t="n">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AH75" t="n">
         <v>24</v>
@@ -15027,25 +15027,25 @@
         <v>29</v>
       </c>
       <c r="AP75" t="n">
-        <v>10</v>
+        <v>8.4</v>
       </c>
       <c r="AQ75" t="n">
-        <v>7.6</v>
+        <v>6.4</v>
       </c>
       <c r="AR75" t="n">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AS75" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="AT75" t="n">
-        <v>10.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU75" t="n">
         <v>6.6</v>
       </c>
       <c r="AV75" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AW75" t="n">
         <v>20</v>
@@ -15054,7 +15054,7 @@
         <v>18</v>
       </c>
       <c r="AY75" t="n">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AZ75" t="n">
         <v>16.5</v>
@@ -15082,7 +15082,7 @@
       </c>
       <c r="BH75" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -15146,19 +15146,19 @@
         <v>1.97</v>
       </c>
       <c r="Q76" t="n">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="R76" t="n">
         <v>1.38</v>
       </c>
       <c r="S76" t="n">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="T76" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="U76" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="V76" t="n">
         <v>2.2</v>
@@ -15276,7 +15276,7 @@
       </c>
       <c r="BH76" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -15307,43 +15307,43 @@
         </is>
       </c>
       <c r="F77" t="n">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="G77" t="n">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="H77" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="I77" t="n">
         <v>1.74</v>
       </c>
-      <c r="I77" t="n">
-        <v>1.76</v>
-      </c>
       <c r="J77" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K77" t="n">
         <v>4.3</v>
       </c>
       <c r="L77" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="M77" t="n">
         <v>1.05</v>
       </c>
       <c r="N77" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="O77" t="n">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P77" t="n">
         <v>2.28</v>
       </c>
       <c r="Q77" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R77" t="n">
-        <v>1.5</v>
+        <v>1.51</v>
       </c>
       <c r="S77" t="n">
         <v>2.84</v>
@@ -15352,28 +15352,28 @@
         <v>1.75</v>
       </c>
       <c r="U77" t="n">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="V77" t="n">
-        <v>2.3</v>
+        <v>2.34</v>
       </c>
       <c r="W77" t="n">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="X77" t="n">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="Y77" t="n">
         <v>10.5</v>
       </c>
       <c r="Z77" t="n">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AA77" t="n">
         <v>18</v>
       </c>
       <c r="AB77" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC77" t="n">
         <v>9.4</v>
@@ -15382,7 +15382,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AE77" t="n">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AF77" t="n">
         <v>42</v>
@@ -15397,7 +15397,7 @@
         <v>29</v>
       </c>
       <c r="AJ77" t="n">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AK77" t="n">
         <v>65</v>
@@ -15418,19 +15418,19 @@
         <v>17.5</v>
       </c>
       <c r="AQ77" t="n">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AR77" t="n">
         <v>10.5</v>
       </c>
       <c r="AS77" t="n">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AT77" t="n">
         <v>20</v>
       </c>
       <c r="AU77" t="n">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV77" t="n">
         <v>9.4</v>
@@ -15442,7 +15442,7 @@
         <v>38</v>
       </c>
       <c r="AY77" t="n">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AZ77" t="n">
         <v>17</v>
@@ -15451,7 +15451,7 @@
         <v>27</v>
       </c>
       <c r="BB77" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="BC77" t="n">
         <v>50</v>
@@ -15460,17 +15460,17 @@
         <v>50</v>
       </c>
       <c r="BE77" t="n">
-        <v>16.5</v>
+        <v>36</v>
       </c>
       <c r="BF77" t="n">
-        <v>46</v>
+        <v>30</v>
       </c>
       <c r="BG77" t="n">
         <v>8</v>
       </c>
       <c r="BH77" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -15504,13 +15504,13 @@
         <v>2.26</v>
       </c>
       <c r="G78" t="n">
-        <v>2.54</v>
+        <v>2.52</v>
       </c>
       <c r="H78" t="n">
         <v>3.15</v>
       </c>
       <c r="I78" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="J78" t="n">
         <v>3.25</v>
@@ -15525,16 +15525,16 @@
         <v>1.07</v>
       </c>
       <c r="N78" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="O78" t="n">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P78" t="n">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q78" t="n">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R78" t="n">
         <v>1.32</v>
@@ -15543,16 +15543,16 @@
         <v>3.55</v>
       </c>
       <c r="T78" t="n">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="U78" t="n">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="V78" t="n">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W78" t="n">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="X78" t="n">
         <v>16.5</v>
@@ -15570,7 +15570,7 @@
         <v>12</v>
       </c>
       <c r="AC78" t="n">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AD78" t="n">
         <v>17.5</v>
@@ -15603,7 +15603,7 @@
         <v>120</v>
       </c>
       <c r="AN78" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AO78" t="n">
         <v>50</v>
@@ -15633,7 +15633,7 @@
         <v>4.2</v>
       </c>
       <c r="AX78" t="n">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AY78" t="n">
         <v>9.6</v>
@@ -15642,7 +15642,7 @@
         <v>15</v>
       </c>
       <c r="BA78" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="BB78" t="n">
         <v>4.3</v>
@@ -15651,7 +15651,7 @@
         <v>19</v>
       </c>
       <c r="BD78" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="BE78" t="n">
         <v>4.2</v>
@@ -15664,7 +15664,7 @@
       </c>
       <c r="BH78" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -15695,10 +15695,10 @@
         </is>
       </c>
       <c r="F79" t="n">
-        <v>2.84</v>
+        <v>2.86</v>
       </c>
       <c r="G79" t="n">
-        <v>2.86</v>
+        <v>2.88</v>
       </c>
       <c r="H79" t="n">
         <v>2.86</v>
@@ -15749,7 +15749,7 @@
         <v>1.53</v>
       </c>
       <c r="X79" t="n">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="Y79" t="n">
         <v>9.6</v>
@@ -15833,10 +15833,10 @@
         <v>12</v>
       </c>
       <c r="AZ79" t="n">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BA79" t="n">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="BB79" t="n">
         <v>40</v>
@@ -15851,14 +15851,14 @@
         <v>90</v>
       </c>
       <c r="BF79" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BG79" t="n">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BH79" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -15889,13 +15889,13 @@
         </is>
       </c>
       <c r="F80" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="G80" t="n">
         <v>3.7</v>
       </c>
       <c r="H80" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="I80" t="n">
         <v>2.64</v>
@@ -15907,28 +15907,28 @@
         <v>3.45</v>
       </c>
       <c r="L80" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="M80" t="n">
         <v>1.1</v>
       </c>
       <c r="N80" t="n">
-        <v>2.76</v>
+        <v>2.92</v>
       </c>
       <c r="O80" t="n">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="P80" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Q80" t="n">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="R80" t="n">
         <v>1.23</v>
       </c>
       <c r="S80" t="n">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="T80" t="n">
         <v>1.77</v>
@@ -16052,7 +16052,7 @@
       </c>
       <c r="BH80" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -16083,10 +16083,10 @@
         </is>
       </c>
       <c r="F81" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="G81" t="n">
-        <v>2.02</v>
+        <v>1.99</v>
       </c>
       <c r="H81" t="n">
         <v>4.5</v>
@@ -16107,7 +16107,7 @@
         <v>1.09</v>
       </c>
       <c r="N81" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="O81" t="n">
         <v>1.39</v>
@@ -16116,28 +16116,28 @@
         <v>1.78</v>
       </c>
       <c r="Q81" t="n">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="R81" t="n">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="S81" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="T81" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="U81" t="n">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="V81" t="n">
         <v>1.25</v>
       </c>
       <c r="W81" t="n">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="X81" t="n">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="Y81" t="n">
         <v>14.5</v>
@@ -16152,7 +16152,7 @@
         <v>8</v>
       </c>
       <c r="AC81" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AD81" t="n">
         <v>19</v>
@@ -16197,10 +16197,10 @@
         <v>12.5</v>
       </c>
       <c r="AR81" t="n">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AS81" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AT81" t="n">
         <v>7</v>
@@ -16212,19 +16212,19 @@
         <v>16.5</v>
       </c>
       <c r="AW81" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AX81" t="n">
         <v>10</v>
       </c>
       <c r="AY81" t="n">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ81" t="n">
         <v>18</v>
       </c>
       <c r="BA81" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB81" t="n">
         <v>20</v>
@@ -16233,20 +16233,20 @@
         <v>20</v>
       </c>
       <c r="BD81" t="n">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BE81" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BF81" t="n">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="BG81" t="n">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BH81" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -16277,16 +16277,16 @@
         </is>
       </c>
       <c r="F82" t="n">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="G82" t="n">
         <v>3.95</v>
       </c>
       <c r="H82" t="n">
-        <v>1.92</v>
+        <v>1.93</v>
       </c>
       <c r="I82" t="n">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="J82" t="n">
         <v>4.3</v>
@@ -16295,40 +16295,40 @@
         <v>4.5</v>
       </c>
       <c r="L82" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="M82" t="n">
         <v>1.03</v>
       </c>
       <c r="N82" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="O82" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="P82" t="n">
         <v>2.68</v>
       </c>
       <c r="Q82" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="S82" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="T82" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="U82" t="n">
         <v>2.66</v>
       </c>
       <c r="V82" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="W82" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="X82" t="n">
         <v>26</v>
@@ -16367,7 +16367,7 @@
         <v>25</v>
       </c>
       <c r="AJ82" t="n">
-        <v>80</v>
+        <v>990</v>
       </c>
       <c r="AK82" t="n">
         <v>38</v>
@@ -16436,11 +16436,11 @@
         <v>24</v>
       </c>
       <c r="BG82" t="n">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="BH82" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -16471,7 +16471,7 @@
         </is>
       </c>
       <c r="F83" t="n">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="G83" t="n">
         <v>2.52</v>
@@ -16480,7 +16480,7 @@
         <v>3.25</v>
       </c>
       <c r="I83" t="n">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J83" t="n">
         <v>3.4</v>
@@ -16634,7 +16634,7 @@
       </c>
       <c r="BH83" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -16689,7 +16689,7 @@
         <v>1.17</v>
       </c>
       <c r="N84" t="n">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="O84" t="n">
         <v>1.74</v>
@@ -16710,7 +16710,7 @@
         <v>2.44</v>
       </c>
       <c r="U84" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="V84" t="n">
         <v>1.68</v>
@@ -16828,7 +16828,7 @@
       </c>
       <c r="BH84" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -17022,7 +17022,7 @@
       </c>
       <c r="BH85" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -17053,22 +17053,22 @@
         </is>
       </c>
       <c r="F86" t="n">
-        <v>2.98</v>
+        <v>3</v>
       </c>
       <c r="G86" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="H86" t="n">
         <v>2.38</v>
       </c>
       <c r="I86" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="J86" t="n">
         <v>3.3</v>
       </c>
       <c r="K86" t="n">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L86" t="n">
         <v>1.01</v>
@@ -17101,10 +17101,10 @@
         <v>1.75</v>
       </c>
       <c r="V86" t="n">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="W86" t="n">
-        <v>1.38</v>
+        <v>1.42</v>
       </c>
       <c r="X86" t="n">
         <v>20</v>
@@ -17216,7 +17216,7 @@
       </c>
       <c r="BH86" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -17250,7 +17250,7 @@
         <v>3.55</v>
       </c>
       <c r="G87" t="n">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="H87" t="n">
         <v>2.22</v>
@@ -17298,7 +17298,7 @@
         <v>1.7</v>
       </c>
       <c r="W87" t="n">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="X87" t="n">
         <v>12.5</v>
@@ -17410,7 +17410,7 @@
       </c>
       <c r="BH87" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -17441,40 +17441,40 @@
         </is>
       </c>
       <c r="F88" t="n">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="G88" t="n">
-        <v>5.4</v>
+        <v>4.8</v>
       </c>
       <c r="H88" t="n">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="I88" t="n">
-        <v>2.06</v>
+        <v>2.16</v>
       </c>
       <c r="J88" t="n">
-        <v>3.3</v>
+        <v>3.05</v>
       </c>
       <c r="K88" t="n">
-        <v>3.65</v>
+        <v>3.35</v>
       </c>
       <c r="L88" t="n">
         <v>1.54</v>
       </c>
       <c r="M88" t="n">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N88" t="n">
         <v>2.5</v>
       </c>
       <c r="O88" t="n">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="P88" t="n">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="Q88" t="n">
-        <v>2.6</v>
+        <v>2.72</v>
       </c>
       <c r="R88" t="n">
         <v>1.17</v>
@@ -17489,122 +17489,122 @@
         <v>1.66</v>
       </c>
       <c r="V88" t="n">
-        <v>1.95</v>
+        <v>1.86</v>
       </c>
       <c r="W88" t="n">
-        <v>1.22</v>
+        <v>1.26</v>
       </c>
       <c r="X88" t="n">
-        <v>9.199999999999999</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Y88" t="n">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="Z88" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AA88" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="AB88" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AC88" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AD88" t="n">
         <v>13</v>
       </c>
-      <c r="AC88" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AD88" t="n">
-        <v>12</v>
-      </c>
       <c r="AE88" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
       <c r="AF88" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="AG88" t="n">
-        <v>23</v>
+        <v>19.5</v>
       </c>
       <c r="AH88" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AI88" t="n">
-        <v>70</v>
+        <v>80</v>
       </c>
       <c r="AJ88" t="n">
-        <v>180</v>
+        <v>140</v>
       </c>
       <c r="AK88" t="n">
+        <v>85</v>
+      </c>
+      <c r="AL88" t="n">
         <v>120</v>
       </c>
-      <c r="AL88" t="n">
-        <v>140</v>
-      </c>
       <c r="AM88" t="n">
-        <v>300</v>
+        <v>270</v>
       </c>
       <c r="AN88" t="n">
-        <v>210</v>
+        <v>160</v>
       </c>
       <c r="AO88" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="AP88" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ88" t="n">
         <v>5.6</v>
       </c>
       <c r="AR88" t="n">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AS88" t="n">
-        <v>19.5</v>
+        <v>7.4</v>
       </c>
       <c r="AT88" t="n">
-        <v>10</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU88" t="n">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="AV88" t="n">
+        <v>10.5</v>
+      </c>
+      <c r="AW88" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AX88" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="AY88" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AZ88" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="BA88" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB88" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BC88" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BD88" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BE88" t="n">
         <v>9.6</v>
       </c>
-      <c r="AW88" t="n">
-        <v>6.8</v>
-      </c>
-      <c r="AX88" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AY88" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AZ88" t="n">
-        <v>7</v>
-      </c>
-      <c r="BA88" t="n">
-        <v>8</v>
-      </c>
-      <c r="BB88" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="BC88" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BD88" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BE88" t="n">
-        <v>8.800000000000001</v>
-      </c>
       <c r="BF88" t="n">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG88" t="n">
         <v>18.5</v>
       </c>
       <c r="BH88" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -17635,7 +17635,7 @@
         </is>
       </c>
       <c r="F89" t="n">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="G89" t="n">
         <v>1.57</v>
@@ -17798,7 +17798,7 @@
       </c>
       <c r="BH89" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -17853,7 +17853,7 @@
         <v>1.01</v>
       </c>
       <c r="N90" t="n">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="O90" t="n">
         <v>1.37</v>
@@ -17992,7 +17992,7 @@
       </c>
       <c r="BH90" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -18044,13 +18044,13 @@
         <v>1.01</v>
       </c>
       <c r="M91" t="n">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N91" t="n">
-        <v>2.38</v>
+        <v>3.05</v>
       </c>
       <c r="O91" t="n">
-        <v>1.01</v>
+        <v>1.42</v>
       </c>
       <c r="P91" t="n">
         <v>1.7</v>
@@ -18059,16 +18059,16 @@
         <v>2.22</v>
       </c>
       <c r="R91" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="S91" t="n">
-        <v>3.55</v>
+        <v>4.2</v>
       </c>
       <c r="T91" t="n">
-        <v>1.11</v>
+        <v>1.89</v>
       </c>
       <c r="U91" t="n">
-        <v>1.11</v>
+        <v>1.98</v>
       </c>
       <c r="V91" t="n">
         <v>1.5</v>
@@ -18077,116 +18077,116 @@
         <v>1.5</v>
       </c>
       <c r="X91" t="n">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="Y91" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z91" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AA91" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AB91" t="n">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC91" t="n">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AD91" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE91" t="n">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF91" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG91" t="n">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH91" t="n">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI91" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ91" t="n">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK91" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AL91" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM91" t="n">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AN91" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AO91" t="n">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AP91" t="n">
-        <v>1.16</v>
+        <v>9.6</v>
       </c>
       <c r="AQ91" t="n">
-        <v>1.16</v>
+        <v>8.6</v>
       </c>
       <c r="AR91" t="n">
-        <v>1.16</v>
+        <v>13.5</v>
       </c>
       <c r="AS91" t="n">
-        <v>1.16</v>
+        <v>4.4</v>
       </c>
       <c r="AT91" t="n">
-        <v>1.16</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AU91" t="n">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV91" t="n">
-        <v>1.16</v>
+        <v>11.5</v>
       </c>
       <c r="AW91" t="n">
-        <v>1.16</v>
+        <v>4.3</v>
       </c>
       <c r="AX91" t="n">
-        <v>1.16</v>
+        <v>13.5</v>
       </c>
       <c r="AY91" t="n">
-        <v>1.16</v>
+        <v>11.5</v>
       </c>
       <c r="AZ91" t="n">
-        <v>1.16</v>
+        <v>16.5</v>
       </c>
       <c r="BA91" t="n">
-        <v>1.16</v>
+        <v>4.4</v>
       </c>
       <c r="BB91" t="n">
-        <v>1.16</v>
+        <v>4.4</v>
       </c>
       <c r="BC91" t="n">
-        <v>1.16</v>
+        <v>4.3</v>
       </c>
       <c r="BD91" t="n">
-        <v>1.16</v>
+        <v>4.4</v>
       </c>
       <c r="BE91" t="n">
-        <v>1.16</v>
+        <v>4.6</v>
       </c>
       <c r="BF91" t="n">
-        <v>1.16</v>
+        <v>4.3</v>
       </c>
       <c r="BG91" t="n">
-        <v>1.16</v>
+        <v>4.3</v>
       </c>
       <c r="BH91" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -18380,7 +18380,7 @@
       </c>
       <c r="BH92" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
@@ -18402,186 +18402,186 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Racing Club</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Barracas Central</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="F93" t="n">
-        <v>1.14</v>
+        <v>2.48</v>
       </c>
       <c r="G93" t="n">
-        <v>1000</v>
+        <v>2.68</v>
       </c>
       <c r="H93" t="n">
-        <v>1.13</v>
+        <v>3.65</v>
       </c>
       <c r="I93" t="n">
-        <v>1000</v>
+        <v>4</v>
       </c>
       <c r="J93" t="n">
-        <v>1.1</v>
+        <v>2.74</v>
       </c>
       <c r="K93" t="n">
-        <v>950</v>
+        <v>2.96</v>
       </c>
       <c r="L93" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M93" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N93" t="n">
-        <v>1.1</v>
+        <v>0</v>
       </c>
       <c r="O93" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="P93" t="n">
-        <v>1.07</v>
+        <v>1.37</v>
       </c>
       <c r="Q93" t="n">
-        <v>1.01</v>
+        <v>3.25</v>
       </c>
       <c r="R93" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="T93" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="U93" t="n">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="V93" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="W93" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z93" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA93" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB93" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC93" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD93" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH93" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI93" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ93" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK93" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL93" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM93" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN93" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO93" t="n">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP93" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ93" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR93" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS93" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT93" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU93" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV93" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW93" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX93" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY93" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ93" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA93" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB93" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC93" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD93" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE93" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF93" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG93" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH93" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
@@ -18596,28 +18596,28 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Audax Italiano</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Deportes Limache</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="F94" t="n">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="G94" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="H94" t="n">
-        <v>2.86</v>
+        <v>1.13</v>
       </c>
       <c r="I94" t="n">
-        <v>990</v>
+        <v>1000</v>
       </c>
       <c r="J94" t="n">
-        <v>2.22</v>
+        <v>1.1</v>
       </c>
       <c r="K94" t="n">
         <v>950</v>
@@ -18629,22 +18629,22 @@
         <v>1.01</v>
       </c>
       <c r="N94" t="n">
-        <v>2.14</v>
+        <v>1.1</v>
       </c>
       <c r="O94" t="n">
-        <v>1.27</v>
+        <v>1.01</v>
       </c>
       <c r="P94" t="n">
-        <v>1.85</v>
+        <v>1.07</v>
       </c>
       <c r="Q94" t="n">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="R94" t="n">
-        <v>1.25</v>
+        <v>1.07</v>
       </c>
       <c r="S94" t="n">
-        <v>2.2</v>
+        <v>1.05</v>
       </c>
       <c r="T94" t="n">
         <v>1.11</v>
@@ -18653,10 +18653,10 @@
         <v>1.11</v>
       </c>
       <c r="V94" t="n">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="W94" t="n">
-        <v>1.49</v>
+        <v>1.01</v>
       </c>
       <c r="X94" t="n">
         <v>1000</v>
@@ -18768,7 +18768,201 @@
       </c>
       <c r="BH94" t="inlineStr">
         <is>
-          <t>2026-04-23 02:50:35</t>
+          <t>2026-04-23 05:10:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Chilean Primera Division</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>2026-04-24</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>21:30:00</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Audax Italiano</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Deportes Limache</t>
+        </is>
+      </c>
+      <c r="F95" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="G95" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="H95" t="n">
+        <v>2.92</v>
+      </c>
+      <c r="I95" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J95" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K95" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="L95" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="M95" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="N95" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="O95" t="n">
+        <v>1.27</v>
+      </c>
+      <c r="P95" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="R95" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="S95" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="T95" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="U95" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="V95" t="n">
+        <v>1.37</v>
+      </c>
+      <c r="W95" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="X95" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Y95" t="n">
+        <v>1000</v>
+      </c>
+      <c r="Z95" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AA95" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AB95" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AC95" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AD95" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AE95" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AG95" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AH95" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI95" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ95" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK95" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL95" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM95" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO95" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP95" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AQ95" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AR95" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AS95" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AT95" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AU95" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AV95" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AW95" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AX95" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AY95" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AZ95" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BA95" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BB95" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BC95" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BD95" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BE95" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BF95" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BG95" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="BH95" t="inlineStr">
+        <is>
+          <t>2026-04-23 05:10:25</t>
         </is>
       </c>
     </row>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-04-24.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-04-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BH12"/>
+  <dimension ref="A1:BH8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -733,7 +733,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Colombian Primera A</t>
+          <t>Brazilian Serie B</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -743,36 +743,36 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>18:00:00</t>
+          <t>20:00:00</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cucuta Deportivo</t>
+          <t>Ponte Preta</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Junior FC Barranquilla</t>
+          <t>America MG</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>3.3</v>
+        <v>1.25</v>
       </c>
       <c r="G2" t="n">
-        <v>3.4</v>
+        <v>1.28</v>
       </c>
       <c r="H2" t="n">
-        <v>3.9</v>
+        <v>42</v>
       </c>
       <c r="I2" t="n">
-        <v>4</v>
+        <v>55</v>
       </c>
       <c r="J2" t="n">
-        <v>2.22</v>
+        <v>5</v>
       </c>
       <c r="K2" t="n">
-        <v>2.24</v>
+        <v>5.7</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -781,34 +781,34 @@
         <v>0</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="P2" t="n">
-        <v>3.2</v>
+        <v>1.06</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.44</v>
+        <v>16</v>
       </c>
       <c r="R2" t="n">
-        <v>1.47</v>
+        <v>1.01</v>
       </c>
       <c r="S2" t="n">
-        <v>3.05</v>
+        <v>110</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V2" t="n">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="W2" t="n">
-        <v>1.41</v>
+        <v>4.5</v>
       </c>
       <c r="X2" t="n">
         <v>1000</v>
@@ -823,111 +823,111 @@
         <v>1000</v>
       </c>
       <c r="AB2" t="n">
-        <v>1000</v>
+        <v>1.57</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.15</v>
+        <v>8.4</v>
       </c>
       <c r="AD2" t="n">
-        <v>5.8</v>
+        <v>1000</v>
       </c>
       <c r="AE2" t="n">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AF2" t="n">
-        <v>1000</v>
+        <v>800</v>
       </c>
       <c r="AG2" t="n">
-        <v>5.2</v>
+        <v>990</v>
       </c>
       <c r="AH2" t="n">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AI2" t="n">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ2" t="n">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AK2" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AL2" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AM2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AS2" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AT2" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="AU2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>42</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="AZ2" t="n">
         <v>160</v>
       </c>
-      <c r="AN2" t="n">
-        <v>75</v>
-      </c>
-      <c r="AO2" t="n">
-        <v>110</v>
-      </c>
-      <c r="AP2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AQ2" t="n">
-        <v>26</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>27</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>25</v>
-      </c>
-      <c r="AT2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AU2" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="AV2" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="AW2" t="n">
-        <v>23</v>
-      </c>
-      <c r="AX2" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AY2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>8.6</v>
-      </c>
       <c r="BA2" t="n">
-        <v>36</v>
+        <v>5.9</v>
       </c>
       <c r="BB2" t="n">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BC2" t="n">
-        <v>17.5</v>
+        <v>7.2</v>
       </c>
       <c r="BD2" t="n">
-        <v>32</v>
+        <v>6.8</v>
       </c>
       <c r="BE2" t="n">
-        <v>100</v>
+        <v>5.9</v>
       </c>
       <c r="BF2" t="n">
-        <v>40</v>
+        <v>5.9</v>
       </c>
       <c r="BG2" t="n">
-        <v>65</v>
+        <v>5.9</v>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2026-04-24 19:33:15</t>
+          <t>2026-04-24 22:06:19</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Chilean Primera Division</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -937,191 +937,191 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>19:00:00</t>
+          <t>20:10:00</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Union La Calera</t>
+          <t>Tigres FC Zipaquira</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Coquimbo Unido</t>
+          <t>Internacional de Palmira</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2.96</v>
+        <v>6.4</v>
       </c>
       <c r="G3" t="n">
-        <v>3.05</v>
+        <v>7.6</v>
       </c>
       <c r="H3" t="n">
-        <v>2.78</v>
+        <v>6.2</v>
       </c>
       <c r="I3" t="n">
-        <v>2.84</v>
+        <v>6.8</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2</v>
+        <v>1.41</v>
       </c>
       <c r="K3" t="n">
-        <v>3.3</v>
+        <v>1.44</v>
       </c>
       <c r="L3" t="n">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>1.12</v>
+        <v>2.88</v>
       </c>
       <c r="N3" t="n">
-        <v>2.84</v>
+        <v>1.06</v>
       </c>
       <c r="O3" t="n">
-        <v>1.52</v>
+        <v>13.5</v>
       </c>
       <c r="P3" t="n">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="Q3" t="n">
-        <v>2.6</v>
+        <v>110</v>
       </c>
       <c r="R3" t="n">
-        <v>1.21</v>
+        <v>1.01</v>
       </c>
       <c r="S3" t="n">
-        <v>5.6</v>
+        <v>200</v>
       </c>
       <c r="T3" t="n">
-        <v>2.1</v>
+        <v>18.5</v>
       </c>
       <c r="U3" t="n">
-        <v>1.84</v>
+        <v>1.03</v>
       </c>
       <c r="V3" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W3" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X3" t="n">
         <v>1.53</v>
       </c>
-      <c r="W3" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="X3" t="n">
-        <v>9.6</v>
-      </c>
       <c r="Y3" t="n">
-        <v>8.800000000000001</v>
+        <v>7.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>17.5</v>
+        <v>85</v>
       </c>
       <c r="AA3" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AB3" t="n">
-        <v>9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC3" t="n">
+        <v>40</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>490</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>970</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>550</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AO3" t="n">
+        <v>1000</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>50</v>
+      </c>
+      <c r="AS3" t="n">
+        <v>110</v>
+      </c>
+      <c r="AT3" t="n">
         <v>7.2</v>
       </c>
-      <c r="AD3" t="n">
-        <v>13</v>
-      </c>
-      <c r="AE3" t="n">
-        <v>40</v>
-      </c>
-      <c r="AF3" t="n">
-        <v>18</v>
-      </c>
-      <c r="AG3" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AH3" t="n">
-        <v>22</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AK3" t="n">
-        <v>44</v>
-      </c>
-      <c r="AL3" t="n">
-        <v>80</v>
-      </c>
-      <c r="AM3" t="n">
-        <v>200</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>60</v>
-      </c>
-      <c r="AO3" t="n">
+      <c r="AU3" t="n">
+        <v>28</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>100</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>70</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>75</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>240</v>
+      </c>
+      <c r="AZ3" t="n">
+        <v>110</v>
+      </c>
+      <c r="BA3" t="n">
         <v>46</v>
       </c>
-      <c r="AP3" t="n">
-        <v>9</v>
-      </c>
-      <c r="AQ3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AR3" t="n">
+      <c r="BB3" t="n">
+        <v>90</v>
+      </c>
+      <c r="BC3" t="n">
+        <v>90</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>46</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>70</v>
+      </c>
+      <c r="BF3" t="n">
         <v>15.5</v>
       </c>
-      <c r="AS3" t="n">
-        <v>36</v>
-      </c>
-      <c r="AT3" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU3" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AV3" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AW3" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX3" t="n">
-        <v>16</v>
-      </c>
-      <c r="AY3" t="n">
-        <v>12</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA3" t="n">
-        <v>50</v>
-      </c>
-      <c r="BB3" t="n">
-        <v>42</v>
-      </c>
-      <c r="BC3" t="n">
-        <v>36</v>
-      </c>
-      <c r="BD3" t="n">
-        <v>50</v>
-      </c>
-      <c r="BE3" t="n">
-        <v>110</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>40</v>
-      </c>
       <c r="BG3" t="n">
-        <v>36</v>
+        <v>15.5</v>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2026-04-24 19:33:15</t>
+          <t>2026-04-24 22:06:19</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Argentinian Primera Division</t>
+          <t>Bolivian Liga de Futbol Profesional</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1131,184 +1131,184 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>21:00:00</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Estudiantes Rio Cuarto</t>
+          <t>Club Independiente Petro</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Rosario Central</t>
+          <t>Universitario de Vinto</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>4.7</v>
+        <v>2.3</v>
       </c>
       <c r="G4" t="n">
-        <v>4.9</v>
+        <v>2.4</v>
       </c>
       <c r="H4" t="n">
-        <v>2.12</v>
+        <v>3.8</v>
       </c>
       <c r="I4" t="n">
-        <v>2.14</v>
+        <v>4</v>
       </c>
       <c r="J4" t="n">
         <v>3.1</v>
       </c>
       <c r="K4" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L4" t="n">
-        <v>1.65</v>
+        <v>3.4</v>
       </c>
       <c r="M4" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="N4" t="n">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="O4" t="n">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="P4" t="n">
-        <v>1.49</v>
+        <v>1.53</v>
       </c>
       <c r="Q4" t="n">
-        <v>2.96</v>
+        <v>2.86</v>
       </c>
       <c r="R4" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="S4" t="n">
         <v>6.4</v>
       </c>
       <c r="T4" t="n">
-        <v>2.36</v>
+        <v>2.26</v>
       </c>
       <c r="U4" t="n">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="V4" t="n">
-        <v>1.87</v>
+        <v>1.32</v>
       </c>
       <c r="W4" t="n">
-        <v>1.26</v>
+        <v>1.71</v>
       </c>
       <c r="X4" t="n">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="Y4" t="n">
-        <v>6.4</v>
+        <v>10.5</v>
       </c>
       <c r="Z4" t="n">
-        <v>11</v>
+        <v>23</v>
       </c>
       <c r="AA4" t="n">
-        <v>26</v>
+        <v>85</v>
       </c>
       <c r="AB4" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="AC4" t="n">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AD4" t="n">
-        <v>11.5</v>
+        <v>19</v>
       </c>
       <c r="AE4" t="n">
-        <v>34</v>
+        <v>80</v>
       </c>
       <c r="AF4" t="n">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="AG4" t="n">
-        <v>21</v>
+        <v>13.5</v>
       </c>
       <c r="AH4" t="n">
         <v>29</v>
       </c>
       <c r="AI4" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="AJ4" t="n">
-        <v>130</v>
+        <v>36</v>
       </c>
       <c r="AK4" t="n">
+        <v>40</v>
+      </c>
+      <c r="AL4" t="n">
         <v>95</v>
       </c>
-      <c r="AL4" t="n">
-        <v>130</v>
-      </c>
       <c r="AM4" t="n">
-        <v>250</v>
+        <v>300</v>
       </c>
       <c r="AN4" t="n">
-        <v>190</v>
+        <v>46</v>
       </c>
       <c r="AO4" t="n">
-        <v>32</v>
+        <v>120</v>
       </c>
       <c r="AP4" t="n">
         <v>7.2</v>
       </c>
       <c r="AQ4" t="n">
-        <v>6</v>
+        <v>9.4</v>
       </c>
       <c r="AR4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AS4" t="n">
-        <v>24</v>
+        <v>65</v>
       </c>
       <c r="AT4" t="n">
-        <v>10</v>
+        <v>6.6</v>
       </c>
       <c r="AU4" t="n">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV4" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>50</v>
+      </c>
+      <c r="AX4" t="n">
         <v>10.5</v>
       </c>
-      <c r="AW4" t="n">
-        <v>29</v>
-      </c>
-      <c r="AX4" t="n">
-        <v>28</v>
-      </c>
       <c r="AY4" t="n">
-        <v>19</v>
+        <v>11.5</v>
       </c>
       <c r="AZ4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="BA4" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="BB4" t="n">
-        <v>100</v>
+        <v>27</v>
       </c>
       <c r="BC4" t="n">
-        <v>80</v>
+        <v>30</v>
       </c>
       <c r="BD4" t="n">
-        <v>42</v>
+        <v>65</v>
       </c>
       <c r="BE4" t="n">
-        <v>80</v>
+        <v>200</v>
       </c>
       <c r="BF4" t="n">
-        <v>130</v>
+        <v>30</v>
       </c>
       <c r="BG4" t="n">
-        <v>27</v>
+        <v>70</v>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2026-04-24 19:33:15</t>
+          <t>2026-04-24 22:06:19</t>
         </is>
       </c>
     </row>
@@ -1325,191 +1325,191 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>19:15:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Lanus</t>
+          <t>CA Platense</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Central Cordoba (SdE)</t>
+          <t>San Lorenzo</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1.45</v>
+        <v>2.52</v>
       </c>
       <c r="G5" t="n">
-        <v>1.47</v>
+        <v>2.58</v>
       </c>
       <c r="H5" t="n">
-        <v>10</v>
+        <v>3.8</v>
       </c>
       <c r="I5" t="n">
-        <v>11</v>
+        <v>4.2</v>
       </c>
       <c r="J5" t="n">
-        <v>4.5</v>
+        <v>2.78</v>
       </c>
       <c r="K5" t="n">
-        <v>4.6</v>
+        <v>2.92</v>
       </c>
       <c r="L5" t="n">
-        <v>1.49</v>
+        <v>1.86</v>
       </c>
       <c r="M5" t="n">
-        <v>1.09</v>
+        <v>1.2</v>
       </c>
       <c r="N5" t="n">
-        <v>3.3</v>
+        <v>2.1</v>
       </c>
       <c r="O5" t="n">
-        <v>1.42</v>
+        <v>1.86</v>
       </c>
       <c r="P5" t="n">
-        <v>1.78</v>
+        <v>1.34</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.26</v>
+        <v>3.75</v>
       </c>
       <c r="R5" t="n">
-        <v>1.29</v>
+        <v>1.11</v>
       </c>
       <c r="S5" t="n">
-        <v>4.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="T5" t="n">
         <v>2.54</v>
       </c>
       <c r="U5" t="n">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="V5" t="n">
-        <v>1.1</v>
+        <v>1.33</v>
       </c>
       <c r="W5" t="n">
-        <v>3.15</v>
+        <v>1.62</v>
       </c>
       <c r="X5" t="n">
-        <v>11.5</v>
+        <v>5.9</v>
       </c>
       <c r="Y5" t="n">
-        <v>24</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="Z5" t="n">
-        <v>110</v>
+        <v>29</v>
       </c>
       <c r="AA5" t="n">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB5" t="n">
         <v>6.2</v>
       </c>
       <c r="AC5" t="n">
-        <v>10.5</v>
+        <v>7.2</v>
       </c>
       <c r="AD5" t="n">
-        <v>42</v>
+        <v>19</v>
       </c>
       <c r="AE5" t="n">
-        <v>290</v>
+        <v>100</v>
       </c>
       <c r="AF5" t="n">
-        <v>6.8</v>
+        <v>14.5</v>
       </c>
       <c r="AG5" t="n">
-        <v>10.5</v>
+        <v>15</v>
       </c>
       <c r="AH5" t="n">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AI5" t="n">
-        <v>540</v>
+        <v>160</v>
       </c>
       <c r="AJ5" t="n">
-        <v>11.5</v>
+        <v>48</v>
       </c>
       <c r="AK5" t="n">
-        <v>18.5</v>
+        <v>55</v>
       </c>
       <c r="AL5" t="n">
+        <v>130</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>440</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>85</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>180</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>5.4</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AS5" t="n">
+        <v>80</v>
+      </c>
+      <c r="AT5" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="AU5" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AW5" t="n">
         <v>70</v>
       </c>
-      <c r="AM5" t="n">
-        <v>300</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>11</v>
-      </c>
-      <c r="AQ5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>80</v>
-      </c>
-      <c r="AS5" t="n">
-        <v>130</v>
-      </c>
-      <c r="AT5" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AU5" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AV5" t="n">
-        <v>40</v>
-      </c>
-      <c r="AW5" t="n">
-        <v>48</v>
-      </c>
       <c r="AX5" t="n">
-        <v>6.6</v>
+        <v>12</v>
       </c>
       <c r="AY5" t="n">
-        <v>9.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="AZ5" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="BA5" t="n">
-        <v>50</v>
+        <v>110</v>
       </c>
       <c r="BB5" t="n">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="BC5" t="n">
-        <v>17.5</v>
+        <v>44</v>
       </c>
       <c r="BD5" t="n">
+        <v>95</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>230</v>
+      </c>
+      <c r="BF5" t="n">
         <v>60</v>
       </c>
-      <c r="BE5" t="n">
-        <v>65</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BG5" t="n">
-        <v>55</v>
+        <v>95</v>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2026-04-24 19:33:15</t>
+          <t>2026-04-24 22:06:19</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Brazilian Serie B</t>
+          <t>Argentinian Primera Division</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1519,191 +1519,191 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>20:00:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Ponte Preta</t>
+          <t>Racing Club</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>America MG</t>
+          <t>Barracas Central</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>3</v>
+        <v>2.2</v>
       </c>
       <c r="G6" t="n">
-        <v>3.15</v>
+        <v>2.48</v>
       </c>
       <c r="H6" t="n">
-        <v>2.76</v>
+        <v>3.5</v>
       </c>
       <c r="I6" t="n">
-        <v>2.88</v>
+        <v>5</v>
       </c>
       <c r="J6" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="K6" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="L6" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="M6" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="O6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="P6" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="Q6" t="n">
         <v>3.1</v>
       </c>
-      <c r="K6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="L6" t="n">
-        <v>1.55</v>
-      </c>
-      <c r="M6" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N6" t="n">
-        <v>2.92</v>
-      </c>
-      <c r="O6" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="P6" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>2.5</v>
-      </c>
       <c r="R6" t="n">
-        <v>1.22</v>
+        <v>1.11</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="T6" t="n">
         <v>2</v>
       </c>
       <c r="U6" t="n">
-        <v>1.91</v>
+        <v>1.45</v>
       </c>
       <c r="V6" t="n">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="W6" t="n">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="X6" t="n">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="Y6" t="n">
-        <v>9</v>
+        <v>60</v>
       </c>
       <c r="Z6" t="n">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AA6" t="n">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AB6" t="n">
-        <v>9.4</v>
+        <v>27</v>
       </c>
       <c r="AC6" t="n">
-        <v>7</v>
+        <v>990</v>
       </c>
       <c r="AD6" t="n">
-        <v>13</v>
+        <v>990</v>
       </c>
       <c r="AE6" t="n">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="AF6" t="n">
-        <v>19</v>
+        <v>1000</v>
       </c>
       <c r="AG6" t="n">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AH6" t="n">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AI6" t="n">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AJ6" t="n">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AK6" t="n">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="AL6" t="n">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AM6" t="n">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN6" t="n">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="AO6" t="n">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="AP6" t="n">
-        <v>8.6</v>
+        <v>1.21</v>
       </c>
       <c r="AQ6" t="n">
-        <v>8.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR6" t="n">
-        <v>15.5</v>
+        <v>2.9</v>
       </c>
       <c r="AS6" t="n">
-        <v>40</v>
+        <v>1.41</v>
       </c>
       <c r="AT6" t="n">
-        <v>9</v>
+        <v>5.6</v>
       </c>
       <c r="AU6" t="n">
-        <v>6.6</v>
+        <v>5.7</v>
       </c>
       <c r="AV6" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>7.2</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AZ6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BA6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BB6" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="BC6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="BF6" t="n">
         <v>12.5</v>
       </c>
-      <c r="AW6" t="n">
-        <v>32</v>
-      </c>
-      <c r="AX6" t="n">
-        <v>17</v>
-      </c>
-      <c r="AY6" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>19</v>
-      </c>
-      <c r="BA6" t="n">
-        <v>40</v>
-      </c>
-      <c r="BB6" t="n">
-        <v>18</v>
-      </c>
-      <c r="BC6" t="n">
-        <v>36</v>
-      </c>
-      <c r="BD6" t="n">
-        <v>40</v>
-      </c>
-      <c r="BE6" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>44</v>
-      </c>
       <c r="BG6" t="n">
-        <v>40</v>
+        <v>4.5</v>
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2026-04-24 19:33:15</t>
+          <t>2026-04-24 22:06:19</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Colombian Primera B</t>
+          <t>Chilean Primera Division</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1713,191 +1713,191 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>20:10:00</t>
+          <t>21:30:00</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Tigres FC Zipaquira</t>
+          <t>Audax Italiano</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Internacional de Palmira</t>
+          <t>Deportes Limache</t>
         </is>
       </c>
       <c r="F7" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="G7" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="H7" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="I7" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J7" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K7" t="n">
         <v>3.5</v>
       </c>
-      <c r="G7" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="H7" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="I7" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="J7" t="n">
-        <v>3</v>
-      </c>
-      <c r="K7" t="n">
+      <c r="L7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="M7" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="N7" t="n">
         <v>3.25</v>
       </c>
-      <c r="L7" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="M7" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N7" t="n">
-        <v>2.82</v>
-      </c>
       <c r="O7" t="n">
-        <v>1.52</v>
+        <v>1.41</v>
       </c>
       <c r="P7" t="n">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.58</v>
+        <v>2.26</v>
       </c>
       <c r="R7" t="n">
-        <v>1.21</v>
+        <v>1.31</v>
       </c>
       <c r="S7" t="n">
-        <v>5.2</v>
+        <v>4.2</v>
       </c>
       <c r="T7" t="n">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="U7" t="n">
-        <v>1.81</v>
+        <v>1.95</v>
       </c>
       <c r="V7" t="n">
-        <v>1.65</v>
+        <v>1.48</v>
       </c>
       <c r="W7" t="n">
-        <v>1.36</v>
+        <v>1.59</v>
       </c>
       <c r="X7" t="n">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="Y7" t="n">
+        <v>11</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>21</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>60</v>
+      </c>
+      <c r="AB7" t="n">
         <v>9.6</v>
       </c>
-      <c r="Z7" t="n">
-        <v>18</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>38</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>19</v>
-      </c>
       <c r="AC7" t="n">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AE7" t="n">
-        <v>34</v>
+        <v>40</v>
       </c>
       <c r="AF7" t="n">
-        <v>27</v>
+        <v>17</v>
       </c>
       <c r="AG7" t="n">
-        <v>950</v>
+        <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>950</v>
+        <v>21</v>
       </c>
       <c r="AI7" t="n">
         <v>65</v>
       </c>
       <c r="AJ7" t="n">
-        <v>80</v>
+        <v>42</v>
       </c>
       <c r="AK7" t="n">
+        <v>36</v>
+      </c>
+      <c r="AL7" t="n">
         <v>55</v>
       </c>
-      <c r="AL7" t="n">
-        <v>80</v>
-      </c>
       <c r="AM7" t="n">
-        <v>220</v>
+        <v>150</v>
       </c>
       <c r="AN7" t="n">
-        <v>85</v>
+        <v>36</v>
       </c>
       <c r="AO7" t="n">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AP7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AQ7" t="n">
-        <v>6.8</v>
+        <v>9.4</v>
       </c>
       <c r="AR7" t="n">
-        <v>6.8</v>
+        <v>16.5</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.800000000000001</v>
+        <v>42</v>
       </c>
       <c r="AT7" t="n">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AU7" t="n">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="AV7" t="n">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AW7" t="n">
-        <v>8.6</v>
+        <v>32</v>
       </c>
       <c r="AX7" t="n">
-        <v>8.4</v>
+        <v>13.5</v>
       </c>
       <c r="AY7" t="n">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AZ7" t="n">
-        <v>8.199999999999999</v>
+        <v>16.5</v>
       </c>
       <c r="BA7" t="n">
-        <v>11</v>
+        <v>46</v>
       </c>
       <c r="BB7" t="n">
-        <v>10.5</v>
+        <v>34</v>
       </c>
       <c r="BC7" t="n">
-        <v>10.5</v>
+        <v>27</v>
       </c>
       <c r="BD7" t="n">
-        <v>11</v>
+        <v>42</v>
       </c>
       <c r="BE7" t="n">
-        <v>5</v>
+        <v>95</v>
       </c>
       <c r="BF7" t="n">
-        <v>8.199999999999999</v>
+        <v>26</v>
       </c>
       <c r="BG7" t="n">
-        <v>10</v>
+        <v>32</v>
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2026-04-24 19:33:15</t>
+          <t>2026-04-24 22:06:19</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Bolivian Liga de Futbol Profesional</t>
+          <t>Colombian Primera B</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1907,960 +1907,184 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>21:00:00</t>
+          <t>22:15:00</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Club Independiente Petro</t>
+          <t>Quindio</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Universitario de Vinto</t>
+          <t>Envigado</t>
         </is>
       </c>
       <c r="F8" t="n">
-        <v>2.3</v>
+        <v>2.44</v>
       </c>
       <c r="G8" t="n">
-        <v>2.42</v>
+        <v>2.54</v>
       </c>
       <c r="H8" t="n">
-        <v>2.86</v>
+        <v>3.45</v>
       </c>
       <c r="I8" t="n">
-        <v>3.05</v>
+        <v>3.8</v>
       </c>
       <c r="J8" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="K8" t="n">
-        <v>4.5</v>
+        <v>3.25</v>
       </c>
       <c r="L8" t="n">
-        <v>1.26</v>
+        <v>1.57</v>
       </c>
       <c r="M8" t="n">
-        <v>1.03</v>
+        <v>1.12</v>
       </c>
       <c r="N8" t="n">
-        <v>6.8</v>
+        <v>2.78</v>
       </c>
       <c r="O8" t="n">
-        <v>1.15</v>
+        <v>1.51</v>
       </c>
       <c r="P8" t="n">
-        <v>2.96</v>
+        <v>1.58</v>
       </c>
       <c r="Q8" t="n">
-        <v>1.47</v>
+        <v>2.58</v>
       </c>
       <c r="R8" t="n">
-        <v>1.79</v>
+        <v>1.2</v>
       </c>
       <c r="S8" t="n">
-        <v>2.18</v>
+        <v>5.2</v>
       </c>
       <c r="T8" t="n">
-        <v>1.49</v>
+        <v>2.06</v>
       </c>
       <c r="U8" t="n">
-        <v>2.92</v>
+        <v>1.84</v>
       </c>
       <c r="V8" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="W8" t="n">
-        <v>1.71</v>
+        <v>1.64</v>
       </c>
       <c r="X8" t="n">
-        <v>30</v>
+        <v>9</v>
       </c>
       <c r="Y8" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="Z8" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="AA8" t="n">
-        <v>65</v>
+        <v>90</v>
       </c>
       <c r="AB8" t="n">
-        <v>19.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC8" t="n">
-        <v>10.5</v>
+        <v>7.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AE8" t="n">
+        <v>70</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>15</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AH8" t="n">
         <v>28</v>
       </c>
-      <c r="AF8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG8" t="n">
+      <c r="AI8" t="n">
+        <v>110</v>
+      </c>
+      <c r="AJ8" t="n">
+        <v>42</v>
+      </c>
+      <c r="AK8" t="n">
+        <v>48</v>
+      </c>
+      <c r="AL8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AM8" t="n">
+        <v>820</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>55</v>
+      </c>
+      <c r="AO8" t="n">
+        <v>100</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS8" t="n">
+        <v>50</v>
+      </c>
+      <c r="AT8" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AU8" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AX8" t="n">
         <v>12</v>
       </c>
-      <c r="AH8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AI8" t="n">
-        <v>29</v>
-      </c>
-      <c r="AJ8" t="n">
-        <v>65</v>
-      </c>
-      <c r="AK8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL8" t="n">
-        <v>25</v>
-      </c>
-      <c r="AM8" t="n">
-        <v>75</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AO8" t="n">
-        <v>14</v>
-      </c>
-      <c r="AP8" t="n">
-        <v>22</v>
-      </c>
-      <c r="AQ8" t="n">
-        <v>20</v>
-      </c>
-      <c r="AR8" t="n">
-        <v>23</v>
-      </c>
-      <c r="AS8" t="n">
-        <v>30</v>
-      </c>
-      <c r="AT8" t="n">
-        <v>17</v>
-      </c>
-      <c r="AU8" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AV8" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AW8" t="n">
-        <v>21</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>18</v>
-      </c>
       <c r="AY8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AZ8" t="n">
-        <v>12</v>
+        <v>19</v>
       </c>
       <c r="BA8" t="n">
-        <v>25</v>
+        <v>46</v>
       </c>
       <c r="BB8" t="n">
         <v>27</v>
       </c>
       <c r="BC8" t="n">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="BD8" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="BE8" t="n">
-        <v>34</v>
+        <v>130</v>
       </c>
       <c r="BF8" t="n">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="BG8" t="n">
-        <v>12.5</v>
+        <v>46</v>
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2026-04-24 19:33:15</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Argentinian Primera Division</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>CA Platense</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>San Lorenzo</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="G9" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="H9" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="I9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J9" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="K9" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="L9" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="M9" t="n">
-        <v>1.19</v>
-      </c>
-      <c r="N9" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="O9" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="P9" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="Q9" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="S9" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="T9" t="n">
-        <v>2.52</v>
-      </c>
-      <c r="U9" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="V9" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="W9" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="X9" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>8.6</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>95</v>
-      </c>
-      <c r="AB9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AC9" t="n">
-        <v>7</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>85</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>14.5</v>
-      </c>
-      <c r="AH9" t="n">
-        <v>32</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>140</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>42</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>48</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>100</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>330</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>65</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>140</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>5.8</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>8</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>22</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>60</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>6</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>17</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>55</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>13</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>28</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>42</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>38</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>42</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>48</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>21</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>40</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>42</v>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>2026-04-24 19:33:15</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Argentinian Primera Division</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Racing Club</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Barracas Central</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="H10" t="n">
-        <v>9</v>
-      </c>
-      <c r="I10" t="n">
-        <v>9.4</v>
-      </c>
-      <c r="J10" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K10" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="L10" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="M10" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="N10" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="O10" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="P10" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="S10" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.46</v>
-      </c>
-      <c r="U10" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="V10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="X10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>22</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>80</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>470</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>5.9</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AE10" t="n">
-        <v>250</v>
-      </c>
-      <c r="AF10" t="n">
-        <v>7.2</v>
-      </c>
-      <c r="AG10" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>55</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>230</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AK10" t="n">
-        <v>21</v>
-      </c>
-      <c r="AL10" t="n">
-        <v>70</v>
-      </c>
-      <c r="AM10" t="n">
-        <v>330</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AO10" t="n">
-        <v>1000</v>
-      </c>
-      <c r="AP10" t="n">
-        <v>9.6</v>
-      </c>
-      <c r="AQ10" t="n">
-        <v>18.5</v>
-      </c>
-      <c r="AR10" t="n">
-        <v>48</v>
-      </c>
-      <c r="AS10" t="n">
-        <v>13</v>
-      </c>
-      <c r="AT10" t="n">
-        <v>5.3</v>
-      </c>
-      <c r="AU10" t="n">
-        <v>9</v>
-      </c>
-      <c r="AV10" t="n">
-        <v>30</v>
-      </c>
-      <c r="AW10" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AX10" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AY10" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>28</v>
-      </c>
-      <c r="BA10" t="n">
-        <v>14</v>
-      </c>
-      <c r="BB10" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="BC10" t="n">
-        <v>16</v>
-      </c>
-      <c r="BD10" t="n">
-        <v>44</v>
-      </c>
-      <c r="BE10" t="n">
-        <v>13</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>10.5</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>18</v>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>2026-04-24 19:33:15</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Chilean Primera Division</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>21:30:00</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Audax Italiano</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Deportes Limache</t>
-        </is>
-      </c>
-      <c r="F11" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="G11" t="n">
-        <v>2.84</v>
-      </c>
-      <c r="H11" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="I11" t="n">
-        <v>2.76</v>
-      </c>
-      <c r="J11" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="K11" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="L11" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="M11" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="N11" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="O11" t="n">
-        <v>1.28</v>
-      </c>
-      <c r="P11" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="R11" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="S11" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="T11" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="U11" t="n">
-        <v>2.32</v>
-      </c>
-      <c r="V11" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="W11" t="n">
-        <v>1.54</v>
-      </c>
-      <c r="X11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="Y11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="Z11" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>13</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>12</v>
-      </c>
-      <c r="AE11" t="n">
-        <v>28</v>
-      </c>
-      <c r="AF11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>12.5</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>38</v>
-      </c>
-      <c r="AJ11" t="n">
-        <v>44</v>
-      </c>
-      <c r="AK11" t="n">
-        <v>29</v>
-      </c>
-      <c r="AL11" t="n">
-        <v>40</v>
-      </c>
-      <c r="AM11" t="n">
-        <v>80</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>23</v>
-      </c>
-      <c r="AO11" t="n">
-        <v>21</v>
-      </c>
-      <c r="AP11" t="n">
-        <v>15</v>
-      </c>
-      <c r="AQ11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AR11" t="n">
-        <v>16.5</v>
-      </c>
-      <c r="AS11" t="n">
-        <v>26</v>
-      </c>
-      <c r="AT11" t="n">
-        <v>11.5</v>
-      </c>
-      <c r="AU11" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AV11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AW11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="AX11" t="n">
-        <v>17.5</v>
-      </c>
-      <c r="AY11" t="n">
-        <v>11</v>
-      </c>
-      <c r="AZ11" t="n">
-        <v>14</v>
-      </c>
-      <c r="BA11" t="n">
-        <v>30</v>
-      </c>
-      <c r="BB11" t="n">
-        <v>24</v>
-      </c>
-      <c r="BC11" t="n">
-        <v>24</v>
-      </c>
-      <c r="BD11" t="n">
-        <v>27</v>
-      </c>
-      <c r="BE11" t="n">
-        <v>48</v>
-      </c>
-      <c r="BF11" t="n">
-        <v>19.5</v>
-      </c>
-      <c r="BG11" t="n">
-        <v>18</v>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>2026-04-24 19:33:15</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Colombian Primera B</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-04-24</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>22:15:00</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Quindio</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Envigado</t>
-        </is>
-      </c>
-      <c r="F12" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="G12" t="n">
-        <v>2.62</v>
-      </c>
-      <c r="H12" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="I12" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="J12" t="n">
-        <v>2.98</v>
-      </c>
-      <c r="K12" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L12" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="M12" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="N12" t="n">
-        <v>2.74</v>
-      </c>
-      <c r="O12" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="P12" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>2.58</v>
-      </c>
-      <c r="R12" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="S12" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="T12" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="X12" t="n">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="Y12" t="n">
-        <v>11</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>25</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>80</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AD12" t="n">
-        <v>950</v>
-      </c>
-      <c r="AE12" t="n">
-        <v>60</v>
-      </c>
-      <c r="AF12" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="AG12" t="n">
-        <v>950</v>
-      </c>
-      <c r="AH12" t="n">
-        <v>950</v>
-      </c>
-      <c r="AI12" t="n">
-        <v>80</v>
-      </c>
-      <c r="AJ12" t="n">
-        <v>40</v>
-      </c>
-      <c r="AK12" t="n">
-        <v>36</v>
-      </c>
-      <c r="AL12" t="n">
-        <v>65</v>
-      </c>
-      <c r="AM12" t="n">
-        <v>190</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>38</v>
-      </c>
-      <c r="AO12" t="n">
-        <v>80</v>
-      </c>
-      <c r="AP12" t="n">
-        <v>4.7</v>
-      </c>
-      <c r="AQ12" t="n">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AR12" t="n">
-        <v>20</v>
-      </c>
-      <c r="AS12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AT12" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="AU12" t="n">
-        <v>6.2</v>
-      </c>
-      <c r="AV12" t="n">
-        <v>13.5</v>
-      </c>
-      <c r="AW12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AX12" t="n">
-        <v>12</v>
-      </c>
-      <c r="AY12" t="n">
-        <v>10</v>
-      </c>
-      <c r="AZ12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BA12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BB12" t="n">
-        <v>30</v>
-      </c>
-      <c r="BC12" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="BD12" t="n">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="BE12" t="n">
-        <v>9</v>
-      </c>
-      <c r="BF12" t="n">
-        <v>7.6</v>
-      </c>
-      <c r="BG12" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>2026-04-24 19:33:15</t>
+          <t>2026-04-24 22:06:19</t>
         </is>
       </c>
     </row>
